--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7660479779482341</v>
+        <v>0.7660479779482339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1866889045987777</v>
+        <v>0.1866889045987776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4932106465203208</v>
+        <v>0.4932106465203206</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05360369613219044</v>
+        <v>0.05360369613219043</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921175811433187e-05</v>
+        <v>7.921175811433154e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.0001714878572393352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005394736185933638</v>
+        <v>0.0005394736185933622</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004121356485860285</v>
+        <v>0.0004121356485860273</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000453619265089943</v>
+        <v>0.000453619265089941</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003668849361264691</v>
+        <v>0.0003668849361264688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001415921500504478</v>
+        <v>0.001415921500504445</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599611269127</v>
+        <v>0.02910599611269149</v>
       </c>
     </row>
     <row r="3">
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7621699919335372</v>
+        <v>0.7621699919335371</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853547660920927</v>
+        <v>0.1853547660920928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4918893120110954</v>
+        <v>0.4918893120110955</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05252503758493637</v>
+        <v>0.05252503758493641</v>
       </c>
       <c r="H3" t="n">
-        <v>7.137165240197179e-05</v>
+        <v>7.13716524019717e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.000162708354477617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005168698152984767</v>
+        <v>0.0005168698152984818</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004066695497614141</v>
+        <v>0.0004066695497614152</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004338473151447467</v>
+        <v>0.0004338473151447451</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003617932932367358</v>
+        <v>0.0003617932932367356</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001341620180368657</v>
+        <v>0.001341620180368709</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0291059960847232</v>
+        <v>0.02910599608472264</v>
       </c>
     </row>
     <row r="4">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7578078941797338</v>
+        <v>0.7578078941797345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.184507178013775</v>
+        <v>0.1845071780137751</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4909672958858871</v>
+        <v>0.4909672958858874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007991238058413</v>
+        <v>0.05007991238058419</v>
       </c>
       <c r="H4" t="n">
-        <v>6.998006613657974e-05</v>
+        <v>6.998006613657981e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001558665476670602</v>
+        <v>0.0001558665476670605</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004949566457814372</v>
+        <v>0.0004949566457814393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003988781058089494</v>
+        <v>0.0003988781058089502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004233356256196214</v>
+        <v>0.0004233356256196216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003560800933561517</v>
+        <v>0.0003560800933561526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001248414768927995</v>
+        <v>0.001248414768928015</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910599604618969</v>
+        <v>0.02910599604619002</v>
       </c>
     </row>
     <row r="5">
@@ -677,34 +677,34 @@
         <v>0.1837119874489483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4893821169337039</v>
+        <v>0.4893821169337035</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04507804313086049</v>
+        <v>0.04507804313086052</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407289173658668e-05</v>
+        <v>7.407289173658673e-05</v>
       </c>
       <c r="I5" t="n">
         <v>0.0001451058906403937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004672522928425162</v>
+        <v>0.0004672522928425141</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003927127609719665</v>
+        <v>0.0003927127609719663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004022065929443335</v>
+        <v>0.000402206592944334</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003476445021532626</v>
+        <v>0.0003476445021532632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00119035840513544</v>
+        <v>0.001190358405135439</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599599272201</v>
+        <v>0.02910599599272246</v>
       </c>
     </row>
     <row r="6">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7032751978556692</v>
+        <v>0.7032751978556691</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1753471103477981</v>
+        <v>0.1753471103477979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4822268274729182</v>
+        <v>0.4822268274729181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01439878533781299</v>
+        <v>0.01439878533781298</v>
       </c>
       <c r="H6" t="n">
-        <v>3.508576433303402e-05</v>
+        <v>3.508576433303448e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.283676957931581e-05</v>
+        <v>8.283676957931602e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002789070773255336</v>
+        <v>0.0002789070773255332</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000353810863076296</v>
+        <v>0.0003538108630762968</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002681799771236139</v>
+        <v>0.0002681799771236148</v>
       </c>
       <c r="M6" t="n">
         <v>0.0003083368905920419</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008693218746920907</v>
+        <v>0.0008693218746920755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599548041792</v>
+        <v>0.02910599548041815</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6860183850138696</v>
+        <v>0.6860183850138699</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1715724663424561</v>
+        <v>0.1715724663424564</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4793177656445256</v>
+        <v>0.4793177656445257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004241855389366118</v>
+        <v>0.004241855389366121</v>
       </c>
       <c r="H7" t="n">
-        <v>1.692114242823003e-05</v>
+        <v>1.692114242822988e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.075382406745321e-05</v>
+        <v>6.075382406745312e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001969550889336479</v>
+        <v>0.0001969550889336476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003230823493690553</v>
+        <v>0.0003230823493690548</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002259508829036921</v>
+        <v>0.000225950882903642</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002911365785721281</v>
+        <v>0.0002911365785721284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006655024821091087</v>
+        <v>0.0006655024821091067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599528913849</v>
+        <v>0.02910599528913838</v>
       </c>
     </row>
     <row r="8">
@@ -824,37 +824,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6796210042921865</v>
+        <v>0.6796210042921864</v>
       </c>
       <c r="E8" t="n">
         <v>0.1697131509464237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4775594107603392</v>
+        <v>0.477559410760339</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001650156026784801</v>
+        <v>0.001650156026784814</v>
       </c>
       <c r="H8" t="n">
-        <v>1.101821568936294e-05</v>
+        <v>1.101821568936297e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>5.283561682207669e-05</v>
+        <v>5.283561682207666e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001681721465813297</v>
+        <v>0.0001681721465813424</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003093431046993888</v>
+        <v>0.0003093431046993885</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002060793747675172</v>
+        <v>0.0002060793747675171</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002822060859815676</v>
+        <v>0.0002822060859815677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005626367800593334</v>
+        <v>0.0005626367800593186</v>
       </c>
       <c r="O8" t="n">
         <v>0.02910599523403834</v>
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.747194363431356</v>
+        <v>0.7471943634313566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1826463454923022</v>
+        <v>0.1826463454923021</v>
       </c>
       <c r="F9" t="n">
         <v>0.4892430735297845</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0432070350092932</v>
+        <v>0.04320703500929315</v>
       </c>
       <c r="H9" t="n">
-        <v>5.718122567657989e-05</v>
+        <v>5.718122567657981e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001434980509519483</v>
+        <v>0.0001434980509519481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004534273424585213</v>
+        <v>0.000453427342458522</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003921960435794464</v>
+        <v>0.0003921960435794465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004000148671560215</v>
+        <v>0.0004000148671560226</v>
       </c>
       <c r="M9" t="n">
         <v>0.0003534661189507374</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001192129816140599</v>
+        <v>0.001192129816140601</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599593506236</v>
+        <v>0.02910599593506313</v>
       </c>
     </row>
     <row r="10">
@@ -926,37 +926,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.712925149195484</v>
+        <v>0.7129251491954843</v>
       </c>
       <c r="E10" t="n">
         <v>0.1771309742958767</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4848073313405104</v>
+        <v>0.4848073313405107</v>
       </c>
       <c r="G10" t="n">
-        <v>0.019511317691232</v>
+        <v>0.01951131769123194</v>
       </c>
       <c r="H10" t="n">
-        <v>3.562328169704739e-05</v>
+        <v>3.562328169704752e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001040832594284719</v>
+        <v>0.0001040832594284717</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003057392513972164</v>
+        <v>0.0003057392513972144</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003599073326292377</v>
+        <v>0.0003599073326292378</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003349422873555102</v>
+        <v>0.0003349422873555892</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003332622098989638</v>
+        <v>0.0003332622098989641</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008959727000278912</v>
+        <v>0.0008959727000278909</v>
       </c>
       <c r="O10" t="n">
         <v>0.02910599554543059</v>
@@ -977,40 +977,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6866490170534209</v>
+        <v>0.6866490170534206</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1726441914303112</v>
+        <v>0.1726441914303111</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4800661717903075</v>
+        <v>0.4800661717903071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002978861611404622</v>
+        <v>0.002978861611404609</v>
       </c>
       <c r="H11" t="n">
-        <v>3.160476681661418e-05</v>
+        <v>3.160476681661419e-05</v>
       </c>
       <c r="I11" t="n">
         <v>5.7166415459671e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001930842097990841</v>
+        <v>0.0001930842097990845</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003252648291629597</v>
+        <v>0.0003252648291629606</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002307966325901143</v>
+        <v>0.0002307966325899407</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002910371054924278</v>
+        <v>0.0002910371054924277</v>
       </c>
       <c r="N11" t="n">
         <v>0.0007248429705152061</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910599529156144</v>
+        <v>0.02910599529156188</v>
       </c>
     </row>
   </sheetData>
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4815491638970732</v>
+        <v>0.4815491638970726</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1866889045987777</v>
+        <v>0.1866889045987776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2087118254219067</v>
+        <v>0.2087118254219066</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05360369613219044</v>
+        <v>0.05360369613219043</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921175811433187e-05</v>
+        <v>7.921175811433154e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.0001714878572393352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005394736185933638</v>
+        <v>0.0005394736185933622</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004121356485860285</v>
+        <v>0.0004121356485860273</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000453619265089943</v>
+        <v>0.000453619265089941</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003668849361264691</v>
+        <v>0.0003668849361264688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001415921500504478</v>
+        <v>0.001415921500504445</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600315994438</v>
+        <v>0.0291060031599441</v>
       </c>
     </row>
     <row r="3">
@@ -1165,40 +1165,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4763260704378974</v>
+        <v>0.4763260704378976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853547660920927</v>
+        <v>0.1853547660920928</v>
       </c>
       <c r="F3" t="n">
         <v>0.2060453834348836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05252503758493637</v>
+        <v>0.05252503758493641</v>
       </c>
       <c r="H3" t="n">
-        <v>7.137165240197179e-05</v>
+        <v>7.13716524019717e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.000162708354477617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005168698152984767</v>
+        <v>0.0005168698152984818</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004066695497614141</v>
+        <v>0.0004066695497614152</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004338473151447467</v>
+        <v>0.0004338473151447451</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003617932932367358</v>
+        <v>0.0003617932932367356</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001341620180368657</v>
+        <v>0.001341620180368709</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600316529516</v>
+        <v>0.0291060031652951</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4675954887758158</v>
+        <v>0.4675954887758163</v>
       </c>
       <c r="E4" t="n">
-        <v>0.184507178013775</v>
+        <v>0.1845071780137751</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2007548832931866</v>
+        <v>0.2007548832931868</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007991238058413</v>
+        <v>0.05007991238058419</v>
       </c>
       <c r="H4" t="n">
-        <v>6.998006613657974e-05</v>
+        <v>6.998006613657981e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001558665476670602</v>
+        <v>0.0001558665476670605</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004949566457814372</v>
+        <v>0.0004949566457814393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003988781058089494</v>
+        <v>0.0003988781058089502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004233356256196214</v>
+        <v>0.0004233356256196216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003560800933561517</v>
+        <v>0.0003560800933561526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001248414768927995</v>
+        <v>0.001248414768928015</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600323497231</v>
+        <v>0.02910600323497242</v>
       </c>
     </row>
     <row r="5">
@@ -1276,31 +1276,31 @@
         <v>0.1902383354106287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04507804313086049</v>
+        <v>0.04507804313086052</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407289173658668e-05</v>
+        <v>7.407289173658673e-05</v>
       </c>
       <c r="I5" t="n">
         <v>0.0001451058906403937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004672522928425162</v>
+        <v>0.0004672522928425141</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003927127609719665</v>
+        <v>0.0003927127609719663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004022065929443335</v>
+        <v>0.000402206592944334</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003476445021532626</v>
+        <v>0.0003476445021532632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00119035840513544</v>
+        <v>0.001190358405135439</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600340274178</v>
+        <v>0.02910600340274166</v>
       </c>
     </row>
     <row r="6">
@@ -1321,37 +1321,37 @@
         <v>0.3464305993909066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1753471103477981</v>
+        <v>0.1753471103477979</v>
       </c>
       <c r="F6" t="n">
         <v>0.1253822201688447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01439878533781299</v>
+        <v>0.01439878533781298</v>
       </c>
       <c r="H6" t="n">
-        <v>3.508576433303402e-05</v>
+        <v>3.508576433303448e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.283676957931581e-05</v>
+        <v>8.283676957931602e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002789070773255336</v>
+        <v>0.0002789070773255332</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000353810863076296</v>
+        <v>0.0003538108630762968</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002681799771236139</v>
+        <v>0.0002681799771236148</v>
       </c>
       <c r="M6" t="n">
         <v>0.0003083368905920419</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008693218746920907</v>
+        <v>0.0008693218746920755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600431972887</v>
+        <v>0.02910600431972921</v>
       </c>
     </row>
     <row r="7">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3103311309501277</v>
+        <v>0.3103311309501284</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1715724663424561</v>
+        <v>0.1715724663424564</v>
       </c>
       <c r="F7" t="n">
         <v>0.1036305022747249</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004241855389366118</v>
+        <v>0.004241855389366121</v>
       </c>
       <c r="H7" t="n">
-        <v>1.692114242823003e-05</v>
+        <v>1.692114242822988e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.075382406745321e-05</v>
+        <v>6.075382406745312e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001969550889336479</v>
+        <v>0.0001969550889336476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003230823493690553</v>
+        <v>0.0003230823493690548</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002259508829036921</v>
+        <v>0.000225950882903642</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002911365785721281</v>
+        <v>0.0002911365785721284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006655024821091087</v>
+        <v>0.0006655024821091067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600459519724</v>
+        <v>0.02910600459519774</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2998914742556355</v>
+        <v>0.2998914742556354</v>
       </c>
       <c r="E8" t="n">
         <v>0.1697131509464237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09782987131759825</v>
+        <v>0.09782987131759821</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001650156026784801</v>
+        <v>0.001650156026784814</v>
       </c>
       <c r="H8" t="n">
-        <v>1.101821568936294e-05</v>
+        <v>1.101821568936297e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>5.283561682207669e-05</v>
+        <v>5.283561682207666e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001681721465813297</v>
+        <v>0.0001681721465813424</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003093431046993888</v>
+        <v>0.0003093431046993885</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002060793747675172</v>
+        <v>0.0002060793747675171</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002822060859815676</v>
+        <v>0.0002822060859815677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005626367800593334</v>
+        <v>0.0005626367800593186</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600464022822</v>
+        <v>0.02910600464022811</v>
       </c>
     </row>
     <row r="9">
@@ -1471,40 +1471,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.444013328378876</v>
+        <v>0.4440133283788757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1826463454923022</v>
+        <v>0.1826463454923021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1860620309672782</v>
+        <v>0.1860620309672783</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0432070350092932</v>
+        <v>0.04320703500929315</v>
       </c>
       <c r="H9" t="n">
-        <v>5.718122567657989e-05</v>
+        <v>5.718122567657981e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001434980509519483</v>
+        <v>0.0001434980509519481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004534273424585213</v>
+        <v>0.000453427342458522</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003921960435794464</v>
+        <v>0.0003921960435794465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004000148671560215</v>
+        <v>0.0004000148671560226</v>
       </c>
       <c r="M9" t="n">
         <v>0.0003534661189507374</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001192129816140599</v>
+        <v>0.001192129816140601</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600344508851</v>
+        <v>0.02910600344508829</v>
       </c>
     </row>
     <row r="10">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3643762429867549</v>
+        <v>0.3643762429867544</v>
       </c>
       <c r="E10" t="n">
         <v>0.1771309742958767</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1362584164979578</v>
+        <v>0.1362584164979575</v>
       </c>
       <c r="G10" t="n">
-        <v>0.019511317691232</v>
+        <v>0.01951131769123194</v>
       </c>
       <c r="H10" t="n">
-        <v>3.562328169704739e-05</v>
+        <v>3.562328169704752e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001040832594284719</v>
+        <v>0.0001040832594284717</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003057392513972164</v>
+        <v>0.0003057392513972144</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003599073326292377</v>
+        <v>0.0003599073326292378</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003349422873555102</v>
+        <v>0.0003349422873555892</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003332622098989638</v>
+        <v>0.0003332622098989641</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008959727000278912</v>
+        <v>0.0008959727000278909</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600417925413</v>
+        <v>0.0291060041792538</v>
       </c>
     </row>
     <row r="11">
@@ -1576,37 +1576,37 @@
         <v>0.3080237643164246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1726441914303112</v>
+        <v>0.1726441914303111</v>
       </c>
       <c r="F11" t="n">
-        <v>0.101440909674475</v>
+        <v>0.1014409096744749</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002978861611404622</v>
+        <v>0.002978861611404609</v>
       </c>
       <c r="H11" t="n">
-        <v>3.160476681661418e-05</v>
+        <v>3.160476681661419e-05</v>
       </c>
       <c r="I11" t="n">
         <v>5.7166415459671e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001930842097990841</v>
+        <v>0.0001930842097990845</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003252648291629597</v>
+        <v>0.0003252648291629606</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002307966325901143</v>
+        <v>0.0002307966325899407</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002910371054924278</v>
+        <v>0.0002910371054924277</v>
       </c>
       <c r="N11" t="n">
         <v>0.0007248429705152061</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600467039781</v>
+        <v>0.02910600467039803</v>
       </c>
     </row>
   </sheetData>
@@ -1765,70 +1765,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.7677407324745584</v>
+        <v>-0.7677407324745474</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.543640299864821</v>
+        <v>-1.543640299864819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3911462452855115</v>
+        <v>0.3911462452855103</v>
       </c>
       <c r="G2" t="n">
-        <v>2.984454214624142e-07</v>
+        <v>2.984454214624129e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.523095385633463e-06</v>
+        <v>8.523095385633446e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000126691527850805</v>
+        <v>0.0001266915278508042</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004275772565445746</v>
+        <v>0.0004275772565445741</v>
       </c>
       <c r="K2" t="n">
-        <v>2.503445707936076e-05</v>
+        <v>2.50344570793607e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.223884065407579e-05</v>
+        <v>1.223884065407576e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.592701516855549e-05</v>
+        <v>8.592701516855507e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008223914620516627</v>
+        <v>0.008223914620516599</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003838809415013748</v>
+        <v>0.003838809415013736</v>
       </c>
       <c r="P2" t="n">
-        <v>5.221776058905553e-05</v>
+        <v>5.221776058905534e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03969714077583929</v>
+        <v>0.03969714077580061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003140044090813462</v>
+        <v>0.0003140044090813449</v>
       </c>
       <c r="S2" t="n">
-        <v>6.389143387132725e-06</v>
+        <v>6.389143387132737e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2371683117825594</v>
+        <v>0.2371683117825592</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0437933469241377</v>
+        <v>0.04379334692413765</v>
       </c>
       <c r="V2" t="n">
-        <v>3.210913585271702e-06</v>
+        <v>3.210913585271694e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004023305245837803</v>
+        <v>0.0004023305245837792</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01491670501361361</v>
+        <v>0.01491670501361362</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03565060669689302</v>
+        <v>0.03565060669689291</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.8211149345135521</v>
+        <v>-0.8211149345135473</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.548552526799712</v>
+        <v>-1.548552526799714</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3582641838659265</v>
+        <v>0.3582641838659262</v>
       </c>
       <c r="G3" t="n">
-        <v>2.938249295551992e-07</v>
+        <v>2.938249295552e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.43386593214987e-06</v>
+        <v>8.433865932149897e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001213831860228299</v>
+        <v>0.00012138318602283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003916593801250676</v>
+        <v>0.0003916593801250655</v>
       </c>
       <c r="K3" t="n">
-        <v>2.397248798693175e-05</v>
+        <v>2.397248798693176e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.24875626649027e-06</v>
+        <v>9.24875626648807e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.349104392323624e-05</v>
+        <v>7.349104392331186e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006598496097763674</v>
+        <v>0.006598496097750385</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003604726379278821</v>
+        <v>0.003604726379278822</v>
       </c>
       <c r="P3" t="n">
-        <v>4.464421096513779e-05</v>
+        <v>4.464421096513778e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03602073614976462</v>
+        <v>0.03602073614977452</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003055084980190618</v>
+        <v>0.0003055084980191464</v>
       </c>
       <c r="S3" t="n">
-        <v>6.103346785554195e-06</v>
+        <v>6.103346785554142e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2313193694814722</v>
+        <v>0.2313193694814723</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04177654030320353</v>
+        <v>0.0417765403032035</v>
       </c>
       <c r="V3" t="n">
-        <v>3.148995043468603e-06</v>
+        <v>3.148995043468605e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003791611948882337</v>
+        <v>0.0003791611948882342</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01404529179711737</v>
+        <v>0.01404529179711745</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03444115632082732</v>
+        <v>0.03444115632082735</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.8743503409083733</v>
+        <v>-0.8743503409083634</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.55285987808766</v>
+        <v>-1.552859878087658</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3249226228969051</v>
+        <v>0.3249226228969054</v>
       </c>
       <c r="G4" t="n">
         <v>2.927454183056332e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.336945058143522e-06</v>
+        <v>8.33694505814349e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001162370346069253</v>
+        <v>0.0001162370346069258</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003943996471618472</v>
+        <v>0.000394399647161848</v>
       </c>
       <c r="K4" t="n">
-        <v>2.351893276114666e-05</v>
+        <v>2.351893276114675e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13651508887772e-05</v>
+        <v>1.13651508887753e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.296972782481737e-05</v>
+        <v>6.296972782481752e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007500770538859473</v>
+        <v>0.007500770538863322</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003258336336513774</v>
+        <v>0.003258336336513775</v>
       </c>
       <c r="P4" t="n">
-        <v>3.824850222583087e-05</v>
+        <v>3.824850222583101e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03472997528470097</v>
+        <v>0.03472997528472878</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002901491587058077</v>
+        <v>0.0002901491587058078</v>
       </c>
       <c r="S4" t="n">
-        <v>6.008275873013462e-06</v>
+        <v>6.008275873013482e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2184721326041906</v>
+        <v>0.2184721326041908</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0409840467546924</v>
+        <v>0.04098404675469247</v>
       </c>
       <c r="V4" t="n">
-        <v>3.124189143904344e-06</v>
+        <v>3.12418914390435e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003816985413991883</v>
+        <v>0.0003816985413991878</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01406623360557274</v>
+        <v>0.01406623360557272</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03323902780654614</v>
+        <v>0.03323902780654613</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,70 +2017,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9233123887485074</v>
+        <v>-0.9233123887485092</v>
       </c>
       <c r="E5" t="n">
         <v>-1.556738233570283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3096055495304237</v>
+        <v>0.3096055495304235</v>
       </c>
       <c r="G5" t="n">
-        <v>2.917016178548732e-07</v>
+        <v>2.917016178548731e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.119466845662251e-06</v>
+        <v>8.11946684566222e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001097308651095147</v>
+        <v>0.000109730865109514</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003912708848375732</v>
+        <v>0.0003912708848375731</v>
       </c>
       <c r="K5" t="n">
-        <v>1.977087103586779e-05</v>
+        <v>1.97708710358678e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.576058768969429e-05</v>
+        <v>1.57605876896943e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.598449067432356e-05</v>
+        <v>6.598449067432354e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009563910066843291</v>
+        <v>0.009563910066825788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002845526751928383</v>
+        <v>0.002845526751928385</v>
       </c>
       <c r="P5" t="n">
-        <v>4.016268801886043e-05</v>
+        <v>4.016268801886045e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03155612540451773</v>
+        <v>0.0315561254045422</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002679156197843731</v>
+        <v>0.0002679156197843732</v>
       </c>
       <c r="S5" t="n">
-        <v>5.876633588545484e-06</v>
+        <v>5.876633588545471e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1922095651264996</v>
+        <v>0.1922095651264997</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0402422510335499</v>
+        <v>0.04024225103354983</v>
       </c>
       <c r="V5" t="n">
-        <v>2.956139068150039e-06</v>
+        <v>2.95613906815004e-06</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003980019919055489</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01456717915598272</v>
+        <v>0.01456717915598267</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03150985462883565</v>
+        <v>0.03150985462883569</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2101,70 +2101,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.190623609213862</v>
+        <v>-1.190623609213609</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.57883027454593</v>
+        <v>-1.578830274545917</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2427189673863046</v>
+        <v>0.2427189673863042</v>
       </c>
       <c r="G6" t="n">
-        <v>2.678556754452366e-07</v>
+        <v>2.678556754452359e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.131051423049377e-06</v>
+        <v>7.131051423049384e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.549933590248241e-05</v>
+        <v>6.549933590248229e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.0002346749130229082</v>
       </c>
       <c r="K6" t="n">
-        <v>9.428134489366406e-06</v>
+        <v>9.428134489366389e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.397422519193615e-06</v>
+        <v>4.397422519193585e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.479553093783753e-05</v>
+        <v>2.479553093783973e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0035928822169248</v>
+        <v>0.003592882216917141</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001328710325171001</v>
+        <v>0.001328710325166195</v>
       </c>
       <c r="P6" t="n">
-        <v>1.601200290212821e-05</v>
+        <v>1.601200290212819e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01422948311503273</v>
+        <v>0.01422948311527578</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001272976197297749</v>
+        <v>0.0001272976197297748</v>
       </c>
       <c r="S6" t="n">
-        <v>4.204067264215092e-06</v>
+        <v>4.204067264215096e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06001336585039156</v>
+        <v>0.06001336585039163</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02870253846434272</v>
+        <v>0.02870253846434258</v>
       </c>
       <c r="V6" t="n">
-        <v>2.445636668598095e-06</v>
+        <v>2.445636668598097e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003240802142328528</v>
+        <v>0.0003240802142328521</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01176532636107038</v>
+        <v>0.01176532636107058</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02503512352431157</v>
+        <v>0.02503512352431177</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.311202438825403</v>
+        <v>-1.311202438825416</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.589900700460984</v>
+        <v>-1.589900700460991</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1909438827258206</v>
+        <v>0.19094388272582</v>
       </c>
       <c r="G7" t="n">
-        <v>2.579422061079822e-07</v>
+        <v>2.57942206107982e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.829407418963167e-06</v>
+        <v>6.829407418963171e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.625349651027759e-05</v>
+        <v>4.62534965102777e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001771595582368026</v>
+        <v>0.0001771595582368021</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.419317233416728e-06</v>
+        <v>-5.419317233416729e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.941933952661077e-06</v>
+        <v>3.941933952664982e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.388243265068812e-05</v>
+        <v>-1.38824326506882e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003115223133395872</v>
+        <v>0.003115223133395875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003842520169805562</v>
+        <v>0.000384252016980555</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.150375765521144e-06</v>
+        <v>-7.150375765521175e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007780705773054104</v>
+        <v>0.007780705773031575</v>
       </c>
       <c r="R7" t="n">
-        <v>6.19059917996424e-05</v>
+        <v>6.190599179961673e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.651876098830466e-06</v>
+        <v>3.651876098830449e-06</v>
       </c>
       <c r="T7" t="n">
         <v>0.01744030167551252</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02513214986569704</v>
+        <v>0.02513214986569703</v>
       </c>
       <c r="V7" t="n">
-        <v>1.809168029065868e-06</v>
+        <v>1.809168029065866e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003079313759237363</v>
+        <v>0.0003079313759237366</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01101356487231437</v>
+        <v>0.01101356487231434</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02230486080155496</v>
+        <v>0.02230486080155479</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.349040724976792</v>
+        <v>-1.349040724976763</v>
       </c>
       <c r="E8" t="n">
         <v>-1.59511408432486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1749294466173711</v>
+        <v>0.1749294466173705</v>
       </c>
       <c r="G8" t="n">
-        <v>2.521995069116719e-07</v>
+        <v>2.5219950691167e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.684710252674405e-06</v>
+        <v>6.684710252674426e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.949402798952801e-05</v>
+        <v>3.949402798952767e-05</v>
       </c>
       <c r="J8" t="n">
         <v>0.0001082783609247903</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.352667417555739e-06</v>
+        <v>-8.352667417555761e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>4.43256797727876e-06</v>
+        <v>4.432567977278747e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.070889147111441e-05</v>
+        <v>-1.070889147111446e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003247782951171712</v>
+        <v>0.003247782951171726</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004017150555136957</v>
+        <v>0.0004017150555136959</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.273446401444217e-06</v>
+        <v>-5.273446401444332e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003498316484212993</v>
+        <v>0.003498316484202467</v>
       </c>
       <c r="R8" t="n">
-        <v>6.318400981914616e-05</v>
+        <v>6.318400981914636e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.36219328583594e-06</v>
+        <v>3.362193285835949e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008093835738304586</v>
+        <v>0.008093835738304573</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02359435354804466</v>
+        <v>0.02359435354804461</v>
       </c>
       <c r="V8" t="n">
-        <v>1.699141589740833e-06</v>
+        <v>1.69914158974083e-06</v>
       </c>
       <c r="W8" t="n">
         <v>0.0003034607070947392</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01076821513162564</v>
+        <v>0.01076821513162563</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0210331493254667</v>
+        <v>0.02103314932546677</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2353,70 +2353,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9270229997468293</v>
+        <v>-0.9270229997468754</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.55672577641725</v>
+        <v>-1.556725776417249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.324029668805998</v>
+        <v>0.3240296688059983</v>
       </c>
       <c r="G9" t="n">
-        <v>2.876251985609634e-07</v>
+        <v>2.876251985609642e-07</v>
       </c>
       <c r="H9" t="n">
         <v>8.252529158133144e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001064841742126048</v>
+        <v>0.0001064841742126046</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003294856130470997</v>
+        <v>0.0003294856130470996</v>
       </c>
       <c r="K9" t="n">
-        <v>1.779779759276698e-05</v>
+        <v>1.779779759276699e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.167602754122511e-06</v>
+        <v>8.167602754122513e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.608340559183713e-05</v>
+        <v>4.608340559183711e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005842860599069089</v>
+        <v>0.005842860599028159</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003294203225700094</v>
+        <v>0.003294203225700093</v>
       </c>
       <c r="P9" t="n">
-        <v>2.817709754468168e-05</v>
+        <v>2.81770975446817e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02864267932227349</v>
+        <v>0.02864267932226826</v>
       </c>
       <c r="R9" t="n">
         <v>0.000271661883021187</v>
       </c>
       <c r="S9" t="n">
-        <v>5.736294117122313e-06</v>
+        <v>5.736294117122319e-06</v>
       </c>
       <c r="T9" t="n">
         <v>0.1822643546579034</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03887410218274581</v>
+        <v>0.03887410218274584</v>
       </c>
       <c r="V9" t="n">
-        <v>2.86803002865127e-06</v>
+        <v>2.868030028651272e-06</v>
       </c>
       <c r="W9" t="n">
         <v>0.0003644210123998408</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01343402698694938</v>
+        <v>0.01343402698694935</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03213141727304104</v>
+        <v>0.03213141727304096</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.154404236222954</v>
+        <v>-1.154404236222947</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.572614478790382</v>
+        <v>-1.572614478790379</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2436475073948443</v>
+        <v>0.243647507394845</v>
       </c>
       <c r="G10" t="n">
-        <v>2.748103029401186e-07</v>
+        <v>2.748103029401187e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.840360181233478e-06</v>
+        <v>7.840360181233483e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>7.180068041968625e-05</v>
+        <v>7.180068041968735e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002297984827315457</v>
+        <v>0.0002297984827315466</v>
       </c>
       <c r="K10" t="n">
         <v>8.655092556628991e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>6.073045656094262e-06</v>
+        <v>6.073045656095798e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.503304723287844e-06</v>
+        <v>-6.503304723221623e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004536335745657216</v>
+        <v>0.004536335745676274</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006942952701578876</v>
+        <v>0.0006942952701584735</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.152465245097759e-06</v>
+        <v>-3.152465245097748e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01764635388102887</v>
+        <v>0.01764635388103663</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001895478873878298</v>
+        <v>0.0001895478873876016</v>
       </c>
       <c r="S10" t="n">
-        <v>4.957298464688398e-06</v>
+        <v>4.957298464688405e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07784774543321747</v>
+        <v>0.07784774543321717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03277076939265745</v>
+        <v>0.03277076939265744</v>
       </c>
       <c r="V10" t="n">
         <v>2.452106812550828e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.000336235825787842</v>
+        <v>0.0003362358257878419</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01220563268114976</v>
+        <v>0.01220563268114982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02801358759864148</v>
+        <v>0.02801358759864141</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.295211669058574</v>
+        <v>-1.295211669058601</v>
       </c>
       <c r="E11" t="n">
         <v>-1.587288147203645</v>
@@ -2530,61 +2530,61 @@
         <v>0.204892102990357</v>
       </c>
       <c r="G11" t="n">
-        <v>2.601266596963649e-07</v>
+        <v>2.601266596963642e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.77656243928643e-06</v>
+        <v>6.776562439286423e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.534444818097775e-05</v>
+        <v>4.534444818097766e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001586873086612173</v>
+        <v>0.0001586873086612161</v>
       </c>
       <c r="K11" t="n">
-        <v>6.938852258171081e-06</v>
+        <v>6.938852258171009e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.542681204280625e-06</v>
+        <v>6.542681204280627e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.052326025607146e-05</v>
+        <v>-1.052326025607139e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004606745876187306</v>
+        <v>0.004606745876187312</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003373521385567689</v>
+        <v>0.0003373521385567686</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.852513101995415e-06</v>
+        <v>-4.852513101995552e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01090155629395893</v>
+        <v>0.01090155629395872</v>
       </c>
       <c r="R11" t="n">
-        <v>7.151385629781433e-05</v>
+        <v>7.151385629783058e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.729556646114069e-06</v>
+        <v>3.729556646114099e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01264450920801343</v>
+        <v>0.01264450920801339</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02362616739407781</v>
+        <v>0.02362616739407782</v>
       </c>
       <c r="V11" t="n">
-        <v>2.318558766892814e-06</v>
+        <v>2.318558766892811e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003216123663310025</v>
+        <v>0.0003216123663310024</v>
       </c>
       <c r="X11" t="n">
         <v>0.01171143252600476</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0227482312165396</v>
+        <v>0.02274823121653961</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.520830836609084</v>
+        <v>-0.5208308366090769</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.543640299864821</v>
+        <v>-1.543640299864819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6380561412452864</v>
+        <v>0.6380561412452856</v>
       </c>
       <c r="G2" t="n">
-        <v>2.984454214624142e-07</v>
+        <v>2.984454214624129e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.523095385633463e-06</v>
+        <v>8.523095385633446e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000126691527850805</v>
+        <v>0.0001266915278508042</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004275772565445746</v>
+        <v>0.0004275772565445741</v>
       </c>
       <c r="K2" t="n">
-        <v>2.503445707936076e-05</v>
+        <v>2.50344570793607e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.223884065407579e-05</v>
+        <v>1.223884065407576e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.592701516855549e-05</v>
+        <v>8.592701516855507e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008223914620516627</v>
+        <v>0.008223914620516599</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003838809415013748</v>
+        <v>0.003838809415013736</v>
       </c>
       <c r="P2" t="n">
-        <v>5.221776058905553e-05</v>
+        <v>5.221776058905534e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03969714077583929</v>
+        <v>0.03969714077580061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003140044090813462</v>
+        <v>0.0003140044090813449</v>
       </c>
       <c r="S2" t="n">
-        <v>6.389143387132725e-06</v>
+        <v>6.389143387132737e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2371683117825594</v>
+        <v>0.2371683117825592</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0437933469241377</v>
+        <v>0.04379334692413765</v>
       </c>
       <c r="V2" t="n">
-        <v>3.210913585271702e-06</v>
+        <v>3.210913585271694e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004023305245837803</v>
+        <v>0.0004023305245837792</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01491670501361361</v>
+        <v>0.01491670501361362</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03565060669689302</v>
+        <v>0.03565060669689291</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2830,70 +2830,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.6388404557494005</v>
+        <v>-0.6388404557494289</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.548552526799712</v>
+        <v>-1.548552526799714</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5405386626997364</v>
+        <v>0.5405386626997369</v>
       </c>
       <c r="G3" t="n">
-        <v>2.938249295551992e-07</v>
+        <v>2.938249295552e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.43386593214987e-06</v>
+        <v>8.433865932149897e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001213831860228299</v>
+        <v>0.00012138318602283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003916593801250676</v>
+        <v>0.0003916593801250655</v>
       </c>
       <c r="K3" t="n">
-        <v>2.397248798693175e-05</v>
+        <v>2.397248798693176e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.24875626649027e-06</v>
+        <v>9.24875626648807e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.349104392323624e-05</v>
+        <v>7.349104392331186e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006598496097763674</v>
+        <v>0.006598496097750385</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003604726379278821</v>
+        <v>0.003604726379278822</v>
       </c>
       <c r="P3" t="n">
-        <v>4.464421096513779e-05</v>
+        <v>4.464421096513778e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03602073614976462</v>
+        <v>0.03602073614977452</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003055084980190618</v>
+        <v>0.0003055084980191464</v>
       </c>
       <c r="S3" t="n">
-        <v>6.103346785554195e-06</v>
+        <v>6.103346785554142e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2313193694814722</v>
+        <v>0.2313193694814723</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04177654030320353</v>
+        <v>0.0417765403032035</v>
       </c>
       <c r="V3" t="n">
-        <v>3.148995043468603e-06</v>
+        <v>3.148995043468605e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003791611948882337</v>
+        <v>0.0003791611948882342</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01404529179711737</v>
+        <v>0.01404529179711745</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03444115632082732</v>
+        <v>0.03444115632082735</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7255036931646294</v>
+        <v>-0.7255036931646232</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.55285987808766</v>
+        <v>-1.552859878087658</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4737692706975233</v>
+        <v>0.4737692706975236</v>
       </c>
       <c r="G4" t="n">
         <v>2.927454183056332e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.336945058143522e-06</v>
+        <v>8.33694505814349e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001162370346069253</v>
+        <v>0.0001162370346069258</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003943996471618472</v>
+        <v>0.000394399647161848</v>
       </c>
       <c r="K4" t="n">
-        <v>2.351893276114666e-05</v>
+        <v>2.351893276114675e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13651508887772e-05</v>
+        <v>1.13651508887753e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.296972782481737e-05</v>
+        <v>6.296972782481752e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007500770538859473</v>
+        <v>0.007500770538863322</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003258336336513774</v>
+        <v>0.003258336336513775</v>
       </c>
       <c r="P4" t="n">
-        <v>3.824850222583087e-05</v>
+        <v>3.824850222583101e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03472997528470097</v>
+        <v>0.03472997528472878</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002901491587058077</v>
+        <v>0.0002901491587058078</v>
       </c>
       <c r="S4" t="n">
-        <v>6.008275873013462e-06</v>
+        <v>6.008275873013482e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2184721326041906</v>
+        <v>0.2184721326041908</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0409840467546924</v>
+        <v>0.04098404675469247</v>
       </c>
       <c r="V4" t="n">
-        <v>3.124189143904344e-06</v>
+        <v>3.12418914390435e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003816985413991883</v>
+        <v>0.0003816985413991878</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01406623360557274</v>
+        <v>0.01406623360557272</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03323902780654614</v>
+        <v>0.03323902780654613</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,70 +2998,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7970441906012862</v>
+        <v>-0.7970441906012755</v>
       </c>
       <c r="E5" t="n">
         <v>-1.556738233570283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4358737477258914</v>
+        <v>0.4358737477258912</v>
       </c>
       <c r="G5" t="n">
-        <v>2.917016178548732e-07</v>
+        <v>2.917016178548731e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.119466845662251e-06</v>
+        <v>8.11946684566222e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001097308651095147</v>
+        <v>0.000109730865109514</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003912708848375732</v>
+        <v>0.0003912708848375731</v>
       </c>
       <c r="K5" t="n">
-        <v>1.977087103586779e-05</v>
+        <v>1.97708710358678e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.576058768969429e-05</v>
+        <v>1.57605876896943e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.598449067432356e-05</v>
+        <v>6.598449067432354e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009563910066843291</v>
+        <v>0.009563910066825788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002845526751928383</v>
+        <v>0.002845526751928385</v>
       </c>
       <c r="P5" t="n">
-        <v>4.016268801886043e-05</v>
+        <v>4.016268801886045e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03155612540451773</v>
+        <v>0.0315561254045422</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002679156197843731</v>
+        <v>0.0002679156197843732</v>
       </c>
       <c r="S5" t="n">
-        <v>5.876633588545484e-06</v>
+        <v>5.876633588545471e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1922095651264996</v>
+        <v>0.1922095651264997</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0402422510335499</v>
+        <v>0.04024225103354983</v>
       </c>
       <c r="V5" t="n">
-        <v>2.956139068150039e-06</v>
+        <v>2.95613906815004e-06</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003980019919055489</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01456717915598272</v>
+        <v>0.01456717915598267</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03150985462883565</v>
+        <v>0.03150985462883569</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3082,70 +3082,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.083171446913911</v>
+        <v>-1.083171446913733</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.57883027454593</v>
+        <v>-1.578830274545917</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3501711297272689</v>
+        <v>0.3501711297272686</v>
       </c>
       <c r="G6" t="n">
-        <v>2.678556754452366e-07</v>
+        <v>2.678556754452359e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.131051423049377e-06</v>
+        <v>7.131051423049384e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.549933590248241e-05</v>
+        <v>6.549933590248229e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.0002346749130229082</v>
       </c>
       <c r="K6" t="n">
-        <v>9.428134489366406e-06</v>
+        <v>9.428134489366389e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.397422519193615e-06</v>
+        <v>4.397422519193585e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.479553093783753e-05</v>
+        <v>2.479553093783973e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0035928822169248</v>
+        <v>0.003592882216917141</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001328710325171001</v>
+        <v>0.001328710325166195</v>
       </c>
       <c r="P6" t="n">
-        <v>1.601200290212821e-05</v>
+        <v>1.601200290212819e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01422948311503273</v>
+        <v>0.01422948311527578</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001272976197297749</v>
+        <v>0.0001272976197297748</v>
       </c>
       <c r="S6" t="n">
-        <v>4.204067264215092e-06</v>
+        <v>4.204067264215096e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06001336585039156</v>
+        <v>0.06001336585039163</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02870253846434272</v>
+        <v>0.02870253846434258</v>
       </c>
       <c r="V6" t="n">
-        <v>2.445636668598095e-06</v>
+        <v>2.445636668598097e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003240802142328528</v>
+        <v>0.0003240802142328521</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01176532636107038</v>
+        <v>0.01176532636107058</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02503512352431157</v>
+        <v>0.02503512352431177</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.228558175150692</v>
+        <v>-1.228558175150788</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.589900700460984</v>
+        <v>-1.589900700460991</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2735881464320922</v>
+        <v>0.2735881464320915</v>
       </c>
       <c r="G7" t="n">
-        <v>2.579422061079822e-07</v>
+        <v>2.57942206107982e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.829407418963167e-06</v>
+        <v>6.829407418963171e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.625349651027759e-05</v>
+        <v>4.62534965102777e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001771595582368026</v>
+        <v>0.0001771595582368021</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.419317233416728e-06</v>
+        <v>-5.419317233416729e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.941933952661077e-06</v>
+        <v>3.941933952664982e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.388243265068812e-05</v>
+        <v>-1.38824326506882e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003115223133395872</v>
+        <v>0.003115223133395875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003842520169805562</v>
+        <v>0.000384252016980555</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.150375765521144e-06</v>
+        <v>-7.150375765521175e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007780705773054104</v>
+        <v>0.007780705773031575</v>
       </c>
       <c r="R7" t="n">
-        <v>6.19059917996424e-05</v>
+        <v>6.190599179961673e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.651876098830466e-06</v>
+        <v>3.651876098830449e-06</v>
       </c>
       <c r="T7" t="n">
         <v>0.01744030167551252</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02513214986569704</v>
+        <v>0.02513214986569703</v>
       </c>
       <c r="V7" t="n">
-        <v>1.809168029065868e-06</v>
+        <v>1.809168029065866e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003079313759237363</v>
+        <v>0.0003079313759237366</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01101356487231437</v>
+        <v>0.01101356487231434</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02230486080155496</v>
+        <v>0.02230486080155479</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.2772790489913</v>
+        <v>-1.27727904899128</v>
       </c>
       <c r="E8" t="n">
         <v>-1.59511408432486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2466911226302813</v>
+        <v>0.2466911226302814</v>
       </c>
       <c r="G8" t="n">
-        <v>2.521995069116719e-07</v>
+        <v>2.5219950691167e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.684710252674405e-06</v>
+        <v>6.684710252674426e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.949402798952801e-05</v>
+        <v>3.949402798952767e-05</v>
       </c>
       <c r="J8" t="n">
         <v>0.0001082783609247903</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.352667417555739e-06</v>
+        <v>-8.352667417555761e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>4.43256797727876e-06</v>
+        <v>4.432567977278747e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.070889147111441e-05</v>
+        <v>-1.070889147111446e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003247782951171712</v>
+        <v>0.003247782951171726</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004017150555136957</v>
+        <v>0.0004017150555136959</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.273446401444217e-06</v>
+        <v>-5.273446401444332e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003498316484212993</v>
+        <v>0.003498316484202467</v>
       </c>
       <c r="R8" t="n">
-        <v>6.318400981914616e-05</v>
+        <v>6.318400981914636e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.36219328583594e-06</v>
+        <v>3.362193285835949e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008093835738304586</v>
+        <v>0.008093835738304573</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02359435354804466</v>
+        <v>0.02359435354804461</v>
       </c>
       <c r="V8" t="n">
-        <v>1.699141589740833e-06</v>
+        <v>1.69914158974083e-06</v>
       </c>
       <c r="W8" t="n">
         <v>0.0003034607070947392</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01076821513162564</v>
+        <v>0.01076821513162563</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0210331493254667</v>
+        <v>0.02103314932546677</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3334,70 +3334,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7524293036588791</v>
+        <v>-0.752429303658901</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.55672577641725</v>
+        <v>-1.556725776417249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4986233649606518</v>
+        <v>0.498623364960652</v>
       </c>
       <c r="G9" t="n">
-        <v>2.876251985609634e-07</v>
+        <v>2.876251985609642e-07</v>
       </c>
       <c r="H9" t="n">
         <v>8.252529158133144e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001064841742126048</v>
+        <v>0.0001064841742126046</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003294856130470997</v>
+        <v>0.0003294856130470996</v>
       </c>
       <c r="K9" t="n">
-        <v>1.779779759276698e-05</v>
+        <v>1.779779759276699e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.167602754122511e-06</v>
+        <v>8.167602754122513e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.608340559183713e-05</v>
+        <v>4.608340559183711e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005842860599069089</v>
+        <v>0.005842860599028159</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003294203225700094</v>
+        <v>0.003294203225700093</v>
       </c>
       <c r="P9" t="n">
-        <v>2.817709754468168e-05</v>
+        <v>2.81770975446817e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02864267932227349</v>
+        <v>0.02864267932226826</v>
       </c>
       <c r="R9" t="n">
         <v>0.000271661883021187</v>
       </c>
       <c r="S9" t="n">
-        <v>5.736294117122313e-06</v>
+        <v>5.736294117122319e-06</v>
       </c>
       <c r="T9" t="n">
         <v>0.1822643546579034</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03887410218274581</v>
+        <v>0.03887410218274584</v>
       </c>
       <c r="V9" t="n">
-        <v>2.86803002865127e-06</v>
+        <v>2.868030028651272e-06</v>
       </c>
       <c r="W9" t="n">
         <v>0.0003644210123998408</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01343402698694938</v>
+        <v>0.01343402698694935</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03213141727304104</v>
+        <v>0.03213141727304096</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.025409965987968</v>
+        <v>-1.025409965987958</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.572614478790382</v>
+        <v>-1.572614478790379</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3726417776790973</v>
+        <v>0.3726417776790972</v>
       </c>
       <c r="G10" t="n">
-        <v>2.748103029401186e-07</v>
+        <v>2.748103029401187e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.840360181233478e-06</v>
+        <v>7.840360181233483e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>7.180068041968625e-05</v>
+        <v>7.180068041968735e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002297984827315457</v>
+        <v>0.0002297984827315466</v>
       </c>
       <c r="K10" t="n">
         <v>8.655092556628991e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>6.073045656094262e-06</v>
+        <v>6.073045656095798e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.503304723287844e-06</v>
+        <v>-6.503304723221623e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004536335745657216</v>
+        <v>0.004536335745676274</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006942952701578876</v>
+        <v>0.0006942952701584735</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.152465245097759e-06</v>
+        <v>-3.152465245097748e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01764635388102887</v>
+        <v>0.01764635388103663</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001895478873878298</v>
+        <v>0.0001895478873876016</v>
       </c>
       <c r="S10" t="n">
-        <v>4.957298464688398e-06</v>
+        <v>4.957298464688405e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07784774543321747</v>
+        <v>0.07784774543321717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03277076939265745</v>
+        <v>0.03277076939265744</v>
       </c>
       <c r="V10" t="n">
         <v>2.452106812550828e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.000336235825787842</v>
+        <v>0.0003362358257878419</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01220563268114976</v>
+        <v>0.01220563268114982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02801358759864148</v>
+        <v>0.02801358759864141</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.279349830733667</v>
+        <v>-1.279349830733657</v>
       </c>
       <c r="E11" t="n">
         <v>-1.587288147203645</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2207539413213405</v>
+        <v>0.2207539413213406</v>
       </c>
       <c r="G11" t="n">
-        <v>2.601266596963649e-07</v>
+        <v>2.601266596963642e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.77656243928643e-06</v>
+        <v>6.776562439286423e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.534444818097775e-05</v>
+        <v>4.534444818097766e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001586873086612173</v>
+        <v>0.0001586873086612161</v>
       </c>
       <c r="K11" t="n">
-        <v>6.938852258171081e-06</v>
+        <v>6.938852258171009e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.542681204280625e-06</v>
+        <v>6.542681204280627e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.052326025607146e-05</v>
+        <v>-1.052326025607139e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004606745876187306</v>
+        <v>0.004606745876187312</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003373521385567689</v>
+        <v>0.0003373521385567686</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.852513101995415e-06</v>
+        <v>-4.852513101995552e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01090155629395893</v>
+        <v>0.01090155629395872</v>
       </c>
       <c r="R11" t="n">
-        <v>7.151385629781433e-05</v>
+        <v>7.151385629783058e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.729556646114069e-06</v>
+        <v>3.729556646114099e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01264450920801343</v>
+        <v>0.01264450920801339</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02362616739407781</v>
+        <v>0.02362616739407782</v>
       </c>
       <c r="V11" t="n">
-        <v>2.318558766892814e-06</v>
+        <v>2.318558766892811e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003216123663310025</v>
+        <v>0.0003216123663310024</v>
       </c>
       <c r="X11" t="n">
         <v>0.01171143252600476</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0227482312165396</v>
+        <v>0.02274823121653961</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7660479779482339</v>
+        <v>0.7601163848026872</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1866889045987776</v>
+        <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4932106465203206</v>
+        <v>0.4920544887818212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05360369613219043</v>
+        <v>0.05008330144474995</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921175811433154e-05</v>
+        <v>7.949768237084973e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001714878572393352</v>
+        <v>0.0001613694320761283</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005394736185933622</v>
+        <v>0.000517286039759243</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004121356485860273</v>
+        <v>0.000409794518758543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000453619265089941</v>
+        <v>0.0004302669151791527</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003668849361264688</v>
+        <v>0.0003579362092265941</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001415921500504445</v>
+        <v>0.001368727882702079</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599611269149</v>
+        <v>0.02910599605561259</v>
       </c>
     </row>
     <row r="3">
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7621699919335371</v>
+        <v>0.7548790495114223</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853547660920928</v>
+        <v>0.1838291906059022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4918893120110955</v>
+        <v>0.4905789875069382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05252503758493641</v>
+        <v>0.04821494231345641</v>
       </c>
       <c r="H3" t="n">
-        <v>7.13716524019717e-05</v>
+        <v>7.022525470537622e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000162708354477617</v>
+        <v>0.0001518113141943921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005168698152984818</v>
+        <v>0.0004892489959522313</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004066695497614152</v>
+        <v>0.000399244423139644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004338473151447451</v>
+        <v>0.0004081963405496427</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003617932932367356</v>
+        <v>0.0003511156023621058</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001341620180368709</v>
+        <v>0.001280091146362088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599608472264</v>
+        <v>0.02910599600786001</v>
       </c>
     </row>
     <row r="4">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7578078941797345</v>
+        <v>0.7499402999043687</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1845071780137751</v>
+        <v>0.182638839815567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4909672958858874</v>
+        <v>0.4895073441437352</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007991238058419</v>
+        <v>0.04572335899261114</v>
       </c>
       <c r="H4" t="n">
-        <v>6.998006613657981e-05</v>
+        <v>6.771938650382351e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001558665476670605</v>
+        <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004949566457814393</v>
+        <v>0.0004620497936773626</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003988781058089502</v>
+        <v>0.0003863222939694058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004233356256196216</v>
+        <v>0.0003961016985246761</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003560800933561526</v>
+        <v>0.0003437323729270789</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001248414768928015</v>
+        <v>0.001164447078906748</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910599604619002</v>
+        <v>0.0291059959604576</v>
       </c>
     </row>
     <row r="5">
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7502974968426592</v>
+        <v>0.7434813395247808</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1837119874489483</v>
+        <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4893821169337035</v>
+        <v>0.4880694926684757</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04507804313086052</v>
+        <v>0.04161857570575983</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407289173658673e-05</v>
+        <v>7.20020714297296e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001451058906403937</v>
+        <v>0.0001351017835518199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004672522928425141</v>
+        <v>0.0004364619477144923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003927127609719663</v>
+        <v>0.000378926107684234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000402206592944334</v>
+        <v>0.0003784082242100166</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003476445021532632</v>
+        <v>0.0003359067485061816</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001190358405135439</v>
+        <v>0.001100141444635165</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599599272246</v>
+        <v>0.02910599591518026</v>
       </c>
     </row>
     <row r="6">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7032751978556691</v>
+        <v>0.6988591235739661</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1753471103477979</v>
+        <v>0.1734341181339289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4822268274729181</v>
+        <v>0.4810703906623334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01439878533781298</v>
+        <v>0.01323200409367944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.508576433303448e-05</v>
+        <v>3.157387977904127e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.283676957931602e-05</v>
+        <v>7.796561525975038e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002789070773255332</v>
+        <v>0.0002552564668313758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003538108630762968</v>
+        <v>0.0003306029768954351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002681799771236148</v>
+        <v>0.0002533766492009103</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003083368905920419</v>
+        <v>0.00029851366603648</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008693218746920755</v>
+        <v>0.0007693260029412952</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599548041815</v>
+        <v>0.02910599542708003</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6860183850138699</v>
+        <v>0.6820804847150554</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1715724663424564</v>
+        <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4793177656445257</v>
+        <v>0.4780951759294803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004241855389366121</v>
+        <v>0.004005592633530719</v>
       </c>
       <c r="H7" t="n">
-        <v>1.692114242822988e-05</v>
+        <v>1.236515770175312e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.075382406745312e-05</v>
+        <v>5.760624072710079e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001969550889336476</v>
+        <v>0.0001727953620730635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003230823493690548</v>
+        <v>0.0002977309488706833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000225950882903642</v>
+        <v>0.0002149280445553775</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002911365785721284</v>
+        <v>0.0002818988823972426</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006655024821091067</v>
+        <v>0.0005395976008691114</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599528913838</v>
+        <v>0.02910599523675939</v>
       </c>
     </row>
     <row r="8">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6796210042921864</v>
+        <v>0.6763900264371993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1697131509464237</v>
+        <v>0.1677644037114065</v>
       </c>
       <c r="F8" t="n">
-        <v>0.477559410760339</v>
+        <v>0.476583194125612</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001650156026784814</v>
+        <v>0.001516222820624146</v>
       </c>
       <c r="H8" t="n">
-        <v>1.101821568936297e-05</v>
+        <v>7.16512490384524e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.283561682207666e-05</v>
+        <v>5.043924548616532e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001681721465813424</v>
+        <v>0.0001481078092677816</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003093431046993885</v>
+        <v>0.0002870625570381503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002060793747675171</v>
+        <v>0.0001977439027298401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002822060859815677</v>
+        <v>0.0002749288836533894</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005626367800593186</v>
+        <v>0.0004547630681316607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599523403834</v>
+        <v>0.02910599518834567</v>
       </c>
     </row>
     <row r="9">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7471943634313566</v>
+        <v>0.7396161025400686</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1826463454923021</v>
+        <v>0.1807834979870835</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4892430735297845</v>
+        <v>0.4877996382630265</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04320703500929315</v>
+        <v>0.03912270071841051</v>
       </c>
       <c r="H9" t="n">
-        <v>5.718122567657981e-05</v>
+        <v>5.50138090354986e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001434980509519481</v>
+        <v>0.0001323452292307473</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000453427342458522</v>
+        <v>0.0004215950839633038</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003921960435794465</v>
+        <v>0.0003753592200896617</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004000148671560226</v>
+        <v>0.0003729347603893188</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003534661189507374</v>
+        <v>0.0003410339496637569</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001192129816140601</v>
+        <v>0.001105987666444341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599593506313</v>
+        <v>0.02910599585273144</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7129251491954843</v>
+        <v>0.7057775706302638</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1771309742958767</v>
+        <v>0.1746507049116373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4848073313405107</v>
+        <v>0.4831757397813212</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01951131769123194</v>
+        <v>0.01671526278688339</v>
       </c>
       <c r="H10" t="n">
-        <v>3.562328169704752e-05</v>
+        <v>3.146291041691867e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001040832594284717</v>
+        <v>9.407396674874718e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003057392513972144</v>
+        <v>0.0002697707407615794</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003599073326292378</v>
+        <v>0.0003358907712656632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003349422873555892</v>
+        <v>0.0003082578701390418</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003332622098989641</v>
+        <v>0.0003188749954166414</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008959727000278909</v>
+        <v>0.000771536432873719</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599554543059</v>
+        <v>0.02910599546279968</v>
       </c>
     </row>
     <row r="11">
@@ -977,40 +977,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6866490170534206</v>
+        <v>0.6834152438511434</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1726441914303111</v>
+        <v>0.1705839027608459</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4800661717903071</v>
+        <v>0.4791557473132457</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002978861611404609</v>
+        <v>0.002880084518684514</v>
       </c>
       <c r="H11" t="n">
-        <v>3.160476681661419e-05</v>
+        <v>2.810574286629256e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7166415459671e-05</v>
+        <v>5.853933714735999e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001930842097990845</v>
+        <v>0.0001825465042988459</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003252648291629606</v>
+        <v>0.0003112785164106755</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002307966325899407</v>
+        <v>0.0002227612681613601</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002910371054924277</v>
+        <v>0.0002836507017147812</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0007248429705152061</v>
+        <v>0.0006026319471648411</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910599529156188</v>
+        <v>0.0291059952406032</v>
       </c>
     </row>
   </sheetData>
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4815491638970726</v>
+        <v>0.4692672477434643</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1866889045987776</v>
+        <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2087118254219066</v>
+        <v>0.2012053445180427</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05360369613219043</v>
+        <v>0.05008330144474995</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921175811433154e-05</v>
+        <v>7.949768237084973e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001714878572393352</v>
+        <v>0.0001613694320761283</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005394736185933622</v>
+        <v>0.000517286039759243</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004121356485860273</v>
+        <v>0.000409794518758543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000453619265089941</v>
+        <v>0.0004302669151791527</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003668849361264688</v>
+        <v>0.0003579362092265941</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001415921500504445</v>
+        <v>0.001368727882702079</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0291060031599441</v>
+        <v>0.02910600326016843</v>
       </c>
     </row>
     <row r="3">
@@ -1165,40 +1165,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4763260704378976</v>
+        <v>0.4611276245001504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853547660920928</v>
+        <v>0.1838291906059022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2060453834348836</v>
+        <v>0.1968275552192192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05252503758493641</v>
+        <v>0.04821494231345641</v>
       </c>
       <c r="H3" t="n">
-        <v>7.13716524019717e-05</v>
+        <v>7.022525470537622e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000162708354477617</v>
+        <v>0.0001518113141943921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005168698152984818</v>
+        <v>0.0004892489959522313</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004066695497614152</v>
+        <v>0.000399244423139644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004338473151447451</v>
+        <v>0.0004081963405496427</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003617932932367356</v>
+        <v>0.0003511156023621058</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001341620180368709</v>
+        <v>0.001280091146362088</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0291060031652951</v>
+        <v>0.02910600328430707</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4675954887758163</v>
+        <v>0.4517748338148098</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1845071780137751</v>
+        <v>0.182638839815567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2007548832931868</v>
+        <v>0.191341870668391</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05007991238058419</v>
+        <v>0.04572335899261114</v>
       </c>
       <c r="H4" t="n">
-        <v>6.998006613657981e-05</v>
+        <v>6.771938650382351e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001558665476670605</v>
+        <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004949566457814393</v>
+        <v>0.0004620497936773626</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003988781058089502</v>
+        <v>0.0003863222939694058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004233356256196216</v>
+        <v>0.0003961016985246761</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003560800933561526</v>
+        <v>0.0003437323729270789</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001248414768928015</v>
+        <v>0.001164447078906748</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600323497242</v>
+        <v>0.02910600334624275</v>
       </c>
     </row>
     <row r="5">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4511537227296037</v>
+        <v>0.4380690907253919</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1837119874489483</v>
+        <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1902383354106287</v>
+        <v>0.1826572363037926</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04507804313086052</v>
+        <v>0.04161857570575983</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407289173658673e-05</v>
+        <v>7.20020714297296e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001451058906403937</v>
+        <v>0.0001351017835518199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004672522928425141</v>
+        <v>0.0004364619477144923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003927127609719663</v>
+        <v>0.000378926107684234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000402206592944334</v>
+        <v>0.0003784082242100166</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003476445021532632</v>
+        <v>0.0003359067485061816</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001190358405135439</v>
+        <v>0.001100141444635165</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600340274166</v>
+        <v>0.02910600348047454</v>
       </c>
     </row>
     <row r="6">
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3464305993909066</v>
+        <v>0.3402135485309888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1753471103477979</v>
+        <v>0.1734341181339289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1253822201688447</v>
+        <v>0.1224248067354334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01439878533781298</v>
+        <v>0.01323200409367944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.508576433303448e-05</v>
+        <v>3.157387977904127e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.283676957931602e-05</v>
+        <v>7.796561525975038e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002789070773255332</v>
+        <v>0.0002552564668313758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003538108630762968</v>
+        <v>0.0003306029768954351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002681799771236148</v>
+        <v>0.0002533766492009103</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003083368905920419</v>
+        <v>0.00029851366603648</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008693218746920755</v>
+        <v>0.0007693260029412952</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600431972921</v>
+        <v>0.02910600431100285</v>
       </c>
     </row>
     <row r="7">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3103311309501284</v>
+        <v>0.3064215714757724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1715724663424564</v>
+        <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1036305022747249</v>
+        <v>0.102436253384841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004241855389366121</v>
+        <v>0.004005592633530719</v>
       </c>
       <c r="H7" t="n">
-        <v>1.692114242822988e-05</v>
+        <v>1.236515770175312e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.075382406745312e-05</v>
+        <v>5.760624072710079e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001969550889336476</v>
+        <v>0.0001727953620730635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003230823493690548</v>
+        <v>0.0002977309488706833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000225950882903642</v>
+        <v>0.0002149280445553775</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002911365785721284</v>
+        <v>0.0002818988823972426</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006655024821091067</v>
+        <v>0.0005395976008691114</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600459519774</v>
+        <v>0.02910600454211554</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2998914742556354</v>
+        <v>0.2967471889104039</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1697131509464237</v>
+        <v>0.1677644037114065</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09782987131759821</v>
+        <v>0.09694034719477437</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001650156026784814</v>
+        <v>0.001516222820624146</v>
       </c>
       <c r="H8" t="n">
-        <v>1.101821568936297e-05</v>
+        <v>7.16512490384524e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.283561682207666e-05</v>
+        <v>5.043924548616532e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001681721465813424</v>
+        <v>0.0001481078092677816</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003093431046993885</v>
+        <v>0.0002870625570381503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002060793747675171</v>
+        <v>0.0001977439027298401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002822060859815677</v>
+        <v>0.0002749288836533894</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005626367800593186</v>
+        <v>0.0004547630681316607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600464022811</v>
+        <v>0.02910600459238816</v>
       </c>
     </row>
     <row r="9">
@@ -1471,40 +1471,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4440133283788757</v>
+        <v>0.4290321283374212</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1826463454923021</v>
+        <v>0.1807834979870835</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1860620309672783</v>
+        <v>0.1772156563669754</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04320703500929315</v>
+        <v>0.03912270071841051</v>
       </c>
       <c r="H9" t="n">
-        <v>5.718122567657981e-05</v>
+        <v>5.50138090354986e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001434980509519481</v>
+        <v>0.0001323452292307473</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000453427342458522</v>
+        <v>0.0004215950839633038</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003921960435794465</v>
+        <v>0.0003753592200896617</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004000148671560226</v>
+        <v>0.0003729347603893188</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003534661189507374</v>
+        <v>0.0003410339496637569</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001192129816140601</v>
+        <v>0.001105987666444341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600344508829</v>
+        <v>0.02910600354613513</v>
       </c>
     </row>
     <row r="10">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3643762429867544</v>
+        <v>0.3524360103104353</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1771309742958767</v>
+        <v>0.1746507049116373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1362584164979575</v>
+        <v>0.1298341707089521</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01951131769123194</v>
+        <v>0.01671526278688339</v>
       </c>
       <c r="H10" t="n">
-        <v>3.562328169704752e-05</v>
+        <v>3.146291041691867e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001040832594284717</v>
+        <v>9.407396674874718e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003057392513972144</v>
+        <v>0.0002697707407615794</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003599073326292378</v>
+        <v>0.0003358907712656632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003349422873555892</v>
+        <v>0.0003082578701390418</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003332622098989641</v>
+        <v>0.0003188749954166414</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008959727000278909</v>
+        <v>0.000771536432873719</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0291060041792538</v>
+        <v>0.0291060042153401</v>
       </c>
     </row>
     <row r="11">
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3080237643164246</v>
+        <v>0.3048559864273822</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1726441914303111</v>
+        <v>0.1705839027608459</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1014409096744749</v>
+        <v>0.1005964805122836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002978861611404609</v>
+        <v>0.002880084518684514</v>
       </c>
       <c r="H11" t="n">
-        <v>3.160476681661419e-05</v>
+        <v>2.810574286629256e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7166415459671e-05</v>
+        <v>5.853933714735999e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001930842097990845</v>
+        <v>0.0001825465042988459</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003252648291629606</v>
+        <v>0.0003112785164106755</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002307966325899407</v>
+        <v>0.0002227612681613601</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002910371054924277</v>
+        <v>0.0002836507017147812</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0007248429705152061</v>
+        <v>0.0006026319471648411</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600467039803</v>
+        <v>0.02910600461780399</v>
       </c>
     </row>
   </sheetData>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1765,70 +1765,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.7677407324745474</v>
+        <v>-0.8495586183774809</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.543640299864819</v>
+        <v>-1.547784669004612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3911462452855103</v>
+        <v>0.3334126777168157</v>
       </c>
       <c r="G2" t="n">
-        <v>2.984454214624129e-07</v>
+        <v>2.967052734860615e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.523095385633446e-06</v>
+        <v>8.29777497371651e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001266915278508042</v>
+        <v>0.00012148093336588</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004275772565445741</v>
+        <v>0.0004136876998668455</v>
       </c>
       <c r="K2" t="n">
-        <v>2.50344570793607e-05</v>
+        <v>2.36171297709628e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.223884065407576e-05</v>
+        <v>1.265140367188762e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.592701516855507e-05</v>
+        <v>8.650721919925382e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008223914620516599</v>
+        <v>0.008394229475622506</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003838809415013736</v>
+        <v>0.003617560147030653</v>
       </c>
       <c r="P2" t="n">
-        <v>5.221776058905534e-05</v>
+        <v>5.276176111896948e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03969714077580061</v>
+        <v>0.03818848892144527</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003140044090813449</v>
+        <v>0.0003320302303811611</v>
       </c>
       <c r="S2" t="n">
-        <v>6.389143387132737e-06</v>
+        <v>6.136213295679914e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2371683117825592</v>
+        <v>0.2219221647279446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04379334692413765</v>
+        <v>0.04219095408895414</v>
       </c>
       <c r="V2" t="n">
-        <v>3.210913585271694e-06</v>
+        <v>3.133795135691772e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004023305245837792</v>
+        <v>0.0004002502981944428</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01491670501361362</v>
+        <v>0.0147820899870638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03565060669689291</v>
+        <v>0.03425699165471949</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.8211149345135473</v>
+        <v>-0.9085458508562668</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.548552526799714</v>
+        <v>-1.553175046228752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3582641838659262</v>
+        <v>0.2990643430450833</v>
       </c>
       <c r="G3" t="n">
-        <v>2.938249295552e-07</v>
+        <v>2.910982836229393e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.433865932149897e-06</v>
+        <v>8.186346744262235e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00012138318602283</v>
+        <v>0.0001148966337932856</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003916593801250655</v>
+        <v>0.0003800529191866535</v>
       </c>
       <c r="K3" t="n">
-        <v>2.397248798693176e-05</v>
+        <v>2.259359825624103e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.24875626648807e-06</v>
+        <v>9.43119966464731e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.349104392331186e-05</v>
+        <v>7.496199314546062e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006598496097750385</v>
+        <v>0.006687890701502687</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003604726379278822</v>
+        <v>0.003372992321914142</v>
       </c>
       <c r="P3" t="n">
-        <v>4.464421096513778e-05</v>
+        <v>4.579048438156887e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03602073614977452</v>
+        <v>0.03459804462280838</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003055084980191464</v>
+        <v>0.0003212237757518625</v>
       </c>
       <c r="S3" t="n">
-        <v>6.103346785554142e-06</v>
+        <v>5.799016651922711e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2313193694814723</v>
+        <v>0.2128507111936727</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0417765403032035</v>
+        <v>0.03988270036831714</v>
       </c>
       <c r="V3" t="n">
-        <v>3.148995043468605e-06</v>
+        <v>3.053801267327755e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003791611948882342</v>
+        <v>0.0003750554295336958</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01404529179711745</v>
+        <v>0.01383729935453026</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03444115632082735</v>
+        <v>0.03297383526331501</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.8743503409083634</v>
+        <v>-0.9582979757847239</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.552859878087658</v>
+        <v>-1.557577317309589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3249226228969054</v>
+        <v>0.2696976414916735</v>
       </c>
       <c r="G4" t="n">
-        <v>2.927454183056332e-07</v>
+        <v>2.88495663422383e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.33694505814349e-06</v>
+        <v>8.073491503656936e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001162370346069258</v>
+        <v>0.0001085090953228953</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000394399647161848</v>
+        <v>0.0003790084812489929</v>
       </c>
       <c r="K4" t="n">
-        <v>2.351893276114675e-05</v>
+        <v>2.206349487019849e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13651508887753e-05</v>
+        <v>1.152786547445038e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.296972782481752e-05</v>
+        <v>6.340097150061036e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007500770538863322</v>
+        <v>0.007584124395116987</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003258336336513775</v>
+        <v>0.00302688351811925</v>
       </c>
       <c r="P4" t="n">
-        <v>3.824850222583101e-05</v>
+        <v>3.876270632857582e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03472997528472878</v>
+        <v>0.03307471650933609</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002901491587058078</v>
+        <v>0.0003016517052066571</v>
       </c>
       <c r="S4" t="n">
-        <v>6.008275873013482e-06</v>
+        <v>5.655265380564695e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2184721326041908</v>
+        <v>0.2000520167655542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04098404675469247</v>
+        <v>0.03893406919391242</v>
       </c>
       <c r="V4" t="n">
-        <v>3.12418914390435e-06</v>
+        <v>3.01915409020705e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003816985413991878</v>
+        <v>0.000377037710459298</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01406623360557272</v>
+        <v>0.01385317096912715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03323902780654613</v>
+        <v>0.03173767865041889</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2017,70 +2017,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9233123887485092</v>
+        <v>-0.9923784544815986</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.556738233570283</v>
+        <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3096055495304235</v>
+        <v>0.2636515802036559</v>
       </c>
       <c r="G5" t="n">
-        <v>2.917016178548731e-07</v>
+        <v>2.883344926157958e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.11946684566222e-06</v>
+        <v>7.88415612494884e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000109730865109514</v>
+        <v>0.0001024999723783849</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003912708848375731</v>
+        <v>0.000376363985234908</v>
       </c>
       <c r="K5" t="n">
-        <v>1.97708710358678e-05</v>
+        <v>1.855541770166522e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57605876896943e-05</v>
+        <v>1.614399578552711e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.598449067432354e-05</v>
+        <v>6.671436404062432e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009563910066825788</v>
+        <v>0.00976047937667022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002845526751928385</v>
+        <v>0.002647843563617878</v>
       </c>
       <c r="P5" t="n">
-        <v>4.016268801886045e-05</v>
+        <v>4.081677275278294e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0315561254045422</v>
+        <v>0.02999212139064207</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002679156197843732</v>
+        <v>0.0002773755225273111</v>
       </c>
       <c r="S5" t="n">
-        <v>5.876633588545471e-06</v>
+        <v>5.548797294451969e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1922095651264997</v>
+        <v>0.1780728838070509</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04024225103354983</v>
+        <v>0.03845948738098717</v>
       </c>
       <c r="V5" t="n">
-        <v>2.95613906815004e-06</v>
+        <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003980019919055489</v>
+        <v>0.0003948150479346347</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01456717915598267</v>
+        <v>0.01442301014128574</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03150985462883569</v>
+        <v>0.03021285433597517</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2101,70 +2101,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.190623609213609</v>
+        <v>-1.232919685067869</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.578830274545917</v>
+        <v>-1.583529197938965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2427189673863042</v>
+        <v>0.2137819860167696</v>
       </c>
       <c r="G6" t="n">
-        <v>2.678556754452359e-07</v>
+        <v>2.629743532180668e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.131051423049384e-06</v>
+        <v>7.00744658362135e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.549933590248229e-05</v>
+        <v>5.994515887725199e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002346749130229082</v>
+        <v>0.0002218360582685596</v>
       </c>
       <c r="K6" t="n">
-        <v>9.428134489366389e-06</v>
+        <v>8.313474661720802e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.397422519193585e-06</v>
+        <v>4.011007074466353e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.479553093783973e-05</v>
+        <v>2.408844445253663e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003592882216917141</v>
+        <v>0.003413721912265724</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001328710325166195</v>
+        <v>0.001235825335481854</v>
       </c>
       <c r="P6" t="n">
-        <v>1.601200290212819e-05</v>
+        <v>1.563588664813284e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01422948311527578</v>
+        <v>0.01333701183812303</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001272976197297748</v>
+        <v>0.0001282976709059454</v>
       </c>
       <c r="S6" t="n">
-        <v>4.204067264215096e-06</v>
+        <v>3.911559314590972e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06001336585039163</v>
+        <v>0.05547084700405661</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02870253846434258</v>
+        <v>0.02718795563138739</v>
       </c>
       <c r="V6" t="n">
-        <v>2.445636668598097e-06</v>
+        <v>2.350073527008297e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003240802142328521</v>
+        <v>0.0003134989871089374</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01176532636107058</v>
+        <v>0.01138229085736368</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02503512352431177</v>
+        <v>0.02401068144548199</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.311202438825416</v>
+        <v>-1.339682788373142</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.589900700460991</v>
+        <v>-1.594335350441187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.19094388272582</v>
+        <v>0.1716363794886081</v>
       </c>
       <c r="G7" t="n">
-        <v>2.57942206107982e-07</v>
+        <v>2.519333067941321e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.829407418963171e-06</v>
+        <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.62534965102777e-05</v>
+        <v>4.057975714113774e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001771595582368021</v>
+        <v>0.0001634258239776595</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.419317233416729e-06</v>
+        <v>-6.666578390180699e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.941933952664982e-06</v>
+        <v>3.408213536697682e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.38824326506882e-05</v>
+        <v>-1.576179324597284e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003115223133395875</v>
+        <v>0.002852673887755092</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000384252016980555</v>
+        <v>0.0003511833579318713</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.150375765521175e-06</v>
+        <v>-8.306313779496389e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007780705773031575</v>
+        <v>0.006949757463137796</v>
       </c>
       <c r="R7" t="n">
-        <v>6.190599179961673e-05</v>
+        <v>5.894403635046219e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.651876098830449e-06</v>
+        <v>3.377463070821941e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01744030167551252</v>
+        <v>0.01650860249098277</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02513214986569703</v>
+        <v>0.0237718999516727</v>
       </c>
       <c r="V7" t="n">
-        <v>1.809168029065866e-06</v>
+        <v>1.710369379189882e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003079313759237366</v>
+        <v>0.0002970973080769404</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01101356487231434</v>
+        <v>0.01060272397536547</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02230486080155479</v>
+        <v>0.02143450870345178</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.349040724976763</v>
+        <v>-1.371171399275056</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.59511408432486</v>
+        <v>-1.598715785791028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1749294466173705</v>
+        <v>0.1603862493917946</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5219950691167e-07</v>
+        <v>2.483967374914811e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.684710252674426e-06</v>
+        <v>6.617095439383984e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.949402798952767e-05</v>
+        <v>3.478206161720463e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001082783609247903</v>
+        <v>9.33764537050936e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.352667417555761e-06</v>
+        <v>-9.748427478810463e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>4.432567977278747e-06</v>
+        <v>3.874226954002219e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.070889147111446e-05</v>
+        <v>-1.27453122669307e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003247782951171726</v>
+        <v>0.002941585529239589</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004017150555136959</v>
+        <v>0.0003614663475157456</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.273446401444332e-06</v>
+        <v>-6.613356735135387e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003498316484202467</v>
+        <v>0.002643969675912246</v>
       </c>
       <c r="R8" t="n">
-        <v>6.318400981914636e-05</v>
+        <v>6.007275999553564e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.362193285835949e-06</v>
+        <v>3.142631698581945e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008093835738304573</v>
+        <v>0.007516435846575896</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02359435354804461</v>
+        <v>0.02247190753168225</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69914158974083e-06</v>
+        <v>1.611739468424993e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0003034607070947392</v>
+        <v>0.0002936029220226869</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01076821513162563</v>
+        <v>0.01042652077510718</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02103314932546677</v>
+        <v>0.02032799867849813</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2353,70 +2353,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9270229997468754</v>
+        <v>-1.006670578541267</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.556725776417249</v>
+        <v>-1.561927546685941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3240296688059983</v>
+        <v>0.2721354476889458</v>
       </c>
       <c r="G9" t="n">
-        <v>2.876251985609642e-07</v>
+        <v>2.832970733688222e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.252529158133144e-06</v>
+        <v>7.995921861823704e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001064841742126046</v>
+        <v>9.900859556574505e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003294856130470996</v>
+        <v>0.0003133471461989699</v>
       </c>
       <c r="K9" t="n">
-        <v>1.779779759276699e-05</v>
+        <v>1.614932724148671e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.167602754122513e-06</v>
+        <v>8.136039710518895e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.608340559183711e-05</v>
+        <v>4.561153676457521e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005842860599028159</v>
+        <v>0.005797721084024394</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003294203225700093</v>
+        <v>0.003056558056256892</v>
       </c>
       <c r="P9" t="n">
-        <v>2.81770975446817e-05</v>
+        <v>2.809672123789917e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02864267932226826</v>
+        <v>0.02690089148043396</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000271661883021187</v>
+        <v>0.0002837415493334886</v>
       </c>
       <c r="S9" t="n">
-        <v>5.736294117122319e-06</v>
+        <v>5.378735027035154e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1822643546579034</v>
+        <v>0.165665832607281</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03887410218274584</v>
+        <v>0.03679014917743906</v>
       </c>
       <c r="V9" t="n">
-        <v>2.868030028651272e-06</v>
+        <v>2.754907142699131e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003644210123998408</v>
+        <v>0.0003578503953903428</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01343402698694935</v>
+        <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03213141727304096</v>
+        <v>0.0305957347075486</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.154404236222947</v>
+        <v>-1.209163453972461</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.572614478790379</v>
+        <v>-1.578132706625494</v>
       </c>
       <c r="F10" t="n">
-        <v>0.243647507394845</v>
+        <v>0.2113874502663626</v>
       </c>
       <c r="G10" t="n">
-        <v>2.748103029401187e-07</v>
+        <v>2.677170814798685e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.840360181233483e-06</v>
+        <v>7.589085260944301e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>7.180068041968735e-05</v>
+        <v>6.335373248768603e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002297984827315466</v>
+        <v>0.0002098588280031235</v>
       </c>
       <c r="K10" t="n">
-        <v>8.655092556628991e-06</v>
+        <v>7.300184517667918e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>6.073045656095798e-06</v>
+        <v>5.698048824358937e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.503304723221623e-06</v>
+        <v>-8.691806851142419e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004536335745676274</v>
+        <v>0.004311694306037258</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006942952701584735</v>
+        <v>0.0006193173413198168</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.152465245097748e-06</v>
+        <v>-4.334224229830869e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01764635388103663</v>
+        <v>0.01585268796378277</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001895478873876016</v>
+        <v>0.0001915181996051552</v>
       </c>
       <c r="S10" t="n">
-        <v>4.957298464688405e-06</v>
+        <v>4.538711218472183e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07784774543321717</v>
+        <v>0.0670848689354724</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03277076939265744</v>
+        <v>0.03056298822878646</v>
       </c>
       <c r="V10" t="n">
-        <v>2.452106812550828e-06</v>
+        <v>2.342419147874125e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003362358257878419</v>
+        <v>0.0003269952628084279</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01220563268114982</v>
+        <v>0.01182402552573083</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02801358759864141</v>
+        <v>0.02651974913106421</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2521,70 +2521,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.295211669058601</v>
+        <v>-1.320902128073951</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.587288147203645</v>
+        <v>-1.590799838576672</v>
       </c>
       <c r="F11" t="n">
-        <v>0.204892102990357</v>
+        <v>0.1837670328532788</v>
       </c>
       <c r="G11" t="n">
-        <v>2.601266596963642e-07</v>
+        <v>2.568577064977733e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.776562439286423e-06</v>
+        <v>6.71279847143162e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.534444818097766e-05</v>
+        <v>4.286974327631856e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001586873086612161</v>
+        <v>0.0001449922121666099</v>
       </c>
       <c r="K11" t="n">
-        <v>6.938852258171009e-06</v>
+        <v>6.25713811905575e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.542681204280627e-06</v>
+        <v>6.412994932103973e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.052326025607139e-05</v>
+        <v>-1.232690523299285e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004606745876187312</v>
+        <v>0.004408068060791814</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003373521385567686</v>
+        <v>0.0003029178157643883</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.852513101995552e-06</v>
+        <v>-6.041955578430015e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01090155629395872</v>
+        <v>0.01011829992180976</v>
       </c>
       <c r="R11" t="n">
-        <v>7.151385629783058e-05</v>
+        <v>6.924576184647557e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.729556646114099e-06</v>
+        <v>3.55086519756684e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01264450920801339</v>
+        <v>0.01240561713046286</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02362616739407782</v>
+        <v>0.02496506383980429</v>
       </c>
       <c r="V11" t="n">
-        <v>2.318558766892811e-06</v>
+        <v>2.260592111522401e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003216123663310024</v>
+        <v>0.0003185017529477076</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01171143252600476</v>
+        <v>0.01136342941515748</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02274823121653961</v>
+        <v>0.02198455760468075</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.5208308366090769</v>
+        <v>-0.6182362284556114</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.543640299864819</v>
+        <v>-1.547784669004612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6380561412452856</v>
+        <v>0.5647350677270536</v>
       </c>
       <c r="G2" t="n">
-        <v>2.984454214624129e-07</v>
+        <v>2.967052734860615e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.523095385633446e-06</v>
+        <v>8.29777497371651e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001266915278508042</v>
+        <v>0.00012148093336588</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004275772565445741</v>
+        <v>0.0004136876998668455</v>
       </c>
       <c r="K2" t="n">
-        <v>2.50344570793607e-05</v>
+        <v>2.36171297709628e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.223884065407576e-05</v>
+        <v>1.265140367188762e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.592701516855507e-05</v>
+        <v>8.650721919925382e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008223914620516599</v>
+        <v>0.008394229475622506</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003838809415013736</v>
+        <v>0.003617560147030653</v>
       </c>
       <c r="P2" t="n">
-        <v>5.221776058905534e-05</v>
+        <v>5.276176111896948e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03969714077580061</v>
+        <v>0.03818848892144527</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003140044090813449</v>
+        <v>0.0003320302303811611</v>
       </c>
       <c r="S2" t="n">
-        <v>6.389143387132737e-06</v>
+        <v>6.136213295679914e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2371683117825592</v>
+        <v>0.2219221647279446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04379334692413765</v>
+        <v>0.04219095408895414</v>
       </c>
       <c r="V2" t="n">
-        <v>3.210913585271694e-06</v>
+        <v>3.133795135691772e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004023305245837792</v>
+        <v>0.0004002502981944428</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01491670501361362</v>
+        <v>0.0147820899870638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03565060669689291</v>
+        <v>0.03425699165471949</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2830,70 +2830,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.6388404557494289</v>
+        <v>-0.740660942280473</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.548552526799714</v>
+        <v>-1.553175046228752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5405386626997369</v>
+        <v>0.4669492516850288</v>
       </c>
       <c r="G3" t="n">
-        <v>2.938249295552e-07</v>
+        <v>2.910982836229393e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.433865932149897e-06</v>
+        <v>8.186346744262235e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00012138318602283</v>
+        <v>0.0001148966337932856</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003916593801250655</v>
+        <v>0.0003800529191866535</v>
       </c>
       <c r="K3" t="n">
-        <v>2.397248798693176e-05</v>
+        <v>2.259359825624103e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.24875626648807e-06</v>
+        <v>9.43119966464731e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.349104392331186e-05</v>
+        <v>7.496199314546062e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006598496097750385</v>
+        <v>0.006687890701502687</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003604726379278822</v>
+        <v>0.003372992321914142</v>
       </c>
       <c r="P3" t="n">
-        <v>4.464421096513778e-05</v>
+        <v>4.579048438156887e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03602073614977452</v>
+        <v>0.03459804462280838</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003055084980191464</v>
+        <v>0.0003212237757518625</v>
       </c>
       <c r="S3" t="n">
-        <v>6.103346785554142e-06</v>
+        <v>5.799016651922711e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2313193694814723</v>
+        <v>0.2128507111936727</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0417765403032035</v>
+        <v>0.03988270036831714</v>
       </c>
       <c r="V3" t="n">
-        <v>3.148995043468605e-06</v>
+        <v>3.053801267327755e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003791611948882342</v>
+        <v>0.0003750554295336958</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01404529179711745</v>
+        <v>0.01383729935453026</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03444115632082735</v>
+        <v>0.03297383526331501</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7255036931646232</v>
+        <v>-0.8220554352904378</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.552859878087658</v>
+        <v>-1.557577317309589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4737692706975236</v>
+        <v>0.4059401820380397</v>
       </c>
       <c r="G4" t="n">
-        <v>2.927454183056332e-07</v>
+        <v>2.88495663422383e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.33694505814349e-06</v>
+        <v>8.073491503656936e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001162370346069258</v>
+        <v>0.0001085090953228953</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000394399647161848</v>
+        <v>0.0003790084812489929</v>
       </c>
       <c r="K4" t="n">
-        <v>2.351893276114675e-05</v>
+        <v>2.206349487019849e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13651508887753e-05</v>
+        <v>1.152786547445038e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.296972782481752e-05</v>
+        <v>6.340097150061036e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007500770538863322</v>
+        <v>0.007584124395116987</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003258336336513775</v>
+        <v>0.00302688351811925</v>
       </c>
       <c r="P4" t="n">
-        <v>3.824850222583101e-05</v>
+        <v>3.876270632857582e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03472997528472878</v>
+        <v>0.03307471650933609</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002901491587058078</v>
+        <v>0.0003016517052066571</v>
       </c>
       <c r="S4" t="n">
-        <v>6.008275873013482e-06</v>
+        <v>5.655265380564695e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2184721326041908</v>
+        <v>0.2000520167655542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04098404675469247</v>
+        <v>0.03893406919391242</v>
       </c>
       <c r="V4" t="n">
-        <v>3.12418914390435e-06</v>
+        <v>3.01915409020705e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003816985413991878</v>
+        <v>0.000377037710459298</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01406623360557272</v>
+        <v>0.01385317096912715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03323902780654613</v>
+        <v>0.03173767865041889</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2998,70 +2998,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7970441906012755</v>
+        <v>-0.8754081291484458</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.556738233570283</v>
+        <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4358737477258912</v>
+        <v>0.3806219055814981</v>
       </c>
       <c r="G5" t="n">
-        <v>2.917016178548731e-07</v>
+        <v>2.883344926157958e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.11946684566222e-06</v>
+        <v>7.88415612494884e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000109730865109514</v>
+        <v>0.0001024999723783849</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003912708848375731</v>
+        <v>0.000376363985234908</v>
       </c>
       <c r="K5" t="n">
-        <v>1.97708710358678e-05</v>
+        <v>1.855541770166522e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57605876896943e-05</v>
+        <v>1.614399578552711e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.598449067432354e-05</v>
+        <v>6.671436404062432e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009563910066825788</v>
+        <v>0.00976047937667022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002845526751928385</v>
+        <v>0.002647843563617878</v>
       </c>
       <c r="P5" t="n">
-        <v>4.016268801886045e-05</v>
+        <v>4.081677275278294e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0315561254045422</v>
+        <v>0.02999212139064207</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002679156197843732</v>
+        <v>0.0002773755225273111</v>
       </c>
       <c r="S5" t="n">
-        <v>5.876633588545471e-06</v>
+        <v>5.548797294451969e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1922095651264997</v>
+        <v>0.1780728838070509</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04024225103354983</v>
+        <v>0.03845948738098717</v>
       </c>
       <c r="V5" t="n">
-        <v>2.95613906815004e-06</v>
+        <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003980019919055489</v>
+        <v>0.0003948150479346347</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01456717915598267</v>
+        <v>0.01442301014128574</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03150985462883569</v>
+        <v>0.03021285433597517</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3082,70 +3082,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.083171446913733</v>
+        <v>-1.127739769395991</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.578830274545917</v>
+        <v>-1.583529197938965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3501711297272686</v>
+        <v>0.3189619017288311</v>
       </c>
       <c r="G6" t="n">
-        <v>2.678556754452359e-07</v>
+        <v>2.629743532180668e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.131051423049384e-06</v>
+        <v>7.00744658362135e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.549933590248229e-05</v>
+        <v>5.994515887725199e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002346749130229082</v>
+        <v>0.0002218360582685596</v>
       </c>
       <c r="K6" t="n">
-        <v>9.428134489366389e-06</v>
+        <v>8.313474661720802e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.397422519193585e-06</v>
+        <v>4.011007074466353e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.479553093783973e-05</v>
+        <v>2.408844445253663e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003592882216917141</v>
+        <v>0.003413721912265724</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001328710325166195</v>
+        <v>0.001235825335481854</v>
       </c>
       <c r="P6" t="n">
-        <v>1.601200290212819e-05</v>
+        <v>1.563588664813284e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01422948311527578</v>
+        <v>0.01333701183812303</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001272976197297748</v>
+        <v>0.0001282976709059454</v>
       </c>
       <c r="S6" t="n">
-        <v>4.204067264215096e-06</v>
+        <v>3.911559314590972e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06001336585039163</v>
+        <v>0.05547084700405661</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02870253846434258</v>
+        <v>0.02718795563138739</v>
       </c>
       <c r="V6" t="n">
-        <v>2.445636668598097e-06</v>
+        <v>2.350073527008297e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003240802142328521</v>
+        <v>0.0003134989871089374</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01176532636107058</v>
+        <v>0.01138229085736368</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02503512352431177</v>
+        <v>0.02401068144548199</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.228558175150788</v>
+        <v>-1.256227195365545</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.589900700460991</v>
+        <v>-1.594335350441187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2735881464320915</v>
+        <v>0.2550919725281227</v>
       </c>
       <c r="G7" t="n">
-        <v>2.57942206107982e-07</v>
+        <v>2.519333067941321e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.829407418963171e-06</v>
+        <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.62534965102777e-05</v>
+        <v>4.057975714113774e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001771595582368021</v>
+        <v>0.0001634258239776595</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.419317233416729e-06</v>
+        <v>-6.666578390180699e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.941933952664982e-06</v>
+        <v>3.408213536697682e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.38824326506882e-05</v>
+        <v>-1.576179324597284e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003115223133395875</v>
+        <v>0.002852673887755092</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000384252016980555</v>
+        <v>0.0003511833579318713</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.150375765521175e-06</v>
+        <v>-8.306313779496389e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007780705773031575</v>
+        <v>0.006949757463137796</v>
       </c>
       <c r="R7" t="n">
-        <v>6.190599179961673e-05</v>
+        <v>5.894403635046219e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.651876098830449e-06</v>
+        <v>3.377463070821941e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01744030167551252</v>
+        <v>0.01650860249098277</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02513214986569703</v>
+        <v>0.0237718999516727</v>
       </c>
       <c r="V7" t="n">
-        <v>1.809168029065866e-06</v>
+        <v>1.710369379189882e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003079313759237366</v>
+        <v>0.0002970973080769404</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01101356487231434</v>
+        <v>0.01060272397536547</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02230486080155479</v>
+        <v>0.02143450870345178</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.27727904899128</v>
+        <v>-1.298423749374308</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.59511408432486</v>
+        <v>-1.598715785791028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2466911226302814</v>
+        <v>0.2331338993203419</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5219950691167e-07</v>
+        <v>2.483967374914811e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.684710252674426e-06</v>
+        <v>6.617095439383984e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.949402798952767e-05</v>
+        <v>3.478206161720463e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001082783609247903</v>
+        <v>9.33764537050936e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.352667417555761e-06</v>
+        <v>-9.748427478810463e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>4.432567977278747e-06</v>
+        <v>3.874226954002219e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.070889147111446e-05</v>
+        <v>-1.27453122669307e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003247782951171726</v>
+        <v>0.002941585529239589</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004017150555136959</v>
+        <v>0.0003614663475157456</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.273446401444332e-06</v>
+        <v>-6.613356735135387e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003498316484202467</v>
+        <v>0.002643969675912246</v>
       </c>
       <c r="R8" t="n">
-        <v>6.318400981914636e-05</v>
+        <v>6.007275999553564e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.362193285835949e-06</v>
+        <v>3.142631698581945e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008093835738304573</v>
+        <v>0.007516435846575896</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02359435354804461</v>
+        <v>0.02247190753168225</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69914158974083e-06</v>
+        <v>1.611739468424993e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0003034607070947392</v>
+        <v>0.0002936029220226869</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01076821513162563</v>
+        <v>0.01042652077510718</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02103314932546677</v>
+        <v>0.02032799867849813</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3334,70 +3334,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.752429303658901</v>
+        <v>-0.8456452961338262</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.556725776417249</v>
+        <v>-1.561927546685941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.498623364960652</v>
+        <v>0.4331607301579157</v>
       </c>
       <c r="G9" t="n">
-        <v>2.876251985609642e-07</v>
+        <v>2.832970733688222e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.252529158133144e-06</v>
+        <v>7.995921861823704e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001064841742126046</v>
+        <v>9.900859556574505e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003294856130470996</v>
+        <v>0.0003133471461989699</v>
       </c>
       <c r="K9" t="n">
-        <v>1.779779759276699e-05</v>
+        <v>1.614932724148671e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.167602754122513e-06</v>
+        <v>8.136039710518895e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.608340559183711e-05</v>
+        <v>4.561153676457521e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005842860599028159</v>
+        <v>0.005797721084024394</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003294203225700093</v>
+        <v>0.003056558056256892</v>
       </c>
       <c r="P9" t="n">
-        <v>2.81770975446817e-05</v>
+        <v>2.809672123789917e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02864267932226826</v>
+        <v>0.02690089148043396</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000271661883021187</v>
+        <v>0.0002837415493334886</v>
       </c>
       <c r="S9" t="n">
-        <v>5.736294117122319e-06</v>
+        <v>5.378735027035154e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1822643546579034</v>
+        <v>0.165665832607281</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03887410218274584</v>
+        <v>0.03679014917743906</v>
       </c>
       <c r="V9" t="n">
-        <v>2.868030028651272e-06</v>
+        <v>2.754907142699131e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003644210123998408</v>
+        <v>0.0003578503953903428</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01343402698694935</v>
+        <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03213141727304096</v>
+        <v>0.0305957347075486</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.025409965987958</v>
+        <v>-1.089846263233557</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.572614478790379</v>
+        <v>-1.578132706625494</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3726417776790972</v>
+        <v>0.3307046410508491</v>
       </c>
       <c r="G10" t="n">
-        <v>2.748103029401187e-07</v>
+        <v>2.677170814798685e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.840360181233483e-06</v>
+        <v>7.589085260944301e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>7.180068041968735e-05</v>
+        <v>6.335373248768603e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002297984827315466</v>
+        <v>0.0002098588280031235</v>
       </c>
       <c r="K10" t="n">
-        <v>8.655092556628991e-06</v>
+        <v>7.300184517667918e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>6.073045656095798e-06</v>
+        <v>5.698048824358937e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.503304723221623e-06</v>
+        <v>-8.691806851142419e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004536335745676274</v>
+        <v>0.004311694306037258</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006942952701584735</v>
+        <v>0.0006193173413198168</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.152465245097748e-06</v>
+        <v>-4.334224229830869e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01764635388103663</v>
+        <v>0.01585268796378277</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001895478873876016</v>
+        <v>0.0001915181996051552</v>
       </c>
       <c r="S10" t="n">
-        <v>4.957298464688405e-06</v>
+        <v>4.538711218472183e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07784774543321717</v>
+        <v>0.0670848689354724</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03277076939265744</v>
+        <v>0.03056298822878646</v>
       </c>
       <c r="V10" t="n">
-        <v>2.452106812550828e-06</v>
+        <v>2.342419147874125e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003362358257878419</v>
+        <v>0.0003269952628084279</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01220563268114982</v>
+        <v>0.01182402552573083</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02801358759864141</v>
+        <v>0.02651974913106421</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>methanol synthesis, hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
+          <t>methanol synthesis, hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity carbon dioxide, captured from atmosphere, with a solvent-based direct air capture system, 1MtCO2, with heat pump heat, and onshore wind electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.279349830733657</v>
+        <v>-1.247518287573014</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.587288147203645</v>
+        <v>-1.590799838576672</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2207539413213406</v>
+        <v>0.2571508733822176</v>
       </c>
       <c r="G11" t="n">
-        <v>2.601266596963642e-07</v>
+        <v>2.568577064977733e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.776562439286423e-06</v>
+        <v>6.71279847143162e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.534444818097766e-05</v>
+        <v>4.286974327631856e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001586873086612161</v>
+        <v>0.0001449922121666099</v>
       </c>
       <c r="K11" t="n">
-        <v>6.938852258171009e-06</v>
+        <v>6.25713811905575e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.542681204280627e-06</v>
+        <v>6.412994932103973e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.052326025607139e-05</v>
+        <v>-1.232690523299285e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004606745876187312</v>
+        <v>0.004408068060791814</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003373521385567686</v>
+        <v>0.0003029178157643883</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.852513101995552e-06</v>
+        <v>-6.041955578430015e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01090155629395872</v>
+        <v>0.01011829992180976</v>
       </c>
       <c r="R11" t="n">
-        <v>7.151385629783058e-05</v>
+        <v>6.924576184647557e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.729556646114099e-06</v>
+        <v>3.55086519756684e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01264450920801339</v>
+        <v>0.01240561713046286</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02362616739407782</v>
+        <v>0.02496506383980429</v>
       </c>
       <c r="V11" t="n">
-        <v>2.318558766892811e-06</v>
+        <v>2.260592111522401e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003216123663310024</v>
+        <v>0.0003185017529477076</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01171143252600476</v>
+        <v>0.01136342941515748</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02274823121653961</v>
+        <v>0.02198455760468075</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7499402999043687</v>
+        <v>0.7499402999043684</v>
       </c>
       <c r="E4" t="n">
-        <v>0.182638839815567</v>
+        <v>0.1826388398155669</v>
       </c>
       <c r="F4" t="n">
         <v>0.4895073441437352</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261114</v>
+        <v>0.04572335899261105</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382351e-05</v>
+        <v>6.771938650382362e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773626</v>
+        <v>0.0004620497936773625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694058</v>
+        <v>0.0003863222939694053</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985246761</v>
+        <v>0.0003961016985248961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270789</v>
+        <v>0.0003437323729270796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906748</v>
+        <v>0.001164447078906752</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0291059959604576</v>
+        <v>0.02910599596045715</v>
       </c>
     </row>
     <row r="5">
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7434813395247808</v>
+        <v>0.7434813395247807</v>
       </c>
       <c r="E5" t="n">
         <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4880694926684757</v>
+        <v>0.4880694926684758</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04161857570575983</v>
+        <v>0.04161857570575978</v>
       </c>
       <c r="H5" t="n">
-        <v>7.20020714297296e-05</v>
+        <v>7.200207142972934e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518199</v>
+        <v>0.0001351017835518196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144923</v>
+        <v>0.0004364619477144914</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000378926107684234</v>
+        <v>0.000378926107684233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242100166</v>
+        <v>0.0003784082242096817</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061816</v>
+        <v>0.0003359067485061803</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635165</v>
+        <v>0.001100141444635161</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599591518026</v>
+        <v>0.02910599591518037</v>
       </c>
     </row>
     <row r="6">
@@ -782,7 +782,7 @@
         <v>0.4780951759294803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004005592633530719</v>
+        <v>0.004005592633530718</v>
       </c>
       <c r="H7" t="n">
         <v>1.236515770175312e-05</v>
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4517748338148098</v>
+        <v>0.4517748338148095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.182638839815567</v>
+        <v>0.1826388398155669</v>
       </c>
       <c r="F4" t="n">
         <v>0.191341870668391</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261114</v>
+        <v>0.04572335899261105</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382351e-05</v>
+        <v>6.771938650382362e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773626</v>
+        <v>0.0004620497936773625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694058</v>
+        <v>0.0003863222939694053</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985246761</v>
+        <v>0.0003961016985248961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270789</v>
+        <v>0.0003437323729270796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906748</v>
+        <v>0.001164447078906752</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600334624275</v>
+        <v>0.02910600334624253</v>
       </c>
     </row>
     <row r="5">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4380690907253919</v>
+        <v>0.4380690907253913</v>
       </c>
       <c r="E5" t="n">
         <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1826572363037926</v>
+        <v>0.1826572363037925</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04161857570575983</v>
+        <v>0.04161857570575978</v>
       </c>
       <c r="H5" t="n">
-        <v>7.20020714297296e-05</v>
+        <v>7.200207142972934e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518199</v>
+        <v>0.0001351017835518196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144923</v>
+        <v>0.0004364619477144914</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000378926107684234</v>
+        <v>0.000378926107684233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242100166</v>
+        <v>0.0003784082242096817</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061816</v>
+        <v>0.0003359067485061803</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635165</v>
+        <v>0.001100141444635161</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600348047454</v>
+        <v>0.02910600348047443</v>
       </c>
     </row>
     <row r="6">
@@ -1378,7 +1378,7 @@
         <v>0.102436253384841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004005592633530719</v>
+        <v>0.004005592633530718</v>
       </c>
       <c r="H7" t="n">
         <v>1.236515770175312e-05</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9582979757847239</v>
+        <v>-0.9582979757847546</v>
       </c>
       <c r="E4" t="n">
         <v>-1.557577317309589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2696976414916735</v>
+        <v>0.2696976414916737</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88495663422383e-07</v>
+        <v>2.884956634223812e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656936e-06</v>
+        <v>8.073491503656977e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228953</v>
+        <v>0.0001085090953228945</v>
       </c>
       <c r="J4" t="n">
         <v>0.0003790084812489929</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019849e-05</v>
+        <v>2.206349487019852e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445038e-05</v>
+        <v>1.152786547445039e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.340097150061036e-05</v>
+        <v>6.340097150061023e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395116987</v>
+        <v>0.007584124395111018</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00302688351811925</v>
+        <v>0.003026883518119253</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857582e-05</v>
+        <v>3.876270632857585e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933609</v>
+        <v>0.03307471650933492</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066571</v>
+        <v>0.0003016517052066576</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564695e-06</v>
+        <v>5.655265380564692e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2000520167655542</v>
+        <v>0.200052016765554</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391242</v>
+        <v>0.03893406919391239</v>
       </c>
       <c r="V4" t="n">
-        <v>3.01915409020705e-06</v>
+        <v>3.019154090207049e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000377037710459298</v>
+        <v>0.0003770377104592982</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01385317096912715</v>
+        <v>0.01385317096912716</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041889</v>
+        <v>0.03173767865041887</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,64 +2017,64 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9923784544815986</v>
+        <v>-0.9923784544816133</v>
       </c>
       <c r="E5" t="n">
         <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2636515802036559</v>
+        <v>0.2636515802036539</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926157958e-07</v>
+        <v>2.883344926158018e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.88415612494884e-06</v>
+        <v>7.884156124948789e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783849</v>
+        <v>0.0001024999723783845</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000376363985234908</v>
+        <v>0.0003763639852349078</v>
       </c>
       <c r="K5" t="n">
-        <v>1.855541770166522e-05</v>
+        <v>1.855541770166519e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.614399578552711e-05</v>
+        <v>1.614399578552151e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062432e-05</v>
+        <v>6.671436404062409e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00976047937667022</v>
+        <v>0.00976047937666529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617878</v>
+        <v>0.002647843563617872</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278294e-05</v>
+        <v>4.081677275278283e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139064207</v>
+        <v>0.02999212139064692</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273111</v>
+        <v>0.0002773755225273109</v>
       </c>
       <c r="S5" t="n">
-        <v>5.548797294451969e-06</v>
+        <v>5.548797294451971e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070509</v>
+        <v>0.1780728838070505</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03845948738098717</v>
+        <v>0.03845948738098709</v>
       </c>
       <c r="V5" t="n">
-        <v>2.860903834275749e-06</v>
+        <v>2.860903834275751e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003948150479346347</v>
+        <v>0.0003948150479346339</v>
       </c>
       <c r="X5" t="n">
         <v>0.01442301014128574</v>
@@ -2194,7 +2194,7 @@
         <v>0.1716363794886081</v>
       </c>
       <c r="G7" t="n">
-        <v>2.519333067941321e-07</v>
+        <v>2.51933306794132e-07</v>
       </c>
       <c r="H7" t="n">
         <v>6.740428647757436e-06</v>
@@ -2203,10 +2203,10 @@
         <v>4.057975714113774e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001634258239776595</v>
+        <v>0.0001634258239776594</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180699e-06</v>
+        <v>-6.666578390180706e-06</v>
       </c>
       <c r="L7" t="n">
         <v>3.408213536697682e-06</v>
@@ -2215,13 +2215,13 @@
         <v>-1.576179324597284e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887755092</v>
+        <v>0.002852673887755093</v>
       </c>
       <c r="O7" t="n">
         <v>0.0003511833579318713</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496389e-06</v>
+        <v>-8.306313779496392e-06</v>
       </c>
       <c r="Q7" t="n">
         <v>0.006949757463137796</v>
@@ -2554,10 +2554,10 @@
         <v>0.004408068060791814</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643883</v>
+        <v>0.0003029178157643884</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430015e-06</v>
+        <v>-6.041955578430012e-06</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01011829992180976</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.8220554352904378</v>
+        <v>-0.8220554352904254</v>
       </c>
       <c r="E4" t="n">
         <v>-1.557577317309589</v>
@@ -2923,61 +2923,61 @@
         <v>0.4059401820380397</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88495663422383e-07</v>
+        <v>2.884956634223812e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656936e-06</v>
+        <v>8.073491503656977e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228953</v>
+        <v>0.0001085090953228945</v>
       </c>
       <c r="J4" t="n">
         <v>0.0003790084812489929</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019849e-05</v>
+        <v>2.206349487019852e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445038e-05</v>
+        <v>1.152786547445039e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.340097150061036e-05</v>
+        <v>6.340097150061023e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395116987</v>
+        <v>0.007584124395111018</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00302688351811925</v>
+        <v>0.003026883518119253</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857582e-05</v>
+        <v>3.876270632857585e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933609</v>
+        <v>0.03307471650933492</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066571</v>
+        <v>0.0003016517052066576</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564695e-06</v>
+        <v>5.655265380564692e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2000520167655542</v>
+        <v>0.200052016765554</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391242</v>
+        <v>0.03893406919391239</v>
       </c>
       <c r="V4" t="n">
-        <v>3.01915409020705e-06</v>
+        <v>3.019154090207049e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000377037710459298</v>
+        <v>0.0003770377104592982</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01385317096912715</v>
+        <v>0.01385317096912716</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041889</v>
+        <v>0.03173767865041887</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,64 +2998,64 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8754081291484458</v>
+        <v>-0.8754081291484425</v>
       </c>
       <c r="E5" t="n">
         <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3806219055814981</v>
+        <v>0.3806219055814968</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926157958e-07</v>
+        <v>2.883344926158018e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.88415612494884e-06</v>
+        <v>7.884156124948789e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783849</v>
+        <v>0.0001024999723783845</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000376363985234908</v>
+        <v>0.0003763639852349078</v>
       </c>
       <c r="K5" t="n">
-        <v>1.855541770166522e-05</v>
+        <v>1.855541770166519e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.614399578552711e-05</v>
+        <v>1.614399578552151e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062432e-05</v>
+        <v>6.671436404062409e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00976047937667022</v>
+        <v>0.00976047937666529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617878</v>
+        <v>0.002647843563617872</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278294e-05</v>
+        <v>4.081677275278283e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139064207</v>
+        <v>0.02999212139064692</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273111</v>
+        <v>0.0002773755225273109</v>
       </c>
       <c r="S5" t="n">
-        <v>5.548797294451969e-06</v>
+        <v>5.548797294451971e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070509</v>
+        <v>0.1780728838070505</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03845948738098717</v>
+        <v>0.03845948738098709</v>
       </c>
       <c r="V5" t="n">
-        <v>2.860903834275749e-06</v>
+        <v>2.860903834275751e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003948150479346347</v>
+        <v>0.0003948150479346339</v>
       </c>
       <c r="X5" t="n">
         <v>0.01442301014128574</v>
@@ -3175,7 +3175,7 @@
         <v>0.2550919725281227</v>
       </c>
       <c r="G7" t="n">
-        <v>2.519333067941321e-07</v>
+        <v>2.51933306794132e-07</v>
       </c>
       <c r="H7" t="n">
         <v>6.740428647757436e-06</v>
@@ -3184,10 +3184,10 @@
         <v>4.057975714113774e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001634258239776595</v>
+        <v>0.0001634258239776594</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180699e-06</v>
+        <v>-6.666578390180706e-06</v>
       </c>
       <c r="L7" t="n">
         <v>3.408213536697682e-06</v>
@@ -3196,13 +3196,13 @@
         <v>-1.576179324597284e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887755092</v>
+        <v>0.002852673887755093</v>
       </c>
       <c r="O7" t="n">
         <v>0.0003511833579318713</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496389e-06</v>
+        <v>-8.306313779496392e-06</v>
       </c>
       <c r="Q7" t="n">
         <v>0.006949757463137796</v>
@@ -3535,10 +3535,10 @@
         <v>0.004408068060791814</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643883</v>
+        <v>0.0003029178157643884</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430015e-06</v>
+        <v>-6.041955578430012e-06</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01011829992180976</v>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7601163848026872</v>
+        <v>0.760116384802687</v>
       </c>
       <c r="E2" t="n">
         <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4920544887818212</v>
+        <v>0.4920544887818216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05008330144474995</v>
+        <v>0.05008330144475</v>
       </c>
       <c r="H2" t="n">
-        <v>7.949768237084973e-05</v>
+        <v>7.949768237085004e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001613694320761283</v>
+        <v>0.0001613694320761285</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000517286039759243</v>
+        <v>0.0005172860397592441</v>
       </c>
       <c r="K2" t="n">
         <v>0.000409794518758543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004302669151791527</v>
+        <v>0.0004302669151784652</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003579362092265941</v>
+        <v>0.0003579362092265943</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001368727882702079</v>
+        <v>0.001368727882702081</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599605561259</v>
+        <v>0.02910599605561281</v>
       </c>
     </row>
     <row r="3">
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7548790495114223</v>
+        <v>0.7548790495114228</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1838291906059022</v>
+        <v>0.1838291906059023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4905789875069382</v>
+        <v>0.4905789875069383</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04821494231345641</v>
+        <v>0.04821494231345652</v>
       </c>
       <c r="H3" t="n">
-        <v>7.022525470537622e-05</v>
+        <v>7.022525470537647e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001518113141943921</v>
+        <v>0.0001518113141943995</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004892489959522313</v>
+        <v>0.0004892489959522408</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000399244423139644</v>
+        <v>0.0003992444231396447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004081963405496427</v>
+        <v>0.0004081963405497707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003511156023621058</v>
+        <v>0.0003511156023621053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001280091146362088</v>
+        <v>0.00128009114636209</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599600786001</v>
+        <v>0.0291059960078599</v>
       </c>
     </row>
     <row r="4">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7499402999043684</v>
+        <v>0.7499402999043683</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1826388398155669</v>
+        <v>0.1826388398155667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4895073441437352</v>
+        <v>0.489507344143735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261105</v>
+        <v>0.0457233589926111</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382362e-05</v>
+        <v>6.771938650382357e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773625</v>
+        <v>0.0004620497936773616</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694053</v>
+        <v>0.0003863222939694049</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985248961</v>
+        <v>0.0003961016985248371</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270796</v>
+        <v>0.0003437323729270788</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906752</v>
+        <v>0.00116444707890675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910599596045715</v>
+        <v>0.02910599596045749</v>
       </c>
     </row>
     <row r="5">
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7434813395247807</v>
+        <v>0.7434813395247806</v>
       </c>
       <c r="E5" t="n">
         <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4880694926684758</v>
+        <v>0.4880694926684755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04161857570575978</v>
+        <v>0.04161857570575974</v>
       </c>
       <c r="H5" t="n">
-        <v>7.200207142972934e-05</v>
+        <v>7.200207142972945e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518196</v>
+        <v>0.0001351017835518195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144914</v>
+        <v>0.000436461947714484</v>
       </c>
       <c r="K5" t="n">
         <v>0.000378926107684233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242096817</v>
+        <v>0.0003784082242097028</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061803</v>
+        <v>0.00033590674850618</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635161</v>
+        <v>0.001100141444635159</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599591518037</v>
+        <v>0.0291059959151807</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6988591235739661</v>
+        <v>0.6988591235739655</v>
       </c>
       <c r="E6" t="n">
         <v>0.1734341181339289</v>
@@ -734,28 +734,28 @@
         <v>0.01323200409367944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.157387977904127e-05</v>
+        <v>3.15738797790411e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.796561525975038e-05</v>
+        <v>7.796561525975032e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002552564668313758</v>
+        <v>0.0002552564668313752</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003306029768954351</v>
+        <v>0.0003306029768954349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002533766492009103</v>
+        <v>0.0002533766492000678</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00029851366603648</v>
+        <v>0.0002985136660364799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007693260029412952</v>
+        <v>0.000769326002941294</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599542708003</v>
+        <v>0.02910599542708014</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6820804847150554</v>
+        <v>0.6820804847150549</v>
       </c>
       <c r="E7" t="n">
         <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4780951759294803</v>
+        <v>0.47809517592948</v>
       </c>
       <c r="G7" t="n">
         <v>0.004005592633530718</v>
       </c>
       <c r="H7" t="n">
-        <v>1.236515770175312e-05</v>
+        <v>1.236515770175322e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.760624072710079e-05</v>
+        <v>5.760624072710092e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001727953620730635</v>
+        <v>0.0001727953620730642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002977309488706833</v>
+        <v>0.0002977309488706837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002149280445553775</v>
+        <v>0.0002149280445546237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002818988823972426</v>
+        <v>0.0002818988823972428</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005395976008691114</v>
+        <v>0.0005395976008691139</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599523675939</v>
+        <v>0.02910599523675994</v>
       </c>
     </row>
     <row r="8">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6763900264371993</v>
+        <v>0.6763900264371988</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1677644037114065</v>
+        <v>0.1677644037114066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.476583194125612</v>
+        <v>0.4765831941256122</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001516222820624146</v>
+        <v>0.00151622282062415</v>
       </c>
       <c r="H8" t="n">
-        <v>7.16512490384524e-06</v>
+        <v>7.165124903845237e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.043924548616532e-05</v>
+        <v>5.043924548616545e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001481078092677816</v>
+        <v>0.0001481078092677832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002870625570381503</v>
+        <v>0.0002870625570381508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001977439027298401</v>
+        <v>0.0001977439027294321</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002749288836533894</v>
+        <v>0.0002749288836533896</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004547630681316607</v>
+        <v>0.0004547630681316602</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599518834567</v>
+        <v>0.02910599518834545</v>
       </c>
     </row>
     <row r="9">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7396161025400686</v>
+        <v>0.7396161025400694</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1807834979870835</v>
+        <v>0.1807834979870836</v>
       </c>
       <c r="F9" t="n">
         <v>0.4877996382630265</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03912270071841051</v>
+        <v>0.03912270071841047</v>
       </c>
       <c r="H9" t="n">
-        <v>5.50138090354986e-05</v>
+        <v>5.501380903549855e-05</v>
       </c>
       <c r="I9" t="n">
         <v>0.0001323452292307473</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004215950839633038</v>
+        <v>0.0004215950839633037</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003753592200896617</v>
+        <v>0.0003753592200896615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003729347603893188</v>
+        <v>0.0003729347603889794</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003410339496637569</v>
+        <v>0.0003410339496637568</v>
       </c>
       <c r="N9" t="n">
         <v>0.001105987666444341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599585273144</v>
+        <v>0.02910599585273244</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7057775706302638</v>
+        <v>0.7057775706302633</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1746507049116373</v>
+        <v>0.1746507049116372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4831757397813212</v>
+        <v>0.4831757397813213</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01671526278688339</v>
+        <v>0.01671526278688338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.146291041691867e-05</v>
+        <v>3.146291041691862e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>9.407396674874718e-05</v>
+        <v>9.407396674874724e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002697707407615794</v>
+        <v>0.000269770740761578</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003358907712656632</v>
+        <v>0.0003358907712656637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003082578701390418</v>
+        <v>0.0003082578701390431</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003188749954166414</v>
+        <v>0.0003188749954166412</v>
       </c>
       <c r="N10" t="n">
-        <v>0.000771536432873719</v>
+        <v>0.0007715364328737201</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599546279968</v>
+        <v>0.02910599546279913</v>
       </c>
     </row>
     <row r="11">
@@ -977,31 +977,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6834152438511434</v>
+        <v>0.6834152438511432</v>
       </c>
       <c r="E11" t="n">
         <v>0.1705839027608459</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4791557473132457</v>
+        <v>0.4791557473132456</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002880084518684514</v>
+        <v>0.002880084518684503</v>
       </c>
       <c r="H11" t="n">
-        <v>2.810574286629256e-05</v>
+        <v>2.810574286629268e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.853933714735999e-05</v>
+        <v>5.853933714735985e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001825465042988459</v>
+        <v>0.0001825465042988463</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003112785164106755</v>
+        <v>0.0003112785164106758</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002227612681613601</v>
+        <v>0.0002227612681619385</v>
       </c>
       <c r="M11" t="n">
         <v>0.0002836507017147812</v>
@@ -1010,7 +1010,7 @@
         <v>0.0006026319471648411</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0291059952406032</v>
+        <v>0.02910599524060253</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4692672477434643</v>
+        <v>0.4692672477434636</v>
       </c>
       <c r="E2" t="n">
         <v>0.1855477198404307</v>
@@ -1123,31 +1123,31 @@
         <v>0.2012053445180427</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05008330144474995</v>
+        <v>0.05008330144475</v>
       </c>
       <c r="H2" t="n">
-        <v>7.949768237084973e-05</v>
+        <v>7.949768237085004e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001613694320761283</v>
+        <v>0.0001613694320761285</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000517286039759243</v>
+        <v>0.0005172860397592441</v>
       </c>
       <c r="K2" t="n">
         <v>0.000409794518758543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004302669151791527</v>
+        <v>0.0004302669151784652</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003579362092265941</v>
+        <v>0.0003579362092265943</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001368727882702079</v>
+        <v>0.001368727882702081</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600326016843</v>
+        <v>0.02910600326016832</v>
       </c>
     </row>
     <row r="3">
@@ -1165,40 +1165,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4611276245001504</v>
+        <v>0.4611276245001513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1838291906059022</v>
+        <v>0.1838291906059023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1968275552192192</v>
+        <v>0.1968275552192194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04821494231345641</v>
+        <v>0.04821494231345652</v>
       </c>
       <c r="H3" t="n">
-        <v>7.022525470537622e-05</v>
+        <v>7.022525470537647e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001518113141943921</v>
+        <v>0.0001518113141943995</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004892489959522313</v>
+        <v>0.0004892489959522408</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000399244423139644</v>
+        <v>0.0003992444231396447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004081963405496427</v>
+        <v>0.0004081963405497707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003511156023621058</v>
+        <v>0.0003511156023621053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001280091146362088</v>
+        <v>0.00128009114636209</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600328430707</v>
+        <v>0.02910600328430735</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4517748338148095</v>
+        <v>0.4517748338148106</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1826388398155669</v>
+        <v>0.1826388398155667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.191341870668391</v>
+        <v>0.1913418706683908</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261105</v>
+        <v>0.0457233589926111</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382362e-05</v>
+        <v>6.771938650382357e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.0001443883674887858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773625</v>
+        <v>0.0004620497936773616</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694053</v>
+        <v>0.0003863222939694049</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985248961</v>
+        <v>0.0003961016985248371</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270796</v>
+        <v>0.0003437323729270788</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906752</v>
+        <v>0.00116444707890675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600334624253</v>
+        <v>0.02910600334624397</v>
       </c>
     </row>
     <row r="5">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4380690907253913</v>
+        <v>0.4380690907253915</v>
       </c>
       <c r="E5" t="n">
         <v>0.1818503269076333</v>
@@ -1276,31 +1276,31 @@
         <v>0.1826572363037925</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04161857570575978</v>
+        <v>0.04161857570575974</v>
       </c>
       <c r="H5" t="n">
-        <v>7.200207142972934e-05</v>
+        <v>7.200207142972945e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518196</v>
+        <v>0.0001351017835518195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144914</v>
+        <v>0.000436461947714484</v>
       </c>
       <c r="K5" t="n">
         <v>0.000378926107684233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242096817</v>
+        <v>0.0003784082242097028</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061803</v>
+        <v>0.00033590674850618</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635161</v>
+        <v>0.001100141444635159</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600348047443</v>
+        <v>0.02910600348047454</v>
       </c>
     </row>
     <row r="6">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3402135485309888</v>
+        <v>0.3402135485309886</v>
       </c>
       <c r="E6" t="n">
         <v>0.1734341181339289</v>
@@ -1330,28 +1330,28 @@
         <v>0.01323200409367944</v>
       </c>
       <c r="H6" t="n">
-        <v>3.157387977904127e-05</v>
+        <v>3.15738797790411e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.796561525975038e-05</v>
+        <v>7.796561525975032e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002552564668313758</v>
+        <v>0.0002552564668313752</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003306029768954351</v>
+        <v>0.0003306029768954349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002533766492009103</v>
+        <v>0.0002533766492000678</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00029851366603648</v>
+        <v>0.0002985136660364799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007693260029412952</v>
+        <v>0.000769326002941294</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600431100285</v>
+        <v>0.02910600431100324</v>
       </c>
     </row>
     <row r="7">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3064215714757724</v>
+        <v>0.3064215714757727</v>
       </c>
       <c r="E7" t="n">
         <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.102436253384841</v>
+        <v>0.1024362533848411</v>
       </c>
       <c r="G7" t="n">
         <v>0.004005592633530718</v>
       </c>
       <c r="H7" t="n">
-        <v>1.236515770175312e-05</v>
+        <v>1.236515770175322e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.760624072710079e-05</v>
+        <v>5.760624072710092e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001727953620730635</v>
+        <v>0.0001727953620730642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002977309488706833</v>
+        <v>0.0002977309488706837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002149280445553775</v>
+        <v>0.0002149280445546237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002818988823972426</v>
+        <v>0.0002818988823972428</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005395976008691114</v>
+        <v>0.0005395976008691139</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600454211554</v>
+        <v>0.02910600454211659</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2967471889104039</v>
+        <v>0.2967471889104035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1677644037114065</v>
+        <v>0.1677644037114066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09694034719477437</v>
+        <v>0.0969403471947744</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001516222820624146</v>
+        <v>0.00151622282062415</v>
       </c>
       <c r="H8" t="n">
-        <v>7.16512490384524e-06</v>
+        <v>7.165124903845237e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.043924548616532e-05</v>
+        <v>5.043924548616545e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001481078092677816</v>
+        <v>0.0001481078092677832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002870625570381503</v>
+        <v>0.0002870625570381508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001977439027298401</v>
+        <v>0.0001977439027294321</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002749288836533894</v>
+        <v>0.0002749288836533896</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004547630681316607</v>
+        <v>0.0004547630681316602</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600459238816</v>
+        <v>0.02910600459238799</v>
       </c>
     </row>
     <row r="9">
@@ -1471,40 +1471,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4290321283374212</v>
+        <v>0.429032128337421</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1807834979870835</v>
+        <v>0.1807834979870836</v>
       </c>
       <c r="F9" t="n">
         <v>0.1772156563669754</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03912270071841051</v>
+        <v>0.03912270071841047</v>
       </c>
       <c r="H9" t="n">
-        <v>5.50138090354986e-05</v>
+        <v>5.501380903549855e-05</v>
       </c>
       <c r="I9" t="n">
         <v>0.0001323452292307473</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004215950839633038</v>
+        <v>0.0004215950839633037</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003753592200896617</v>
+        <v>0.0003753592200896615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003729347603893188</v>
+        <v>0.0003729347603889794</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003410339496637569</v>
+        <v>0.0003410339496637568</v>
       </c>
       <c r="N9" t="n">
         <v>0.001105987666444341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600354613513</v>
+        <v>0.02910600354613535</v>
       </c>
     </row>
     <row r="10">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3524360103104353</v>
+        <v>0.3524360103104349</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1746507049116373</v>
+        <v>0.1746507049116372</v>
       </c>
       <c r="F10" t="n">
         <v>0.1298341707089521</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01671526278688339</v>
+        <v>0.01671526278688338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.146291041691867e-05</v>
+        <v>3.146291041691862e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>9.407396674874718e-05</v>
+        <v>9.407396674874724e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002697707407615794</v>
+        <v>0.000269770740761578</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003358907712656632</v>
+        <v>0.0003358907712656637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003082578701390418</v>
+        <v>0.0003082578701390431</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003188749954166414</v>
+        <v>0.0003188749954166412</v>
       </c>
       <c r="N10" t="n">
-        <v>0.000771536432873719</v>
+        <v>0.0007715364328737201</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0291060042153401</v>
+        <v>0.02910600421533988</v>
       </c>
     </row>
     <row r="11">
@@ -1582,22 +1582,22 @@
         <v>0.1005964805122836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002880084518684514</v>
+        <v>0.002880084518684503</v>
       </c>
       <c r="H11" t="n">
-        <v>2.810574286629256e-05</v>
+        <v>2.810574286629268e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.853933714735999e-05</v>
+        <v>5.853933714735985e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001825465042988459</v>
+        <v>0.0001825465042988463</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003112785164106755</v>
+        <v>0.0003112785164106758</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002227612681613601</v>
+        <v>0.0002227612681619385</v>
       </c>
       <c r="M11" t="n">
         <v>0.0002836507017147812</v>
@@ -1606,7 +1606,7 @@
         <v>0.0006026319471648411</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600461780399</v>
+        <v>0.02910600461780344</v>
       </c>
     </row>
   </sheetData>
@@ -1765,70 +1765,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.8495586183774809</v>
+        <v>-0.8495586183774689</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.547784669004612</v>
+        <v>-1.54778466900461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3334126777168157</v>
+        <v>0.3334126777168165</v>
       </c>
       <c r="G2" t="n">
-        <v>2.967052734860615e-07</v>
+        <v>2.967052734860609e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.29777497371651e-06</v>
+        <v>8.297774973716524e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00012148093336588</v>
+        <v>0.0001214809333658804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004136876998668455</v>
+        <v>0.0004136876998668463</v>
       </c>
       <c r="K2" t="n">
-        <v>2.36171297709628e-05</v>
+        <v>2.361712977096283e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.265140367188762e-05</v>
+        <v>1.265140367188765e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.650721919925382e-05</v>
+        <v>8.650721919925389e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008394229475622506</v>
+        <v>0.008394229475619176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003617560147030653</v>
+        <v>0.00361756014703065</v>
       </c>
       <c r="P2" t="n">
-        <v>5.276176111896948e-05</v>
+        <v>5.27617611189695e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03818848892144527</v>
+        <v>0.03818848892145319</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003320302303811611</v>
+        <v>0.0003320302303811615</v>
       </c>
       <c r="S2" t="n">
-        <v>6.136213295679914e-06</v>
+        <v>6.13621329567993e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2219221647279446</v>
+        <v>0.2219221647279447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04219095408895414</v>
+        <v>0.04219095408895415</v>
       </c>
       <c r="V2" t="n">
-        <v>3.133795135691772e-06</v>
+        <v>3.133795135691774e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004002502981944428</v>
+        <v>0.0004002502981944427</v>
       </c>
       <c r="X2" t="n">
         <v>0.0147820899870638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03425699165471949</v>
+        <v>0.03425699165471956</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.9085458508562668</v>
+        <v>-0.9085458508562799</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.553175046228752</v>
+        <v>-1.553175046228753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2990643430450833</v>
+        <v>0.2990643430450845</v>
       </c>
       <c r="G3" t="n">
-        <v>2.910982836229393e-07</v>
+        <v>2.9109828362294e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.186346744262235e-06</v>
+        <v>8.186346744262181e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001148966337932856</v>
+        <v>0.0001148966337932874</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003800529191866535</v>
+        <v>0.0003800529191868178</v>
       </c>
       <c r="K3" t="n">
-        <v>2.259359825624103e-05</v>
+        <v>2.25935982562411e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.43119966464731e-06</v>
+        <v>9.431199664647729e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.496199314546062e-05</v>
+        <v>7.496199314546065e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006687890701502687</v>
+        <v>0.006687890701495143</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003372992321914142</v>
+        <v>0.003372992321914147</v>
       </c>
       <c r="P3" t="n">
-        <v>4.579048438156887e-05</v>
+        <v>4.579048438156892e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03459804462280838</v>
+        <v>0.03459804462280362</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003212237757518625</v>
+        <v>0.0003212237757524064</v>
       </c>
       <c r="S3" t="n">
-        <v>5.799016651922711e-06</v>
+        <v>5.79901665192281e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2128507111936727</v>
+        <v>0.2128507111936734</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03988270036831714</v>
+        <v>0.0398827003683172</v>
       </c>
       <c r="V3" t="n">
-        <v>3.053801267327755e-06</v>
+        <v>3.053801267327764e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003750554295336958</v>
+        <v>0.0003750554295336956</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01383729935453026</v>
+        <v>0.01383729935453028</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03297383526331501</v>
+        <v>0.03297383526331502</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9582979757847546</v>
+        <v>-0.9582979757848152</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.557577317309589</v>
+        <v>-1.557577317309591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2696976414916737</v>
+        <v>0.269697641491675</v>
       </c>
       <c r="G4" t="n">
-        <v>2.884956634223812e-07</v>
+        <v>2.884956634223841e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656977e-06</v>
+        <v>8.073491503656933e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228945</v>
+        <v>0.0001085090953228946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003790084812489929</v>
+        <v>0.0003790084812489925</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019852e-05</v>
+        <v>2.206349487019848e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445039e-05</v>
+        <v>1.152786547445036e-05</v>
       </c>
       <c r="M4" t="n">
         <v>6.340097150061023e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395111018</v>
+        <v>0.007584124395110279</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003026883518119253</v>
+        <v>0.003026883518119249</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857585e-05</v>
+        <v>3.876270632857577e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933492</v>
+        <v>0.03307471650930709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066576</v>
+        <v>0.0003016517052066572</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564692e-06</v>
+        <v>5.655265380564658e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.200052016765554</v>
+        <v>0.2000520167655538</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391239</v>
+        <v>0.03893406919391237</v>
       </c>
       <c r="V4" t="n">
-        <v>3.019154090207049e-06</v>
+        <v>3.019154090207047e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003770377104592982</v>
+        <v>0.0003770377104592978</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01385317096912716</v>
+        <v>0.01385317096912715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041887</v>
+        <v>0.03173767865041881</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,70 +2017,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9923784544816133</v>
+        <v>-0.9923784544815966</v>
       </c>
       <c r="E5" t="n">
         <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2636515802036539</v>
+        <v>0.2636515802036542</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926158018e-07</v>
+        <v>2.883344926157982e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.884156124948789e-06</v>
+        <v>7.884156124948743e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783845</v>
+        <v>0.0001024999723783831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003763639852349078</v>
+        <v>0.000376363985234907</v>
       </c>
       <c r="K5" t="n">
-        <v>1.855541770166519e-05</v>
+        <v>1.855541770166515e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.614399578552151e-05</v>
+        <v>1.614399578552149e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062409e-05</v>
+        <v>6.671436404062413e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00976047937666529</v>
+        <v>0.009760479376701811</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617872</v>
+        <v>0.002647843563617866</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278283e-05</v>
+        <v>4.081677275278286e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139064692</v>
+        <v>0.02999212139064147</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273109</v>
+        <v>0.0002773755225273106</v>
       </c>
       <c r="S5" t="n">
-        <v>5.548797294451971e-06</v>
+        <v>5.548797294451941e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070505</v>
+        <v>0.1780728838070506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03845948738098709</v>
+        <v>0.03845948738098705</v>
       </c>
       <c r="V5" t="n">
-        <v>2.860903834275751e-06</v>
+        <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003948150479346339</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01442301014128574</v>
+        <v>0.01442301014128567</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03021285433597517</v>
+        <v>0.0302128543359751</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2101,64 +2101,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.232919685067869</v>
+        <v>-1.232919685067863</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.583529197938965</v>
+        <v>-1.583529197938966</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2137819860167696</v>
+        <v>0.2137819860167682</v>
       </c>
       <c r="G6" t="n">
-        <v>2.629743532180668e-07</v>
+        <v>2.629743532180664e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.00744658362135e-06</v>
+        <v>7.007446583621313e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.994515887725199e-05</v>
+        <v>5.994515887725195e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002218360582685596</v>
+        <v>0.0002218360582685595</v>
       </c>
       <c r="K6" t="n">
-        <v>8.313474661720802e-06</v>
+        <v>8.3134746617208e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.011007074466353e-06</v>
+        <v>4.011007074466354e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.408844445253663e-05</v>
+        <v>2.408844445253659e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003413721912265724</v>
+        <v>0.003413721912279954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001235825335481854</v>
+        <v>0.001235825335481852</v>
       </c>
       <c r="P6" t="n">
-        <v>1.563588664813284e-05</v>
+        <v>1.563588664813283e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01333701183812303</v>
+        <v>0.01333701183812431</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001282976709059454</v>
       </c>
       <c r="S6" t="n">
-        <v>3.911559314590972e-06</v>
+        <v>3.911559314590979e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05547084700405661</v>
+        <v>0.05547084700405668</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02718795563138739</v>
+        <v>0.02718795563138736</v>
       </c>
       <c r="V6" t="n">
-        <v>2.350073527008297e-06</v>
+        <v>2.350073527008299e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003134989871089374</v>
+        <v>0.0003134989871089375</v>
       </c>
       <c r="X6" t="n">
         <v>0.01138229085736368</v>
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.339682788373142</v>
+        <v>-1.339682788373155</v>
       </c>
       <c r="E7" t="n">
         <v>-1.594335350441187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1716363794886081</v>
+        <v>0.1716363794886079</v>
       </c>
       <c r="G7" t="n">
-        <v>2.51933306794132e-07</v>
+        <v>2.519333067941347e-07</v>
       </c>
       <c r="H7" t="n">
         <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.057975714113774e-05</v>
+        <v>4.057975714113793e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001634258239776594</v>
+        <v>0.0001634258239776595</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180706e-06</v>
+        <v>-6.666578390180679e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.408213536697682e-06</v>
+        <v>3.408213536697687e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.576179324597284e-05</v>
+        <v>-1.576179324597281e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887755093</v>
+        <v>0.002852673887765345</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003511833579318713</v>
+        <v>0.0003511833579318724</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496392e-06</v>
+        <v>-8.306313779496396e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006949757463137796</v>
+        <v>0.006949757463129556</v>
       </c>
       <c r="R7" t="n">
-        <v>5.894403635046219e-05</v>
+        <v>5.894403635046221e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.377463070821941e-06</v>
+        <v>3.377463070821967e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01650860249098277</v>
+        <v>0.01650860249098279</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0237718999516727</v>
+        <v>0.02377189995167275</v>
       </c>
       <c r="V7" t="n">
-        <v>1.710369379189882e-06</v>
+        <v>1.710369379189883e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002970973080769404</v>
+        <v>0.0002970973080769403</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01060272397536547</v>
+        <v>0.01060272397536551</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02143450870345178</v>
+        <v>0.02143450870345177</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.371171399275056</v>
+        <v>-1.371171399275058</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.598715785791028</v>
+        <v>-1.598715785791027</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1603862493917946</v>
+        <v>0.1603862493917936</v>
       </c>
       <c r="G8" t="n">
-        <v>2.483967374914811e-07</v>
+        <v>2.483967374914805e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.617095439383984e-06</v>
+        <v>6.617095439383988e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.478206161720463e-05</v>
+        <v>3.478206161720534e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.33764537050936e-05</v>
+        <v>9.337645370510148e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.748427478810463e-06</v>
+        <v>-9.748427478810473e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.874226954002219e-06</v>
+        <v>3.874226954002223e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.27453122669307e-05</v>
+        <v>-1.274531226693063e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002941585529239589</v>
+        <v>0.00294158552923675</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0003614663475157456</v>
+        <v>0.0003614663475157467</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.613356735135387e-06</v>
+        <v>-6.613356735135324e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002643969675912246</v>
+        <v>0.002643969675922295</v>
       </c>
       <c r="R8" t="n">
-        <v>6.007275999553564e-05</v>
+        <v>6.007275999553583e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.142631698581945e-06</v>
+        <v>3.142631698581967e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007516435846575896</v>
+        <v>0.007516435846575938</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02247190753168225</v>
+        <v>0.02247190753168224</v>
       </c>
       <c r="V8" t="n">
-        <v>1.611739468424993e-06</v>
+        <v>1.611739468424995e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002936029220226869</v>
+        <v>0.0002936029220226871</v>
       </c>
       <c r="X8" t="n">
         <v>0.01042652077510718</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02032799867849813</v>
+        <v>0.02032799867849814</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2353,70 +2353,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.006670578541267</v>
+        <v>-1.006670578541273</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.561927546685941</v>
+        <v>-1.561927546685943</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2721354476889458</v>
+        <v>0.2721354476889459</v>
       </c>
       <c r="G9" t="n">
-        <v>2.832970733688222e-07</v>
+        <v>2.832970733688224e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>7.995921861823704e-06</v>
+        <v>7.995921861823706e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>9.900859556574505e-05</v>
+        <v>9.900859556574506e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003133471461989699</v>
+        <v>0.0003133471461989698</v>
       </c>
       <c r="K9" t="n">
-        <v>1.614932724148671e-05</v>
+        <v>1.614932724148667e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.136039710518895e-06</v>
+        <v>8.136039710518897e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.561153676457521e-05</v>
+        <v>4.561153676457514e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005797721084024394</v>
+        <v>0.005797721084023572</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003056558056256892</v>
+        <v>0.003056558056256895</v>
       </c>
       <c r="P9" t="n">
-        <v>2.809672123789917e-05</v>
+        <v>2.80967212378991e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02690089148043396</v>
+        <v>0.02690089148041738</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002837415493334886</v>
+        <v>0.000283741549333489</v>
       </c>
       <c r="S9" t="n">
-        <v>5.378735027035154e-06</v>
+        <v>5.378735027035132e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.165665832607281</v>
+        <v>0.1656658326072805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679014917743906</v>
+        <v>0.03679014917743899</v>
       </c>
       <c r="V9" t="n">
-        <v>2.754907142699131e-06</v>
+        <v>2.754907142699126e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003578503953903428</v>
+        <v>0.0003578503953903429</v>
       </c>
       <c r="X9" t="n">
         <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0305957347075486</v>
+        <v>0.03059573470754852</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.209163453972461</v>
+        <v>-1.209163453972458</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.578132706625494</v>
+        <v>-1.578132706625493</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2113874502663626</v>
+        <v>0.2113874502663624</v>
       </c>
       <c r="G10" t="n">
-        <v>2.677170814798685e-07</v>
+        <v>2.677170814798691e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.589085260944301e-06</v>
+        <v>7.589085260944317e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>6.335373248768603e-05</v>
+        <v>6.335373248768569e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002098588280031235</v>
+        <v>0.0002098588280031234</v>
       </c>
       <c r="K10" t="n">
-        <v>7.300184517667918e-06</v>
+        <v>7.300184517667923e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>5.698048824358937e-06</v>
+        <v>5.698048824358931e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.691806851142419e-06</v>
+        <v>-8.691806851142229e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004311694306037258</v>
+        <v>0.004311694306037253</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006193173413198168</v>
+        <v>0.0006193173413198181</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.334224229830869e-06</v>
+        <v>-4.334224229830883e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01585268796378277</v>
+        <v>0.01585268796379152</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001915181996051552</v>
+        <v>0.0001915181996051556</v>
       </c>
       <c r="S10" t="n">
-        <v>4.538711218472183e-06</v>
+        <v>4.538711218472284e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0670848689354724</v>
+        <v>0.0670848689354723</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03056298822878646</v>
+        <v>0.03056298822878649</v>
       </c>
       <c r="V10" t="n">
-        <v>2.342419147874125e-06</v>
+        <v>2.342419147874124e-06</v>
       </c>
       <c r="W10" t="n">
         <v>0.0003269952628084279</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01182402552573083</v>
+        <v>0.01182402552573087</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02651974913106421</v>
+        <v>0.02651974913106417</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2521,70 +2521,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.320902128073951</v>
+        <v>-1.320902128073866</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.590799838576672</v>
+        <v>-1.590799838576671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1837670328532788</v>
+        <v>0.183767032853279</v>
       </c>
       <c r="G11" t="n">
-        <v>2.568577064977733e-07</v>
+        <v>2.568577064977749e-07</v>
       </c>
       <c r="H11" t="n">
         <v>6.71279847143162e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.286974327631856e-05</v>
+        <v>4.286974327631901e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001449922121666099</v>
+        <v>0.0001449922121666098</v>
       </c>
       <c r="K11" t="n">
-        <v>6.25713811905575e-06</v>
+        <v>6.257138119055734e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.412994932103973e-06</v>
+        <v>6.412994932103974e-06</v>
       </c>
       <c r="M11" t="n">
         <v>-1.232690523299285e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004408068060791814</v>
+        <v>0.00440806806081179</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643884</v>
+        <v>0.0003029178157643874</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430012e-06</v>
+        <v>-6.041955578430036e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01011829992180976</v>
+        <v>0.01011829992186117</v>
       </c>
       <c r="R11" t="n">
-        <v>6.924576184647557e-05</v>
+        <v>6.924576184643173e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55086519756684e-06</v>
+        <v>3.550865197566847e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01240561713046286</v>
+        <v>0.01240561713046294</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02496506383980429</v>
+        <v>0.02496506383980432</v>
       </c>
       <c r="V11" t="n">
-        <v>2.260592111522401e-06</v>
+        <v>2.260592111522402e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003185017529477076</v>
+        <v>0.0003185017529477078</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01136342941515748</v>
+        <v>0.01136342941515753</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02198455760468075</v>
+        <v>0.0219845576046807</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.6182362284556114</v>
+        <v>-0.6182362284556128</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.547784669004612</v>
+        <v>-1.54778466900461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5647350677270536</v>
+        <v>0.5647350677270546</v>
       </c>
       <c r="G2" t="n">
-        <v>2.967052734860615e-07</v>
+        <v>2.967052734860609e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.29777497371651e-06</v>
+        <v>8.297774973716524e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00012148093336588</v>
+        <v>0.0001214809333658804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004136876998668455</v>
+        <v>0.0004136876998668463</v>
       </c>
       <c r="K2" t="n">
-        <v>2.36171297709628e-05</v>
+        <v>2.361712977096283e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.265140367188762e-05</v>
+        <v>1.265140367188765e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.650721919925382e-05</v>
+        <v>8.650721919925389e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008394229475622506</v>
+        <v>0.008394229475619176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003617560147030653</v>
+        <v>0.00361756014703065</v>
       </c>
       <c r="P2" t="n">
-        <v>5.276176111896948e-05</v>
+        <v>5.27617611189695e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03818848892144527</v>
+        <v>0.03818848892145319</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003320302303811611</v>
+        <v>0.0003320302303811615</v>
       </c>
       <c r="S2" t="n">
-        <v>6.136213295679914e-06</v>
+        <v>6.13621329567993e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2219221647279446</v>
+        <v>0.2219221647279447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04219095408895414</v>
+        <v>0.04219095408895415</v>
       </c>
       <c r="V2" t="n">
-        <v>3.133795135691772e-06</v>
+        <v>3.133795135691774e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004002502981944428</v>
+        <v>0.0004002502981944427</v>
       </c>
       <c r="X2" t="n">
         <v>0.0147820899870638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03425699165471949</v>
+        <v>0.03425699165471956</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2830,70 +2830,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.740660942280473</v>
+        <v>-0.7406609422805035</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.553175046228752</v>
+        <v>-1.553175046228753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4669492516850288</v>
+        <v>0.4669492516850298</v>
       </c>
       <c r="G3" t="n">
-        <v>2.910982836229393e-07</v>
+        <v>2.9109828362294e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.186346744262235e-06</v>
+        <v>8.186346744262181e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001148966337932856</v>
+        <v>0.0001148966337932874</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003800529191866535</v>
+        <v>0.0003800529191868178</v>
       </c>
       <c r="K3" t="n">
-        <v>2.259359825624103e-05</v>
+        <v>2.25935982562411e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.43119966464731e-06</v>
+        <v>9.431199664647729e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.496199314546062e-05</v>
+        <v>7.496199314546065e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006687890701502687</v>
+        <v>0.006687890701495143</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003372992321914142</v>
+        <v>0.003372992321914147</v>
       </c>
       <c r="P3" t="n">
-        <v>4.579048438156887e-05</v>
+        <v>4.579048438156892e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03459804462280838</v>
+        <v>0.03459804462280362</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003212237757518625</v>
+        <v>0.0003212237757524064</v>
       </c>
       <c r="S3" t="n">
-        <v>5.799016651922711e-06</v>
+        <v>5.79901665192281e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2128507111936727</v>
+        <v>0.2128507111936734</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03988270036831714</v>
+        <v>0.0398827003683172</v>
       </c>
       <c r="V3" t="n">
-        <v>3.053801267327755e-06</v>
+        <v>3.053801267327764e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003750554295336958</v>
+        <v>0.0003750554295336956</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01383729935453026</v>
+        <v>0.01383729935453028</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03297383526331501</v>
+        <v>0.03297383526331502</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.8220554352904254</v>
+        <v>-0.8220554352904583</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.557577317309589</v>
+        <v>-1.557577317309591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4059401820380397</v>
+        <v>0.4059401820380395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.884956634223812e-07</v>
+        <v>2.884956634223841e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656977e-06</v>
+        <v>8.073491503656933e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228945</v>
+        <v>0.0001085090953228946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003790084812489929</v>
+        <v>0.0003790084812489925</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019852e-05</v>
+        <v>2.206349487019848e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445039e-05</v>
+        <v>1.152786547445036e-05</v>
       </c>
       <c r="M4" t="n">
         <v>6.340097150061023e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395111018</v>
+        <v>0.007584124395110279</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003026883518119253</v>
+        <v>0.003026883518119249</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857585e-05</v>
+        <v>3.876270632857577e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933492</v>
+        <v>0.03307471650930709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066576</v>
+        <v>0.0003016517052066572</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564692e-06</v>
+        <v>5.655265380564658e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.200052016765554</v>
+        <v>0.2000520167655538</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391239</v>
+        <v>0.03893406919391237</v>
       </c>
       <c r="V4" t="n">
-        <v>3.019154090207049e-06</v>
+        <v>3.019154090207047e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003770377104592982</v>
+        <v>0.0003770377104592978</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01385317096912716</v>
+        <v>0.01385317096912715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041887</v>
+        <v>0.03173767865041881</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,70 +2998,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8754081291484425</v>
+        <v>-0.8754081291484531</v>
       </c>
       <c r="E5" t="n">
         <v>-1.560908622433099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3806219055814968</v>
+        <v>0.3806219055814963</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926158018e-07</v>
+        <v>2.883344926157982e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.884156124948789e-06</v>
+        <v>7.884156124948743e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783845</v>
+        <v>0.0001024999723783831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003763639852349078</v>
+        <v>0.000376363985234907</v>
       </c>
       <c r="K5" t="n">
-        <v>1.855541770166519e-05</v>
+        <v>1.855541770166515e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.614399578552151e-05</v>
+        <v>1.614399578552149e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062409e-05</v>
+        <v>6.671436404062413e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00976047937666529</v>
+        <v>0.009760479376701811</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617872</v>
+        <v>0.002647843563617866</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278283e-05</v>
+        <v>4.081677275278286e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139064692</v>
+        <v>0.02999212139064147</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273109</v>
+        <v>0.0002773755225273106</v>
       </c>
       <c r="S5" t="n">
-        <v>5.548797294451971e-06</v>
+        <v>5.548797294451941e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070505</v>
+        <v>0.1780728838070506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03845948738098709</v>
+        <v>0.03845948738098705</v>
       </c>
       <c r="V5" t="n">
-        <v>2.860903834275751e-06</v>
+        <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
         <v>0.0003948150479346339</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01442301014128574</v>
+        <v>0.01442301014128567</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03021285433597517</v>
+        <v>0.0302128543359751</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3082,64 +3082,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.127739769395991</v>
+        <v>-1.127739769395985</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.583529197938965</v>
+        <v>-1.583529197938966</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3189619017288311</v>
+        <v>0.31896190172883</v>
       </c>
       <c r="G6" t="n">
-        <v>2.629743532180668e-07</v>
+        <v>2.629743532180664e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.00744658362135e-06</v>
+        <v>7.007446583621313e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.994515887725199e-05</v>
+        <v>5.994515887725195e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002218360582685596</v>
+        <v>0.0002218360582685595</v>
       </c>
       <c r="K6" t="n">
-        <v>8.313474661720802e-06</v>
+        <v>8.3134746617208e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.011007074466353e-06</v>
+        <v>4.011007074466354e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.408844445253663e-05</v>
+        <v>2.408844445253659e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003413721912265724</v>
+        <v>0.003413721912279954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001235825335481854</v>
+        <v>0.001235825335481852</v>
       </c>
       <c r="P6" t="n">
-        <v>1.563588664813284e-05</v>
+        <v>1.563588664813283e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01333701183812303</v>
+        <v>0.01333701183812431</v>
       </c>
       <c r="R6" t="n">
         <v>0.0001282976709059454</v>
       </c>
       <c r="S6" t="n">
-        <v>3.911559314590972e-06</v>
+        <v>3.911559314590979e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05547084700405661</v>
+        <v>0.05547084700405668</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02718795563138739</v>
+        <v>0.02718795563138736</v>
       </c>
       <c r="V6" t="n">
-        <v>2.350073527008297e-06</v>
+        <v>2.350073527008299e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003134989871089374</v>
+        <v>0.0003134989871089375</v>
       </c>
       <c r="X6" t="n">
         <v>0.01138229085736368</v>
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.256227195365545</v>
+        <v>-1.256227195365537</v>
       </c>
       <c r="E7" t="n">
         <v>-1.594335350441187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2550919725281227</v>
+        <v>0.2550919725281218</v>
       </c>
       <c r="G7" t="n">
-        <v>2.51933306794132e-07</v>
+        <v>2.519333067941347e-07</v>
       </c>
       <c r="H7" t="n">
         <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.057975714113774e-05</v>
+        <v>4.057975714113793e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001634258239776594</v>
+        <v>0.0001634258239776595</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180706e-06</v>
+        <v>-6.666578390180679e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.408213536697682e-06</v>
+        <v>3.408213536697687e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.576179324597284e-05</v>
+        <v>-1.576179324597281e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887755093</v>
+        <v>0.002852673887765345</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003511833579318713</v>
+        <v>0.0003511833579318724</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496392e-06</v>
+        <v>-8.306313779496396e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006949757463137796</v>
+        <v>0.006949757463129556</v>
       </c>
       <c r="R7" t="n">
-        <v>5.894403635046219e-05</v>
+        <v>5.894403635046221e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.377463070821941e-06</v>
+        <v>3.377463070821967e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01650860249098277</v>
+        <v>0.01650860249098279</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0237718999516727</v>
+        <v>0.02377189995167275</v>
       </c>
       <c r="V7" t="n">
-        <v>1.710369379189882e-06</v>
+        <v>1.710369379189883e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002970973080769404</v>
+        <v>0.0002970973080769403</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01060272397536547</v>
+        <v>0.01060272397536551</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02143450870345178</v>
+        <v>0.02143450870345177</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.298423749374308</v>
+        <v>-1.298423749374298</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.598715785791028</v>
+        <v>-1.598715785791027</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2331338993203419</v>
+        <v>0.2331338993203413</v>
       </c>
       <c r="G8" t="n">
-        <v>2.483967374914811e-07</v>
+        <v>2.483967374914805e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.617095439383984e-06</v>
+        <v>6.617095439383988e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.478206161720463e-05</v>
+        <v>3.478206161720534e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.33764537050936e-05</v>
+        <v>9.337645370510148e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.748427478810463e-06</v>
+        <v>-9.748427478810473e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.874226954002219e-06</v>
+        <v>3.874226954002223e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.27453122669307e-05</v>
+        <v>-1.274531226693063e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002941585529239589</v>
+        <v>0.00294158552923675</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0003614663475157456</v>
+        <v>0.0003614663475157467</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.613356735135387e-06</v>
+        <v>-6.613356735135324e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002643969675912246</v>
+        <v>0.002643969675922295</v>
       </c>
       <c r="R8" t="n">
-        <v>6.007275999553564e-05</v>
+        <v>6.007275999553583e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.142631698581945e-06</v>
+        <v>3.142631698581967e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007516435846575896</v>
+        <v>0.007516435846575938</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02247190753168225</v>
+        <v>0.02247190753168224</v>
       </c>
       <c r="V8" t="n">
-        <v>1.611739468424993e-06</v>
+        <v>1.611739468424995e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002936029220226869</v>
+        <v>0.0002936029220226871</v>
       </c>
       <c r="X8" t="n">
         <v>0.01042652077510718</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02032799867849813</v>
+        <v>0.02032799867849814</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3334,70 +3334,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8456452961338262</v>
+        <v>-0.8456452961338092</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.561927546685941</v>
+        <v>-1.561927546685943</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4331607301579157</v>
+        <v>0.4331607301579159</v>
       </c>
       <c r="G9" t="n">
-        <v>2.832970733688222e-07</v>
+        <v>2.832970733688224e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>7.995921861823704e-06</v>
+        <v>7.995921861823706e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>9.900859556574505e-05</v>
+        <v>9.900859556574506e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003133471461989699</v>
+        <v>0.0003133471461989698</v>
       </c>
       <c r="K9" t="n">
-        <v>1.614932724148671e-05</v>
+        <v>1.614932724148667e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.136039710518895e-06</v>
+        <v>8.136039710518897e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.561153676457521e-05</v>
+        <v>4.561153676457514e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005797721084024394</v>
+        <v>0.005797721084023572</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003056558056256892</v>
+        <v>0.003056558056256895</v>
       </c>
       <c r="P9" t="n">
-        <v>2.809672123789917e-05</v>
+        <v>2.80967212378991e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02690089148043396</v>
+        <v>0.02690089148041738</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002837415493334886</v>
+        <v>0.000283741549333489</v>
       </c>
       <c r="S9" t="n">
-        <v>5.378735027035154e-06</v>
+        <v>5.378735027035132e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.165665832607281</v>
+        <v>0.1656658326072805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679014917743906</v>
+        <v>0.03679014917743899</v>
       </c>
       <c r="V9" t="n">
-        <v>2.754907142699131e-06</v>
+        <v>2.754907142699126e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003578503953903428</v>
+        <v>0.0003578503953903429</v>
       </c>
       <c r="X9" t="n">
         <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0305957347075486</v>
+        <v>0.03059573470754852</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.089846263233557</v>
+        <v>-1.089846263233528</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.578132706625494</v>
+        <v>-1.578132706625493</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3307046410508491</v>
+        <v>0.3307046410508493</v>
       </c>
       <c r="G10" t="n">
-        <v>2.677170814798685e-07</v>
+        <v>2.677170814798691e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.589085260944301e-06</v>
+        <v>7.589085260944317e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>6.335373248768603e-05</v>
+        <v>6.335373248768569e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002098588280031235</v>
+        <v>0.0002098588280031234</v>
       </c>
       <c r="K10" t="n">
-        <v>7.300184517667918e-06</v>
+        <v>7.300184517667923e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>5.698048824358937e-06</v>
+        <v>5.698048824358931e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.691806851142419e-06</v>
+        <v>-8.691806851142229e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004311694306037258</v>
+        <v>0.004311694306037253</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006193173413198168</v>
+        <v>0.0006193173413198181</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.334224229830869e-06</v>
+        <v>-4.334224229830883e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01585268796378277</v>
+        <v>0.01585268796379152</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001915181996051552</v>
+        <v>0.0001915181996051556</v>
       </c>
       <c r="S10" t="n">
-        <v>4.538711218472183e-06</v>
+        <v>4.538711218472284e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0670848689354724</v>
+        <v>0.0670848689354723</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03056298822878646</v>
+        <v>0.03056298822878649</v>
       </c>
       <c r="V10" t="n">
-        <v>2.342419147874125e-06</v>
+        <v>2.342419147874124e-06</v>
       </c>
       <c r="W10" t="n">
         <v>0.0003269952628084279</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01182402552573083</v>
+        <v>0.01182402552573087</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02651974913106421</v>
+        <v>0.02651974913106417</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.247518287573014</v>
+        <v>-1.247518287572999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.590799838576672</v>
+        <v>-1.590799838576671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2571508733822176</v>
+        <v>0.2571508733822178</v>
       </c>
       <c r="G11" t="n">
-        <v>2.568577064977733e-07</v>
+        <v>2.568577064977749e-07</v>
       </c>
       <c r="H11" t="n">
         <v>6.71279847143162e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.286974327631856e-05</v>
+        <v>4.286974327631901e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001449922121666099</v>
+        <v>0.0001449922121666098</v>
       </c>
       <c r="K11" t="n">
-        <v>6.25713811905575e-06</v>
+        <v>6.257138119055734e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.412994932103973e-06</v>
+        <v>6.412994932103974e-06</v>
       </c>
       <c r="M11" t="n">
         <v>-1.232690523299285e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004408068060791814</v>
+        <v>0.00440806806081179</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643884</v>
+        <v>0.0003029178157643874</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430012e-06</v>
+        <v>-6.041955578430036e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01011829992180976</v>
+        <v>0.01011829992186117</v>
       </c>
       <c r="R11" t="n">
-        <v>6.924576184647557e-05</v>
+        <v>6.924576184643173e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55086519756684e-06</v>
+        <v>3.550865197566847e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01240561713046286</v>
+        <v>0.01240561713046294</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02496506383980429</v>
+        <v>0.02496506383980432</v>
       </c>
       <c r="V11" t="n">
-        <v>2.260592111522401e-06</v>
+        <v>2.260592111522402e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003185017529477076</v>
+        <v>0.0003185017529477078</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01136342941515748</v>
+        <v>0.01136342941515753</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02198455760468075</v>
+        <v>0.0219845576046807</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7601163848026873</v>
+        <v>0.7601163848026871</v>
       </c>
       <c r="E2" t="n">
         <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4920544887818215</v>
+        <v>0.4920544887818212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05008330144474997</v>
+        <v>0.05008330144474999</v>
       </c>
       <c r="H2" t="n">
-        <v>7.949768237084982e-05</v>
+        <v>7.949768237084969e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001613694320761284</v>
+        <v>0.0001613694320761282</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005172860397592418</v>
+        <v>0.0005172860397592425</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004097945187585435</v>
+        <v>0.0004097945187585431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004302669151790966</v>
+        <v>0.000430266915178355</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003579362092265937</v>
+        <v>0.000357936209226593</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001368727882702079</v>
+        <v>0.001368727882702077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599605561259</v>
+        <v>0.02910599605561326</v>
       </c>
     </row>
     <row r="3">
@@ -569,37 +569,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7548790495114227</v>
+        <v>0.7548790495114225</v>
       </c>
       <c r="E3" t="n">
         <v>0.1838291906059024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4905789875069383</v>
+        <v>0.4905789875069382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04821494231345642</v>
+        <v>0.04821494231345644</v>
       </c>
       <c r="H3" t="n">
-        <v>7.022525470537632e-05</v>
+        <v>7.022525470537653e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001518113141943992</v>
+        <v>0.0001518113141943991</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004892489959522368</v>
+        <v>0.0004892489959522384</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003992444231396447</v>
+        <v>0.0003992444231396446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000408196340549645</v>
+        <v>0.000408196340549481</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003511156023621059</v>
+        <v>0.0003511156023621053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00128009114636209</v>
+        <v>0.001280091146362091</v>
       </c>
       <c r="O3" t="n">
         <v>0.02910599600786012</v>
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7499402999043678</v>
+        <v>0.7499402999043685</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1826388398155668</v>
+        <v>0.1826388398155669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.489507344143735</v>
+        <v>0.4895073441437353</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261105</v>
+        <v>0.04572335899261109</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382357e-05</v>
+        <v>6.771938650382361e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001443883674887858</v>
+        <v>0.000144388367488786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773626</v>
+        <v>0.0004620497936773604</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694055</v>
+        <v>0.0003863222939694058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985250567</v>
+        <v>0.0003961016985248413</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270794</v>
+        <v>0.0003437323729270795</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906749</v>
+        <v>0.00116444707890675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0291059959604566</v>
+        <v>0.02910599596045726</v>
       </c>
     </row>
     <row r="5">
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7434813395247818</v>
+        <v>0.7434813395247803</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1818503269076334</v>
+        <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4880694926684758</v>
+        <v>0.4880694926684757</v>
       </c>
       <c r="G5" t="n">
         <v>0.0416185757057598</v>
       </c>
       <c r="H5" t="n">
-        <v>7.200207142972961e-05</v>
+        <v>7.200207142972947e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518197</v>
+        <v>0.0001351017835518196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144934</v>
+        <v>0.0004364619477144914</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003789261076842334</v>
+        <v>0.0003789261076842336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242093547</v>
+        <v>0.0003784082242100212</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061804</v>
+        <v>0.0003359067485061806</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635163</v>
+        <v>0.001100141444635164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0291059959151817</v>
+        <v>0.02910599591517982</v>
       </c>
     </row>
     <row r="6">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6988591235739661</v>
+        <v>0.6988591235739657</v>
       </c>
       <c r="E6" t="n">
         <v>0.173434118133929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4810703906623334</v>
+        <v>0.4810703906623336</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01323200409367945</v>
+        <v>0.01323200409367942</v>
       </c>
       <c r="H6" t="n">
-        <v>3.157387977904105e-05</v>
+        <v>3.157387977904112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.79656152597503e-05</v>
+        <v>7.796561525975031e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002552564668313772</v>
+        <v>0.0002552564668313761</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003306029768954348</v>
+        <v>0.000330602976895435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002533766491997862</v>
+        <v>0.0002533766492000687</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002985136660364794</v>
+        <v>0.0002985136660364799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007693260029412949</v>
+        <v>0.0007693260029412944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599542708103</v>
+        <v>0.02910599542708026</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6820804847150552</v>
+        <v>0.6820804847150551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1692967986780908</v>
+        <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4780951759294799</v>
+        <v>0.4780951759294801</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00400559263353072</v>
+        <v>0.004005592633530714</v>
       </c>
       <c r="H7" t="n">
-        <v>1.236515770175322e-05</v>
+        <v>1.236515770175327e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7606240727101e-05</v>
+        <v>5.76062407271009e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001727953620730636</v>
+        <v>0.0001727953620730638</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000297730948870685</v>
+        <v>0.0002977309488706835</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002149280445550663</v>
+        <v>0.0002149280445553215</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000281898882397243</v>
+        <v>0.0002818988823972429</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005395976008691142</v>
+        <v>0.0005395976008691132</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599523675983</v>
+        <v>0.02910599523675927</v>
       </c>
     </row>
     <row r="8">
@@ -824,37 +824,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6763900264371993</v>
+        <v>0.676390026437199</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1677644037114067</v>
+        <v>0.1677644037114066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4765831941256122</v>
+        <v>0.4765831941256121</v>
       </c>
       <c r="G8" t="n">
         <v>0.001516222820624147</v>
       </c>
       <c r="H8" t="n">
-        <v>7.165124903845325e-06</v>
+        <v>7.165124903845186e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.043924548616539e-05</v>
+        <v>5.043924548616535e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000148107809267782</v>
+        <v>0.0001481078092677822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002870625570381508</v>
+        <v>0.0002870625570381509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001977439027295459</v>
+        <v>0.0001977439027294427</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002749288836533895</v>
+        <v>0.0002749288836533894</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004547630681316624</v>
+        <v>0.0004547630681316607</v>
       </c>
       <c r="O8" t="n">
         <v>0.02910599518834578</v>
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7396161025400672</v>
+        <v>0.739616102540069</v>
       </c>
       <c r="E9" t="n">
         <v>0.1807834979870836</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4877996382630235</v>
+        <v>0.4877996382630264</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03912270071841051</v>
+        <v>0.03912270071841054</v>
       </c>
       <c r="H9" t="n">
-        <v>5.501380903549852e-05</v>
+        <v>5.501380903549865e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001323452292307473</v>
+        <v>0.0001323452292307474</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004215950839633016</v>
+        <v>0.0004215950839633047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000375359220089662</v>
+        <v>0.0003753592200896626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003729347603890509</v>
+        <v>0.0003729347603890821</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003410339496637566</v>
+        <v>0.0003410339496637572</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001105987666444343</v>
+        <v>0.001105987666444344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599585273321</v>
+        <v>0.0291059958527321</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7057775706302638</v>
+        <v>0.7057775706302636</v>
       </c>
       <c r="E10" t="n">
         <v>0.1746507049116372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.483175739781321</v>
+        <v>0.4831757397813209</v>
       </c>
       <c r="G10" t="n">
         <v>0.01671526278688338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.146291041691863e-05</v>
+        <v>3.146291041691857e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>9.407396674874706e-05</v>
+        <v>9.407396674874713e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002697707407615786</v>
+        <v>0.0002697707407615774</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003358907712656632</v>
+        <v>0.0003358907712656621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003082578701388864</v>
+        <v>0.0003082578701390406</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003188749954166411</v>
+        <v>0.0003188749954166409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007715364328737183</v>
+        <v>0.0007715364328737178</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599546280002</v>
+        <v>0.02910599546279979</v>
       </c>
     </row>
     <row r="11">
@@ -977,40 +977,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6834152438511426</v>
+        <v>0.6834152438511435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1705839027608458</v>
+        <v>0.170583902760846</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4791557473132455</v>
+        <v>0.4791557473132457</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002880084518684511</v>
+        <v>0.002880084518684512</v>
       </c>
       <c r="H11" t="n">
-        <v>2.810574286629264e-05</v>
+        <v>2.810574286629265e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.853933714735997e-05</v>
+        <v>5.853933714735995e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001825465042988449</v>
+        <v>0.0001825465042988454</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003112785164106758</v>
+        <v>0.0003112785164106749</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002227612681621022</v>
+        <v>0.00022276126816172</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002836507017147809</v>
+        <v>0.0002836507017147812</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0006026319471648402</v>
+        <v>0.0006026319471648396</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910599524060198</v>
+        <v>0.02910599524060298</v>
       </c>
     </row>
   </sheetData>
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5106885713704719</v>
+        <v>0.4522675830125251</v>
       </c>
       <c r="E2" t="n">
         <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2426266691710881</v>
+        <v>0.1842056793660092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05008330144474997</v>
+        <v>0.05008330144474999</v>
       </c>
       <c r="H2" t="n">
-        <v>7.949768237084982e-05</v>
+        <v>7.949768237084969e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001613694320761284</v>
+        <v>0.0001613694320761282</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005172860397592418</v>
+        <v>0.0005172860397592425</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004097945187585435</v>
+        <v>0.0004097945187585431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004302669151790966</v>
+        <v>0.000430266915178355</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003579362092265937</v>
+        <v>0.000357936209226593</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001368727882702079</v>
+        <v>0.001368727882702077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600223413062</v>
+        <v>0.02910600368126354</v>
       </c>
     </row>
     <row r="3">
@@ -1165,40 +1165,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5017737729305397</v>
+        <v>0.4453357313820738</v>
       </c>
       <c r="E3" t="n">
         <v>0.1838291906059024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2374737046564442</v>
+        <v>0.1810356617099658</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04821494231345642</v>
+        <v>0.04821494231345644</v>
       </c>
       <c r="H3" t="n">
-        <v>7.022525470537632e-05</v>
+        <v>7.022525470537653e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001518113141943992</v>
+        <v>0.0001518113141943991</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004892489959522368</v>
+        <v>0.0004892489959522384</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003992444231396447</v>
+        <v>0.0003992444231396446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000408196340549645</v>
+        <v>0.000408196340549481</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003511156023621059</v>
+        <v>0.0003511156023621053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00128009114636209</v>
+        <v>0.001280091146362091</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600227747112</v>
+        <v>0.02910600367548388</v>
       </c>
     </row>
     <row r="4">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4917822821102977</v>
+        <v>0.4378556903599112</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1826388398155668</v>
+        <v>0.1826388398155669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2313493199548942</v>
+        <v>0.1774227268687051</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04572335899261105</v>
+        <v>0.04572335899261109</v>
       </c>
       <c r="H4" t="n">
-        <v>6.771938650382357e-05</v>
+        <v>6.771938650382361e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001443883674887858</v>
+        <v>0.000144388367488786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0004620497936773626</v>
+        <v>0.0004620497936773604</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003863222939694055</v>
+        <v>0.0003863222939694058</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003961016985250567</v>
+        <v>0.0003961016985248413</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003437323729270794</v>
+        <v>0.0003437323729270795</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001164447078906749</v>
+        <v>0.00116444707890675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600235522737</v>
+        <v>0.02910600369103017</v>
       </c>
     </row>
     <row r="5">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4775983772238821</v>
+        <v>0.4276574441081791</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1818503269076334</v>
+        <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.222186523781453</v>
+        <v>0.1722455894286758</v>
       </c>
       <c r="G5" t="n">
         <v>0.0416185757057598</v>
       </c>
       <c r="H5" t="n">
-        <v>7.200207142972961e-05</v>
+        <v>7.200207142972947e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001351017835518197</v>
+        <v>0.0001351017835518196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004364619477144934</v>
+        <v>0.0004364619477144914</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003789261076842334</v>
+        <v>0.0003789261076842336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003784082242093547</v>
+        <v>0.0003784082242100212</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003359067485061804</v>
+        <v>0.0003359067485061806</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001100141444635163</v>
+        <v>0.001100141444635164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600250130485</v>
+        <v>0.02910600373837857</v>
       </c>
     </row>
     <row r="6">
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.375884182605738</v>
+        <v>0.359353014398837</v>
       </c>
       <c r="E6" t="n">
         <v>0.173434118133929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.158095441693772</v>
+        <v>0.141564273077381</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01323200409367945</v>
+        <v>0.01323200409367942</v>
       </c>
       <c r="H6" t="n">
-        <v>3.157387977904105e-05</v>
+        <v>3.157387977904112e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.79656152597503e-05</v>
+        <v>7.796561525975031e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002552564668313772</v>
+        <v>0.0002552564668313761</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003306029768954348</v>
+        <v>0.000330602976895435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002533766491997862</v>
+        <v>0.0002533766492000687</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002985136660364794</v>
+        <v>0.0002985136660364799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007693260029412949</v>
+        <v>0.0007693260029412944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600342741437</v>
+        <v>0.02910600383690415</v>
       </c>
     </row>
     <row r="7">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3399397073414047</v>
+        <v>0.3344335188953276</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1692967986780908</v>
+        <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1359543900807421</v>
+        <v>0.1304482014982728</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00400559263353072</v>
+        <v>0.004005592633530714</v>
       </c>
       <c r="H7" t="n">
-        <v>1.236515770175322e-05</v>
+        <v>1.236515770175327e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7606240727101e-05</v>
+        <v>5.76062407271009e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001727953620730636</v>
+        <v>0.0001727953620730638</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000297730948870685</v>
+        <v>0.0002977309488706835</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002149280445550663</v>
+        <v>0.0002149280445553215</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000281898882397243</v>
+        <v>0.0002818988823972429</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005395976008691142</v>
+        <v>0.0005395976008691132</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600371184691</v>
+        <v>0.02910600384823903</v>
       </c>
     </row>
     <row r="8">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3293165674569223</v>
+        <v>0.3270171721505907</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1677644037114067</v>
+        <v>0.1677644037114066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1295097265480612</v>
+        <v>0.1272103311847718</v>
       </c>
       <c r="G8" t="n">
         <v>0.001516222820624147</v>
       </c>
       <c r="H8" t="n">
-        <v>7.165124903845325e-06</v>
+        <v>7.165124903845186e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.043924548616539e-05</v>
+        <v>5.043924548616535e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000148107809267782</v>
+        <v>0.0001481078092677822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002870625570381508</v>
+        <v>0.0002870625570381509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001977439027295459</v>
+        <v>0.0001977439027294427</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002749288836533895</v>
+        <v>0.0002749288836533894</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004547630681316624</v>
+        <v>0.0004547630681316607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600378561978</v>
+        <v>0.02910600384257772</v>
       </c>
     </row>
     <row r="9">
@@ -1471,40 +1471,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4679799839006546</v>
+        <v>0.420824715022991</v>
       </c>
       <c r="E9" t="n">
         <v>0.1807834979870836</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2161635128949772</v>
+        <v>0.1690082428492414</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03912270071841051</v>
+        <v>0.03912270071841054</v>
       </c>
       <c r="H9" t="n">
-        <v>5.501380903549852e-05</v>
+        <v>5.501380903549865e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001323452292307473</v>
+        <v>0.0001323452292307474</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004215950839633016</v>
+        <v>0.0004215950839633047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000375359220089662</v>
+        <v>0.0003753592200896626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003729347603890509</v>
+        <v>0.0003729347603890821</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003410339496637566</v>
+        <v>0.0003410339496637572</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001105987666444343</v>
+        <v>0.001105987666444344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600258136686</v>
+        <v>0.029106003749439</v>
       </c>
     </row>
     <row r="10">
@@ -1522,40 +1522,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3881762173596853</v>
+        <v>0.3670682053263773</v>
       </c>
       <c r="E10" t="n">
         <v>0.1746507049116372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1655743786435144</v>
+        <v>0.1444663660873451</v>
       </c>
       <c r="G10" t="n">
         <v>0.01671526278688338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.146291041691863e-05</v>
+        <v>3.146291041691857e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>9.407396674874706e-05</v>
+        <v>9.407396674874713e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002697707407615786</v>
+        <v>0.0002697707407615774</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003358907712656632</v>
+        <v>0.0003358907712656621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003082578701388864</v>
+        <v>0.0003082578701390406</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003188749954166411</v>
+        <v>0.0003188749954166409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007715364328737183</v>
+        <v>0.0007715364328737178</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600333002805</v>
+        <v>0.02910600385288925</v>
       </c>
     </row>
     <row r="11">
@@ -1573,40 +1573,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3393895491525614</v>
+        <v>0.3353323123361699</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1705839027608458</v>
+        <v>0.170583902760846</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1351300440928854</v>
+        <v>0.1310728071759925</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002880084518684511</v>
+        <v>0.002880084518684512</v>
       </c>
       <c r="H11" t="n">
-        <v>2.810574286629264e-05</v>
+        <v>2.810574286629265e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.853933714735997e-05</v>
+        <v>5.853933714735995e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001825465042988449</v>
+        <v>0.0001825465042988454</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0003112785164106758</v>
+        <v>0.0003112785164106749</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002227612681621022</v>
+        <v>0.00022276126816172</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002836507017147809</v>
+        <v>0.0002836507017147812</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0006026319471648402</v>
+        <v>0.0006026319471648396</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600376238065</v>
+        <v>0.02910600386288237</v>
       </c>
     </row>
   </sheetData>
@@ -1765,70 +1765,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.8495586183774674</v>
+        <v>-0.8495586183774479</v>
       </c>
       <c r="E2" t="n">
         <v>-1.54778466900461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3334126777168162</v>
+        <v>0.3334126777168158</v>
       </c>
       <c r="G2" t="n">
-        <v>2.967052734860608e-07</v>
+        <v>2.967052734860602e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.297774973716502e-06</v>
+        <v>8.29777497371649e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001214809333658798</v>
+        <v>0.0001214809333658801</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004136876998668466</v>
+        <v>0.0004136876998668453</v>
       </c>
       <c r="K2" t="n">
-        <v>2.361712977096279e-05</v>
+        <v>2.361712977096276e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26514036718877e-05</v>
+        <v>1.265140367188762e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.650721919925383e-05</v>
+        <v>8.650721919925378e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008394229475619176</v>
+        <v>0.008394229475619169</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003617560147030654</v>
+        <v>0.003617560147030652</v>
       </c>
       <c r="P2" t="n">
-        <v>5.27617611189695e-05</v>
+        <v>5.276176111896946e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03818848892145318</v>
+        <v>0.03818848892146336</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003320302303811617</v>
+        <v>0.0003320302303811612</v>
       </c>
       <c r="S2" t="n">
-        <v>6.13621329567992e-06</v>
+        <v>6.136213295679849e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2219221647279447</v>
+        <v>0.2219221647279445</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04219095408895416</v>
+        <v>0.04219095408895408</v>
       </c>
       <c r="V2" t="n">
-        <v>3.133795135691773e-06</v>
+        <v>3.133795135691774e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004002502981944433</v>
+        <v>0.0004002502981944427</v>
       </c>
       <c r="X2" t="n">
         <v>0.01478208998706381</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0342569916547195</v>
+        <v>0.03425699165471942</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.9085458508562688</v>
+        <v>-0.9085458508563298</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.553175046228751</v>
+        <v>-1.553175046228754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2990643430450838</v>
+        <v>0.2990643430450837</v>
       </c>
       <c r="G3" t="n">
         <v>2.910982836229399e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.186346744262173e-06</v>
+        <v>8.186346744262183e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001148966337932861</v>
+        <v>0.0001148966337932871</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000380052919186653</v>
+        <v>0.0003800529191865597</v>
       </c>
       <c r="K3" t="n">
-        <v>2.259359825624112e-05</v>
+        <v>2.259359825624122e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.431199664648945e-06</v>
+        <v>9.431199664647312e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.496199314546065e-05</v>
+        <v>7.49619931454608e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006687890701509549</v>
+        <v>0.006687890701524929</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003372992321914139</v>
+        <v>0.003372992321914145</v>
       </c>
       <c r="P3" t="n">
-        <v>4.579048438156879e-05</v>
+        <v>4.579048438156895e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03459804462280596</v>
+        <v>0.03459804462276512</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003212237757524057</v>
+        <v>0.0003212237757524068</v>
       </c>
       <c r="S3" t="n">
-        <v>5.799016651922794e-06</v>
+        <v>5.799016651922795e-06</v>
       </c>
       <c r="T3" t="n">
         <v>0.2128507111936728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03988270036831717</v>
+        <v>0.0398827003683172</v>
       </c>
       <c r="V3" t="n">
-        <v>3.053801267327759e-06</v>
+        <v>3.053801267327763e-06</v>
       </c>
       <c r="W3" t="n">
         <v>0.0003750554295336959</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01383729935453029</v>
+        <v>0.01383729935453028</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03297383526331506</v>
+        <v>0.03297383526331497</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1933,70 +1933,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9582979757847576</v>
+        <v>-0.9582979757847434</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.55757731730959</v>
+        <v>-1.557577317309588</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2696976414916735</v>
+        <v>0.2696976414916739</v>
       </c>
       <c r="G4" t="n">
-        <v>2.884956634223838e-07</v>
+        <v>2.884956634223842e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656926e-06</v>
+        <v>8.073491503656966e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228941</v>
+        <v>0.000108509095322894</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000379008481248993</v>
+        <v>0.0003790084812489932</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019851e-05</v>
+        <v>2.20634948701985e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445034e-05</v>
+        <v>1.152786547445037e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.340097150061019e-05</v>
+        <v>6.34009715006103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395116972</v>
+        <v>0.007584124395116763</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003026883518119257</v>
+        <v>0.003026883518119254</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857587e-05</v>
+        <v>3.876270632857589e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933395</v>
+        <v>0.03307471650934212</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066227</v>
+        <v>0.0003016517052066577</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564697e-06</v>
+        <v>5.655265380564699e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2000520167655541</v>
+        <v>0.2000520167655542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391235</v>
+        <v>0.03893406919391237</v>
       </c>
       <c r="V4" t="n">
-        <v>3.019154090207048e-06</v>
+        <v>3.019154090207047e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003770377104592977</v>
+        <v>0.000377037710459298</v>
       </c>
       <c r="X4" t="n">
         <v>0.01385317096912711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041881</v>
+        <v>0.0317376786504189</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2017,70 +2017,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9923784544815973</v>
+        <v>-0.9923784544815927</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.560908622433097</v>
+        <v>-1.560908622433098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.263651580203655</v>
+        <v>0.2636515802036553</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926158008e-07</v>
+        <v>2.883344926158031e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.884156124948764e-06</v>
+        <v>7.884156124948752e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783849</v>
+        <v>0.0001024999723783846</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003763639852349073</v>
+        <v>0.0003763639852349071</v>
       </c>
       <c r="K5" t="n">
-        <v>1.85554177016652e-05</v>
+        <v>1.855541770166518e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61439957855215e-05</v>
+        <v>1.614399578552147e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062418e-05</v>
+        <v>6.671436404062417e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009760479376679872</v>
+        <v>0.00976047937667022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617872</v>
+        <v>0.002647843563618924</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278286e-05</v>
+        <v>4.081677275278289e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139062996</v>
+        <v>0.02999212139064154</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273109</v>
+        <v>0.0002773755225273108</v>
       </c>
       <c r="S5" t="n">
-        <v>5.54879729445194e-06</v>
+        <v>5.548797294452005e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070508</v>
+        <v>0.1780728838070506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0384594873809871</v>
+        <v>0.03845948738098712</v>
       </c>
       <c r="V5" t="n">
         <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003948150479346342</v>
+        <v>0.0003948150479346343</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01442301014128571</v>
+        <v>0.01442301014128574</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03021285433597503</v>
+        <v>0.03021285433597519</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2101,70 +2101,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.232919685067865</v>
+        <v>-1.232919685067864</v>
       </c>
       <c r="E6" t="n">
         <v>-1.583529197938965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2137819860167677</v>
+        <v>0.2137819860167682</v>
       </c>
       <c r="G6" t="n">
-        <v>2.629743532180662e-07</v>
+        <v>2.629743532180668e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.007446583621304e-06</v>
+        <v>7.00744658362131e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.994515887725241e-05</v>
+        <v>5.994515887725192e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.0002218360582685597</v>
       </c>
       <c r="K6" t="n">
-        <v>8.31347466172079e-06</v>
+        <v>8.313474661720788e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.011007074467619e-06</v>
+        <v>4.011007074466353e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.408844445253661e-05</v>
+        <v>2.408844445253663e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003413721912273376</v>
+        <v>0.003413721912272523</v>
       </c>
       <c r="O6" t="n">
         <v>0.001235825335481853</v>
       </c>
       <c r="P6" t="n">
-        <v>1.563588664813287e-05</v>
+        <v>1.563588664813282e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01333701183812254</v>
+        <v>0.01333701183813676</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001282976709059454</v>
+        <v>0.0001282976709059455</v>
       </c>
       <c r="S6" t="n">
-        <v>3.911559314590964e-06</v>
+        <v>3.911559314591e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05547084700405676</v>
+        <v>0.05547084700405657</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02718795563138742</v>
+        <v>0.02718795563138738</v>
       </c>
       <c r="V6" t="n">
-        <v>2.350073527008298e-06</v>
+        <v>2.350073527008297e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003134989871089377</v>
+        <v>0.0003134989871089374</v>
       </c>
       <c r="X6" t="n">
         <v>0.01138229085736367</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.024010681445482</v>
+        <v>0.02401068144548203</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2185,70 +2185,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.339682788373156</v>
+        <v>-1.339682788373189</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.594335350441187</v>
+        <v>-1.594335350441188</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1716363794886099</v>
+        <v>0.171636379488608</v>
       </c>
       <c r="G7" t="n">
-        <v>2.519333067941323e-07</v>
+        <v>2.519333067941322e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.740428647757431e-06</v>
+        <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.057975714113816e-05</v>
+        <v>4.057975714113807e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00016342582397766</v>
+        <v>0.0001634258239777693</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180671e-06</v>
+        <v>-6.666578390180675e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.408213536697689e-06</v>
+        <v>3.408213536690667e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.576179324597281e-05</v>
+        <v>-1.576179324597282e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887766097</v>
+        <v>0.00285267388776227</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003511833579318729</v>
+        <v>0.0003511833579318726</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496382e-06</v>
+        <v>-8.306313779496416e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006949757463139551</v>
+        <v>0.00694975746313548</v>
       </c>
       <c r="R7" t="n">
-        <v>5.894403635046226e-05</v>
+        <v>5.894403635046211e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.37746307082194e-06</v>
+        <v>3.377463070821951e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0165086024909827</v>
+        <v>0.0165086024909828</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02377189995167278</v>
+        <v>0.02377189995167274</v>
       </c>
       <c r="V7" t="n">
-        <v>1.710369379189881e-06</v>
+        <v>1.710369379189882e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002970973080769407</v>
+        <v>0.0002970973080769404</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01060272397536551</v>
+        <v>0.0106027239753655</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02143450870345181</v>
+        <v>0.02143450870345183</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2269,70 +2269,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.37117139927507</v>
+        <v>-1.371171399275081</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.598715785791028</v>
+        <v>-1.59871578579103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1603862493917942</v>
+        <v>0.1603862493917941</v>
       </c>
       <c r="G8" t="n">
-        <v>2.483967374914814e-07</v>
+        <v>2.483967374914811e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.617095439383973e-06</v>
+        <v>6.61709543938399e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.478206161720517e-05</v>
+        <v>3.478206161720519e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.337645370509367e-05</v>
+        <v>9.337645370509354e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.748427478810487e-06</v>
+        <v>-9.748427478810468e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.874226954002219e-06</v>
+        <v>3.874226954001006e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.274531226693064e-05</v>
+        <v>-1.27453122669307e-05</v>
       </c>
       <c r="N8" t="n">
         <v>0.002941585529239587</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0003614663475145522</v>
+        <v>0.0003614663475157461</v>
       </c>
       <c r="P8" t="n">
         <v>-6.613356735135363e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002643969675923443</v>
+        <v>0.002643969675919659</v>
       </c>
       <c r="R8" t="n">
-        <v>6.007275999553577e-05</v>
+        <v>6.007275999555168e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.142631698581975e-06</v>
+        <v>3.142631698581952e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007516435846575889</v>
+        <v>0.007516435846575863</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02247190753168227</v>
+        <v>0.02247190753168225</v>
       </c>
       <c r="V8" t="n">
         <v>1.611739468424993e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002936029220226871</v>
+        <v>0.0002936029220226865</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01042652077510717</v>
+        <v>0.01042652077510716</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02032799867849809</v>
+        <v>0.02032799867849805</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2353,70 +2353,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.006670578541264</v>
+        <v>-1.006670578541245</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.561927546685941</v>
+        <v>-1.561927546685934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2721354476889467</v>
+        <v>0.2721354476889461</v>
       </c>
       <c r="G9" t="n">
-        <v>2.832970733688312e-07</v>
+        <v>2.832970733688212e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>7.995921861823701e-06</v>
+        <v>7.995921861823711e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>9.900859556574495e-05</v>
+        <v>9.900859556574525e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003133471461987807</v>
+        <v>0.0003133471461989705</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61493272414084e-05</v>
+        <v>1.614932724148674e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.136039710518891e-06</v>
+        <v>8.136039710517989e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.561153676457527e-05</v>
+        <v>4.561153676457526e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005797721084021749</v>
+        <v>0.005797721084011204</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003056558056256897</v>
+        <v>0.003056558056256901</v>
       </c>
       <c r="P9" t="n">
-        <v>2.809672123789914e-05</v>
+        <v>2.809672123789917e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02690089148044643</v>
+        <v>0.02690089148045356</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002837415493334889</v>
+        <v>0.0002837415493334891</v>
       </c>
       <c r="S9" t="n">
-        <v>5.378735027035156e-06</v>
+        <v>5.37873502703517e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1656658326072809</v>
+        <v>0.1656658326072811</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679014917743909</v>
+        <v>0.03679014917743906</v>
       </c>
       <c r="V9" t="n">
-        <v>2.75490714269913e-06</v>
+        <v>2.754907142699132e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003578503953903428</v>
+        <v>0.0003578503953903429</v>
       </c>
       <c r="X9" t="n">
         <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03059573470754863</v>
+        <v>0.03059573470754869</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2437,70 +2437,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.209163453972457</v>
+        <v>-1.209163453972455</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.578132706625495</v>
+        <v>-1.578132706625494</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2113874502663625</v>
+        <v>0.2113874502663622</v>
       </c>
       <c r="G10" t="n">
-        <v>2.677170814798685e-07</v>
+        <v>2.677170814798682e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.589085260944306e-06</v>
+        <v>7.589085260944289e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>6.335373248768605e-05</v>
+        <v>6.335373248768569e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002098588280031237</v>
+        <v>0.0002098588280031248</v>
       </c>
       <c r="K10" t="n">
-        <v>7.300184517667924e-06</v>
+        <v>7.300184517667905e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>5.698048824358934e-06</v>
+        <v>5.698048824358931e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.691806851142321e-06</v>
+        <v>-8.691806851142426e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004311694306037251</v>
+        <v>0.004311694306037248</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006193173413198168</v>
+        <v>0.0006193173413198148</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.334224229830861e-06</v>
+        <v>-4.334224229830919e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01585268796378274</v>
+        <v>0.01585268796378326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001915181996051555</v>
+        <v>0.0001915181996051553</v>
       </c>
       <c r="S10" t="n">
-        <v>4.538711218472203e-06</v>
+        <v>4.538711218472217e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06708486893547234</v>
+        <v>0.06708486893547243</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03056298822878641</v>
+        <v>0.03056298822878644</v>
       </c>
       <c r="V10" t="n">
-        <v>2.342419147874124e-06</v>
+        <v>2.342419147874125e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003269952628084279</v>
+        <v>0.0003269952628084276</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01182402552573084</v>
+        <v>0.01182402552573083</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02651974913106418</v>
+        <v>0.0265197491310642</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2521,70 +2521,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.320902128073861</v>
+        <v>-1.320902128073936</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.590799838576672</v>
+        <v>-1.59079983857667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1837670328532782</v>
+        <v>0.1837670328532793</v>
       </c>
       <c r="G11" t="n">
-        <v>2.568577064977779e-07</v>
+        <v>2.568577064977748e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.712798471431615e-06</v>
+        <v>6.71279847143163e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.28697432763189e-05</v>
+        <v>4.286974327631883e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001449922121666099</v>
+        <v>0.0001449922121666101</v>
       </c>
       <c r="K11" t="n">
-        <v>6.257138119055725e-06</v>
+        <v>6.257138119055737e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.412994932101447e-06</v>
+        <v>6.412994932103972e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.23269052329929e-05</v>
+        <v>-1.232690523299287e-05</v>
       </c>
       <c r="N11" t="n">
         <v>0.004408068060807152</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643873</v>
+        <v>0.0003029178157642581</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430056e-06</v>
+        <v>-6.041955578430032e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01011829992180619</v>
+        <v>0.01011829992179305</v>
       </c>
       <c r="R11" t="n">
-        <v>6.924576184643165e-05</v>
+        <v>6.924576184643168e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.550865197566848e-06</v>
+        <v>3.55086519756683e-06</v>
       </c>
       <c r="T11" t="n">
         <v>0.01240561713046284</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02496506383980431</v>
+        <v>0.02496506383980428</v>
       </c>
       <c r="V11" t="n">
         <v>2.260592111522401e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003185017529477077</v>
+        <v>0.0003185017529477075</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01136342941515755</v>
+        <v>0.01136342941515748</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02198455760468091</v>
+        <v>0.02198455760468072</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2746,70 +2746,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.6182362284556138</v>
+        <v>-0.6182362284555853</v>
       </c>
       <c r="E2" t="n">
         <v>-1.54778466900461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5647350677270548</v>
+        <v>0.5647350677270541</v>
       </c>
       <c r="G2" t="n">
-        <v>2.967052734860608e-07</v>
+        <v>2.967052734860602e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.297774973716502e-06</v>
+        <v>8.29777497371649e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001214809333658798</v>
+        <v>0.0001214809333658801</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004136876998668466</v>
+        <v>0.0004136876998668453</v>
       </c>
       <c r="K2" t="n">
-        <v>2.361712977096279e-05</v>
+        <v>2.361712977096276e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26514036718877e-05</v>
+        <v>1.265140367188762e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.650721919925383e-05</v>
+        <v>8.650721919925378e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008394229475619176</v>
+        <v>0.008394229475619169</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003617560147030654</v>
+        <v>0.003617560147030652</v>
       </c>
       <c r="P2" t="n">
-        <v>5.27617611189695e-05</v>
+        <v>5.276176111896946e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03818848892145318</v>
+        <v>0.03818848892146336</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003320302303811617</v>
+        <v>0.0003320302303811612</v>
       </c>
       <c r="S2" t="n">
-        <v>6.13621329567992e-06</v>
+        <v>6.136213295679849e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2219221647279447</v>
+        <v>0.2219221647279445</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04219095408895416</v>
+        <v>0.04219095408895408</v>
       </c>
       <c r="V2" t="n">
-        <v>3.133795135691773e-06</v>
+        <v>3.133795135691774e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004002502981944433</v>
+        <v>0.0004002502981944427</v>
       </c>
       <c r="X2" t="n">
         <v>0.01478208998706381</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0342569916547195</v>
+        <v>0.03425699165471942</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2830,70 +2830,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.7406609422804703</v>
+        <v>-0.740660942280522</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.553175046228751</v>
+        <v>-1.553175046228754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4669492516850291</v>
+        <v>0.4669492516850288</v>
       </c>
       <c r="G3" t="n">
         <v>2.910982836229399e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.186346744262173e-06</v>
+        <v>8.186346744262183e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001148966337932861</v>
+        <v>0.0001148966337932871</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000380052919186653</v>
+        <v>0.0003800529191865597</v>
       </c>
       <c r="K3" t="n">
-        <v>2.259359825624112e-05</v>
+        <v>2.259359825624122e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.431199664648945e-06</v>
+        <v>9.431199664647312e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.496199314546065e-05</v>
+        <v>7.49619931454608e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006687890701509549</v>
+        <v>0.006687890701524929</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003372992321914139</v>
+        <v>0.003372992321914145</v>
       </c>
       <c r="P3" t="n">
-        <v>4.579048438156879e-05</v>
+        <v>4.579048438156895e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03459804462280596</v>
+        <v>0.03459804462276512</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003212237757524057</v>
+        <v>0.0003212237757524068</v>
       </c>
       <c r="S3" t="n">
-        <v>5.799016651922794e-06</v>
+        <v>5.799016651922795e-06</v>
       </c>
       <c r="T3" t="n">
         <v>0.2128507111936728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03988270036831717</v>
+        <v>0.0398827003683172</v>
       </c>
       <c r="V3" t="n">
-        <v>3.053801267327759e-06</v>
+        <v>3.053801267327763e-06</v>
       </c>
       <c r="W3" t="n">
         <v>0.0003750554295336959</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01383729935453029</v>
+        <v>0.01383729935453028</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03297383526331506</v>
+        <v>0.03297383526331497</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,70 +2914,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.822055435290443</v>
+        <v>-0.8220554352904307</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.55757731730959</v>
+        <v>-1.557577317309588</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4059401820380398</v>
+        <v>0.40594018203804</v>
       </c>
       <c r="G4" t="n">
-        <v>2.884956634223838e-07</v>
+        <v>2.884956634223842e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073491503656926e-06</v>
+        <v>8.073491503656966e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001085090953228941</v>
+        <v>0.000108509095322894</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000379008481248993</v>
+        <v>0.0003790084812489932</v>
       </c>
       <c r="K4" t="n">
-        <v>2.206349487019851e-05</v>
+        <v>2.20634948701985e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.152786547445034e-05</v>
+        <v>1.152786547445037e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.340097150061019e-05</v>
+        <v>6.34009715006103e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007584124395116972</v>
+        <v>0.007584124395116763</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003026883518119257</v>
+        <v>0.003026883518119254</v>
       </c>
       <c r="P4" t="n">
-        <v>3.876270632857587e-05</v>
+        <v>3.876270632857589e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03307471650933395</v>
+        <v>0.03307471650934212</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0003016517052066227</v>
+        <v>0.0003016517052066577</v>
       </c>
       <c r="S4" t="n">
-        <v>5.655265380564697e-06</v>
+        <v>5.655265380564699e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2000520167655541</v>
+        <v>0.2000520167655542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03893406919391235</v>
+        <v>0.03893406919391237</v>
       </c>
       <c r="V4" t="n">
-        <v>3.019154090207048e-06</v>
+        <v>3.019154090207047e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003770377104592977</v>
+        <v>0.000377037710459298</v>
       </c>
       <c r="X4" t="n">
         <v>0.01385317096912711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03173767865041881</v>
+        <v>0.0317376786504189</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2998,70 +2998,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8754081291484328</v>
+        <v>-0.8754081291484449</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.560908622433097</v>
+        <v>-1.560908622433098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3806219055814966</v>
+        <v>0.3806219055814978</v>
       </c>
       <c r="G5" t="n">
-        <v>2.883344926158008e-07</v>
+        <v>2.883344926158031e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.884156124948764e-06</v>
+        <v>7.884156124948752e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001024999723783849</v>
+        <v>0.0001024999723783846</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003763639852349073</v>
+        <v>0.0003763639852349071</v>
       </c>
       <c r="K5" t="n">
-        <v>1.85554177016652e-05</v>
+        <v>1.855541770166518e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61439957855215e-05</v>
+        <v>1.614399578552147e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.671436404062418e-05</v>
+        <v>6.671436404062417e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009760479376679872</v>
+        <v>0.00976047937667022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002647843563617872</v>
+        <v>0.002647843563618924</v>
       </c>
       <c r="P5" t="n">
-        <v>4.081677275278286e-05</v>
+        <v>4.081677275278289e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02999212139062996</v>
+        <v>0.02999212139064154</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002773755225273109</v>
+        <v>0.0002773755225273108</v>
       </c>
       <c r="S5" t="n">
-        <v>5.54879729445194e-06</v>
+        <v>5.548797294452005e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1780728838070508</v>
+        <v>0.1780728838070506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0384594873809871</v>
+        <v>0.03845948738098712</v>
       </c>
       <c r="V5" t="n">
         <v>2.860903834275749e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003948150479346342</v>
+        <v>0.0003948150479346343</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01442301014128571</v>
+        <v>0.01442301014128574</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03021285433597503</v>
+        <v>0.03021285433597519</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3082,70 +3082,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.127739769395991</v>
+        <v>-1.127739769395988</v>
       </c>
       <c r="E6" t="n">
         <v>-1.583529197938965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3189619017288297</v>
+        <v>0.3189619017288301</v>
       </c>
       <c r="G6" t="n">
-        <v>2.629743532180662e-07</v>
+        <v>2.629743532180668e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.007446583621304e-06</v>
+        <v>7.00744658362131e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.994515887725241e-05</v>
+        <v>5.994515887725192e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.0002218360582685597</v>
       </c>
       <c r="K6" t="n">
-        <v>8.31347466172079e-06</v>
+        <v>8.313474661720788e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.011007074467619e-06</v>
+        <v>4.011007074466353e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.408844445253661e-05</v>
+        <v>2.408844445253663e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003413721912273376</v>
+        <v>0.003413721912272523</v>
       </c>
       <c r="O6" t="n">
         <v>0.001235825335481853</v>
       </c>
       <c r="P6" t="n">
-        <v>1.563588664813287e-05</v>
+        <v>1.563588664813282e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01333701183812254</v>
+        <v>0.01333701183813676</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001282976709059454</v>
+        <v>0.0001282976709059455</v>
       </c>
       <c r="S6" t="n">
-        <v>3.911559314590964e-06</v>
+        <v>3.911559314591e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05547084700405676</v>
+        <v>0.05547084700405657</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02718795563138742</v>
+        <v>0.02718795563138738</v>
       </c>
       <c r="V6" t="n">
-        <v>2.350073527008298e-06</v>
+        <v>2.350073527008297e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003134989871089377</v>
+        <v>0.0003134989871089374</v>
       </c>
       <c r="X6" t="n">
         <v>0.01138229085736367</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.024010681445482</v>
+        <v>0.02401068144548203</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3166,70 +3166,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.256227195365527</v>
+        <v>-1.256227195365536</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.594335350441187</v>
+        <v>-1.594335350441188</v>
       </c>
       <c r="F7" t="n">
         <v>0.2550919725281223</v>
       </c>
       <c r="G7" t="n">
-        <v>2.519333067941323e-07</v>
+        <v>2.519333067941322e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.740428647757431e-06</v>
+        <v>6.740428647757436e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.057975714113816e-05</v>
+        <v>4.057975714113807e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00016342582397766</v>
+        <v>0.0001634258239777693</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.666578390180671e-06</v>
+        <v>-6.666578390180675e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.408213536697689e-06</v>
+        <v>3.408213536690667e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.576179324597281e-05</v>
+        <v>-1.576179324597282e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002852673887766097</v>
+        <v>0.00285267388776227</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003511833579318729</v>
+        <v>0.0003511833579318726</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.306313779496382e-06</v>
+        <v>-8.306313779496416e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006949757463139551</v>
+        <v>0.00694975746313548</v>
       </c>
       <c r="R7" t="n">
-        <v>5.894403635046226e-05</v>
+        <v>5.894403635046211e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.37746307082194e-06</v>
+        <v>3.377463070821951e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0165086024909827</v>
+        <v>0.0165086024909828</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02377189995167278</v>
+        <v>0.02377189995167274</v>
       </c>
       <c r="V7" t="n">
-        <v>1.710369379189881e-06</v>
+        <v>1.710369379189882e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002970973080769407</v>
+        <v>0.0002970973080769404</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01060272397536551</v>
+        <v>0.0106027239753655</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02143450870345181</v>
+        <v>0.02143450870345183</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3250,70 +3250,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.29842374937431</v>
+        <v>-1.29842374937432</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.598715785791028</v>
+        <v>-1.59871578579103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2331338993203419</v>
+        <v>0.2331338993203417</v>
       </c>
       <c r="G8" t="n">
-        <v>2.483967374914814e-07</v>
+        <v>2.483967374914811e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.617095439383973e-06</v>
+        <v>6.61709543938399e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>3.478206161720517e-05</v>
+        <v>3.478206161720519e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.337645370509367e-05</v>
+        <v>9.337645370509354e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.748427478810487e-06</v>
+        <v>-9.748427478810468e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>3.874226954002219e-06</v>
+        <v>3.874226954001006e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.274531226693064e-05</v>
+        <v>-1.27453122669307e-05</v>
       </c>
       <c r="N8" t="n">
         <v>0.002941585529239587</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0003614663475145522</v>
+        <v>0.0003614663475157461</v>
       </c>
       <c r="P8" t="n">
         <v>-6.613356735135363e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002643969675923443</v>
+        <v>0.002643969675919659</v>
       </c>
       <c r="R8" t="n">
-        <v>6.007275999553577e-05</v>
+        <v>6.007275999555168e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>3.142631698581975e-06</v>
+        <v>3.142631698581952e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007516435846575889</v>
+        <v>0.007516435846575863</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02247190753168227</v>
+        <v>0.02247190753168225</v>
       </c>
       <c r="V8" t="n">
         <v>1.611739468424993e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002936029220226871</v>
+        <v>0.0002936029220226865</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01042652077510717</v>
+        <v>0.01042652077510716</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02032799867849809</v>
+        <v>0.02032799867849805</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3334,70 +3334,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8456452961338242</v>
+        <v>-0.8456452961337952</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.561927546685941</v>
+        <v>-1.561927546685934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4331607301579167</v>
+        <v>0.4331607301579166</v>
       </c>
       <c r="G9" t="n">
-        <v>2.832970733688312e-07</v>
+        <v>2.832970733688212e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>7.995921861823701e-06</v>
+        <v>7.995921861823711e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>9.900859556574495e-05</v>
+        <v>9.900859556574525e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003133471461987807</v>
+        <v>0.0003133471461989705</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61493272414084e-05</v>
+        <v>1.614932724148674e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.136039710518891e-06</v>
+        <v>8.136039710517989e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>4.561153676457527e-05</v>
+        <v>4.561153676457526e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005797721084021749</v>
+        <v>0.005797721084011204</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003056558056256897</v>
+        <v>0.003056558056256901</v>
       </c>
       <c r="P9" t="n">
-        <v>2.809672123789914e-05</v>
+        <v>2.809672123789917e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02690089148044643</v>
+        <v>0.02690089148045356</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0002837415493334889</v>
+        <v>0.0002837415493334891</v>
       </c>
       <c r="S9" t="n">
-        <v>5.378735027035156e-06</v>
+        <v>5.37873502703517e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1656658326072809</v>
+        <v>0.1656658326072811</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679014917743909</v>
+        <v>0.03679014917743906</v>
       </c>
       <c r="V9" t="n">
-        <v>2.75490714269913e-06</v>
+        <v>2.754907142699132e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003578503953903428</v>
+        <v>0.0003578503953903429</v>
       </c>
       <c r="X9" t="n">
         <v>0.01314623943529364</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03059573470754863</v>
+        <v>0.03059573470754869</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3418,70 +3418,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.089846263233559</v>
+        <v>-1.089846263233556</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.578132706625495</v>
+        <v>-1.578132706625494</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3307046410508487</v>
+        <v>0.3307046410508484</v>
       </c>
       <c r="G10" t="n">
-        <v>2.677170814798685e-07</v>
+        <v>2.677170814798682e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>7.589085260944306e-06</v>
+        <v>7.589085260944289e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>6.335373248768605e-05</v>
+        <v>6.335373248768569e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002098588280031237</v>
+        <v>0.0002098588280031248</v>
       </c>
       <c r="K10" t="n">
-        <v>7.300184517667924e-06</v>
+        <v>7.300184517667905e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>5.698048824358934e-06</v>
+        <v>5.698048824358931e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.691806851142321e-06</v>
+        <v>-8.691806851142426e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004311694306037251</v>
+        <v>0.004311694306037248</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006193173413198168</v>
+        <v>0.0006193173413198148</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.334224229830861e-06</v>
+        <v>-4.334224229830919e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01585268796378274</v>
+        <v>0.01585268796378326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001915181996051555</v>
+        <v>0.0001915181996051553</v>
       </c>
       <c r="S10" t="n">
-        <v>4.538711218472203e-06</v>
+        <v>4.538711218472217e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06708486893547234</v>
+        <v>0.06708486893547243</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03056298822878641</v>
+        <v>0.03056298822878644</v>
       </c>
       <c r="V10" t="n">
-        <v>2.342419147874124e-06</v>
+        <v>2.342419147874125e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0003269952628084279</v>
+        <v>0.0003269952628084276</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01182402552573084</v>
+        <v>0.01182402552573083</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02651974913106418</v>
+        <v>0.0265197491310642</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -3502,70 +3502,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.247518287572989</v>
+        <v>-1.247518287573037</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.590799838576672</v>
+        <v>-1.59079983857667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2571508733822173</v>
+        <v>0.2571508733822183</v>
       </c>
       <c r="G11" t="n">
-        <v>2.568577064977779e-07</v>
+        <v>2.568577064977748e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>6.712798471431615e-06</v>
+        <v>6.71279847143163e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>4.28697432763189e-05</v>
+        <v>4.286974327631883e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001449922121666099</v>
+        <v>0.0001449922121666101</v>
       </c>
       <c r="K11" t="n">
-        <v>6.257138119055725e-06</v>
+        <v>6.257138119055737e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>6.412994932101447e-06</v>
+        <v>6.412994932103972e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.23269052329929e-05</v>
+        <v>-1.232690523299287e-05</v>
       </c>
       <c r="N11" t="n">
         <v>0.004408068060807152</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0003029178157643873</v>
+        <v>0.0003029178157642581</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.041955578430056e-06</v>
+        <v>-6.041955578430032e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01011829992180619</v>
+        <v>0.01011829992179305</v>
       </c>
       <c r="R11" t="n">
-        <v>6.924576184643165e-05</v>
+        <v>6.924576184643168e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>3.550865197566848e-06</v>
+        <v>3.55086519756683e-06</v>
       </c>
       <c r="T11" t="n">
         <v>0.01240561713046284</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02496506383980431</v>
+        <v>0.02496506383980428</v>
       </c>
       <c r="V11" t="n">
         <v>2.260592111522401e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003185017529477077</v>
+        <v>0.0003185017529477075</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01136342941515755</v>
+        <v>0.01136342941515748</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02198455760468091</v>
+        <v>0.02198455760468072</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change breakdown results.xlsx
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4522675830125251</v>
+        <v>0.4129398937825455</v>
       </c>
       <c r="E2" t="n">
         <v>0.1855477198404307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1842056793660092</v>
+        <v>0.1448779891618527</v>
       </c>
       <c r="G2" t="n">
         <v>0.05008330144474999</v>
@@ -1147,7 +1147,7 @@
         <v>0.001368727882702077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600368126354</v>
+        <v>0.02910600465544028</v>
       </c>
     </row>
     <row r="3">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4453357313820738</v>
+        <v>0.4076156296857565</v>
       </c>
       <c r="E3" t="n">
         <v>0.1838291906059024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1810356617099658</v>
+        <v>0.1433155590792927</v>
       </c>
       <c r="G3" t="n">
         <v>0.04821494231345644</v>
@@ -1198,7 +1198,7 @@
         <v>0.001280091146362091</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600367548388</v>
+        <v>0.0291060046098397</v>
       </c>
     </row>
     <row r="4">
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4378556903599112</v>
+        <v>0.4024036950406004</v>
       </c>
       <c r="E4" t="n">
         <v>0.1826388398155669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1774227268687051</v>
+        <v>0.1419707306712215</v>
       </c>
       <c r="G4" t="n">
         <v>0.04572335899261109</v>
@@ -1249,7 +1249,7 @@
         <v>0.00116444707890675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910600369103017</v>
+        <v>0.02910600456920293</v>
       </c>
     </row>
     <row r="5">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4276574441081791</v>
+        <v>0.3961004563542284</v>
       </c>
       <c r="E5" t="n">
         <v>0.1818503269076333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1722455894286758</v>
+        <v>0.1406886008930344</v>
       </c>
       <c r="G5" t="n">
         <v>0.0416185757057598</v>
@@ -1300,7 +1300,7 @@
         <v>0.001100141444635164</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600373837857</v>
+        <v>0.02910600452006917</v>
       </c>
     </row>
     <row r="6">
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.359353014398837</v>
+        <v>0.3495228100342862</v>
       </c>
       <c r="E6" t="n">
         <v>0.173434118133929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.141564273077381</v>
+        <v>0.1317340684693282</v>
       </c>
       <c r="G6" t="n">
         <v>0.01323200409367942</v>
@@ -1351,7 +1351,7 @@
         <v>0.0007693260029412944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600383690415</v>
+        <v>0.02910600408040614</v>
       </c>
     </row>
     <row r="7">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3344335188953276</v>
+        <v>0.331507965293313</v>
       </c>
       <c r="E7" t="n">
         <v>0.1692967986780907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1304482014982728</v>
+        <v>0.1275226478237903</v>
       </c>
       <c r="G7" t="n">
         <v>0.004005592633530714</v>
@@ -1402,7 +1402,7 @@
         <v>0.0005395976008691132</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600384823903</v>
+        <v>0.02910600392070684</v>
       </c>
     </row>
     <row r="8">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3270171721505907</v>
+        <v>0.3256851553443668</v>
       </c>
       <c r="E8" t="n">
         <v>0.1677644037114066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1272103311847718</v>
+        <v>0.1258783143455528</v>
       </c>
       <c r="G8" t="n">
         <v>0.001516222820624147</v>
@@ -1453,7 +1453,7 @@
         <v>0.0004547630681316607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600384257772</v>
+        <v>0.02910600387557288</v>
       </c>
     </row>
     <row r="9">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.420824715022991</v>
+        <v>0.3914664290275745</v>
       </c>
       <c r="E9" t="n">
         <v>0.1807834979870836</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1690082428492414</v>
+        <v>0.1396499561265977</v>
       </c>
       <c r="G9" t="n">
         <v>0.03912270071841054</v>
@@ -1504,7 +1504,7 @@
         <v>0.001105987666444344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.029106003749439</v>
+        <v>0.02910600447666623</v>
       </c>
     </row>
     <row r="10">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3670682053263773</v>
+        <v>0.3551798350017525</v>
       </c>
       <c r="E10" t="n">
         <v>0.1746507049116372</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1444663660873451</v>
+        <v>0.1325779954682365</v>
       </c>
       <c r="G10" t="n">
         <v>0.01671526278688338</v>
@@ -1555,7 +1555,7 @@
         <v>0.0007715364328737178</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600385288925</v>
+        <v>0.02910600414737313</v>
       </c>
     </row>
     <row r="11">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3353323123361699</v>
+        <v>0.3331338647146303</v>
       </c>
       <c r="E11" t="n">
         <v>0.170583902760846</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1310728071759925</v>
+        <v>0.1288743594999962</v>
       </c>
       <c r="G11" t="n">
         <v>0.002880084518684512</v>
@@ -1606,7 +1606,7 @@
         <v>0.0006026319471648396</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02910600386288237</v>
+        <v>0.02910600391733908</v>
       </c>
     </row>
   </sheetData>
